--- a/セリフ編集/キャラタイプ別/クール×寡黙.xlsx
+++ b/セリフ編集/キャラタイプ別/クール×寡黙.xlsx
@@ -306,7 +306,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H264"/>
+  <dimension ref="A1:H297"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1580,7 +1580,7 @@
     <row r="40" ht="40" customHeight="1">
       <c r="A40" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.quiet.cool[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
@@ -1590,12 +1590,12 @@
       </c>
       <c r="C40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES</t>
         </is>
       </c>
       <c r="D40" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.quiet.cool[1]</t>
+          <t xml:space="preserve">ahead.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E40" t="inlineStr" s="2">
@@ -1605,14 +1605,14 @@
       </c>
       <c r="F40" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（静かに目を閉じる）</t>
+          <t xml:space="preserve">……終わった。それだけだ。……それだけのはずだ</t>
         </is>
       </c>
     </row>
     <row r="41" ht="40" customHeight="1">
       <c r="A41" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.quiet.cool[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
@@ -1622,12 +1622,12 @@
       </c>
       <c r="C41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES</t>
         </is>
       </c>
       <c r="D41" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.quiet.cool[1]</t>
+          <t xml:space="preserve">behind.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr" s="2">
@@ -1637,14 +1637,14 @@
       </c>
       <c r="F41" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もう終わった</t>
+          <t xml:space="preserve">……終わっていない。……私の中では</t>
         </is>
       </c>
     </row>
     <row r="42" ht="40" customHeight="1">
       <c r="A42" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.quiet.cool[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D42" t="inlineStr" s="12">
@@ -1669,14 +1669,14 @@
       </c>
       <c r="F42" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……負けた。……でも、悔いはない</t>
+          <t xml:space="preserve">………（静かに目を閉じる）</t>
         </is>
       </c>
     </row>
     <row r="43" ht="40" customHeight="1">
       <c r="A43" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.quiet.cool[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="C43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D43" t="inlineStr" s="12">
@@ -1701,14 +1701,14 @@
       </c>
       <c r="F43" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ありがとう。……これからも</t>
+          <t xml:space="preserve">……もう終わった</t>
         </is>
       </c>
     </row>
     <row r="44" ht="40" customHeight="1">
       <c r="A44" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.quiet.cool[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
@@ -1718,12 +1718,12 @@
       </c>
       <c r="C44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D44" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.quiet.cool[1]</t>
+          <t xml:space="preserve">loser.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E44" t="inlineStr" s="2">
@@ -1733,14 +1733,14 @@
       </c>
       <c r="F44" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ここで、終わる</t>
+          <t xml:space="preserve">……負けた。……でも、悔いはない</t>
         </is>
       </c>
     </row>
     <row r="45" ht="40" customHeight="1">
       <c r="A45" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.quiet.cool[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
@@ -1750,12 +1750,12 @@
       </c>
       <c r="C45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D45" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.quiet.cool[1]</t>
+          <t xml:space="preserve">winner.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E45" t="inlineStr" s="2">
@@ -1765,14 +1765,14 @@
       </c>
       <c r="F45" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……来い</t>
+          <t xml:space="preserve">……ありがとう。……これからも</t>
         </is>
       </c>
     </row>
     <row r="46" ht="40" customHeight="1">
       <c r="A46" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.quiet.cool[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
@@ -1782,12 +1782,12 @@
       </c>
       <c r="C46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
         </is>
       </c>
       <c r="D46" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.quiet.cool[1]</t>
+          <t xml:space="preserve">attacker.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E46" t="inlineStr" s="2">
@@ -1797,14 +1797,14 @@
       </c>
       <c r="F46" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（目を閉じ、開く）</t>
+          <t xml:space="preserve">……ここで、終わる</t>
         </is>
       </c>
     </row>
     <row r="47" ht="40" customHeight="1">
       <c r="A47" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.quiet.cool[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
@@ -1814,12 +1814,12 @@
       </c>
       <c r="C47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
         </is>
       </c>
       <c r="D47" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.quiet.cool[1]</t>
+          <t xml:space="preserve">defender.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E47" t="inlineStr" s="2">
@@ -1829,14 +1829,14 @@
       </c>
       <c r="F47" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……今日、決める</t>
+          <t xml:space="preserve">……来い</t>
         </is>
       </c>
     </row>
     <row r="48" ht="40" customHeight="1">
       <c r="A48" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.quiet.cool[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
         </is>
       </c>
       <c r="D48" t="inlineStr" s="12">
@@ -1861,14 +1861,14 @@
       </c>
       <c r="F48" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……いいだろう</t>
+          <t xml:space="preserve">………（目を閉じ、開く）</t>
         </is>
       </c>
     </row>
     <row r="49" ht="40" customHeight="1">
       <c r="A49" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.quiet.cool[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
@@ -1878,12 +1878,12 @@
       </c>
       <c r="C49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
         </is>
       </c>
       <c r="D49" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.quiet.cool[1]</t>
+          <t xml:space="preserve">attacker.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E49" t="inlineStr" s="2">
@@ -1893,14 +1893,14 @@
       </c>
       <c r="F49" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次だ</t>
+          <t xml:space="preserve">……今日、決める</t>
         </is>
       </c>
     </row>
     <row r="50" ht="40" customHeight="1">
       <c r="A50" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.quiet.cool[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
         </is>
       </c>
       <c r="D50" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.quiet.cool[1]</t>
+          <t xml:space="preserve">defender.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E50" t="inlineStr" s="2">
@@ -1925,14 +1925,14 @@
       </c>
       <c r="F50" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まだ終わらない</t>
+          <t xml:space="preserve">……いいだろう</t>
         </is>
       </c>
     </row>
     <row r="51" ht="40" customHeight="1">
       <c r="A51" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.quiet.cool[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="C51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
         </is>
       </c>
       <c r="D51" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.quiet.cool[1]</t>
+          <t xml:space="preserve">loserLines.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E51" t="inlineStr" s="2">
@@ -1957,14 +1957,14 @@
       </c>
       <c r="F51" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…今日は負けた。…次だ</t>
+          <t xml:space="preserve">……次だ</t>
         </is>
       </c>
     </row>
     <row r="52" ht="40" customHeight="1">
       <c r="A52" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.quiet.cool[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
@@ -1974,12 +1974,12 @@
       </c>
       <c r="C52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
         </is>
       </c>
       <c r="D52" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.quiet.cool[1]</t>
+          <t xml:space="preserve">winnerLines.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E52" t="inlineStr" s="2">
@@ -1989,14 +1989,14 @@
       </c>
       <c r="F52" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一区切り。…でも、終わった気はしない</t>
+          <t xml:space="preserve">……まだ終わらない</t>
         </is>
       </c>
     </row>
     <row r="53" ht="40" customHeight="1">
       <c r="A53" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.quiet.cool[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -2006,12 +2006,12 @@
       </c>
       <c r="C53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D53" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.quiet.cool[1]</t>
+          <t xml:space="preserve">loser.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E53" t="inlineStr" s="2">
@@ -2021,14 +2021,14 @@
       </c>
       <c r="F53" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（膝をつき、動かない）</t>
+          <t xml:space="preserve">…今日は負けた。…次だ</t>
         </is>
       </c>
     </row>
     <row r="54" ht="40" customHeight="1">
       <c r="A54" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.quiet.cool[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -2038,12 +2038,12 @@
       </c>
       <c r="C54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D54" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.quiet.cool[1]</t>
+          <t xml:space="preserve">winner.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E54" t="inlineStr" s="2">
@@ -2053,14 +2053,14 @@
       </c>
       <c r="F54" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝った。……信じられない</t>
+          <t xml:space="preserve">…一区切り。…でも、終わった気はしない</t>
         </is>
       </c>
     </row>
     <row r="55" ht="40" customHeight="1">
       <c r="A55" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.quiet.cool[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
         </is>
       </c>
       <c r="D55" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">awakening.quiet.cool[1]</t>
+          <t xml:space="preserve">loserLines.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E55" t="inlineStr" s="2">
@@ -2085,14 +2085,14 @@
       </c>
       <c r="F55" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameB}が無言で{nameA}の前に立ちはだかった。その目は——もう、以前の{nameB}ではなかった</t>
+          <t xml:space="preserve">………（膝をつき、動かない）</t>
         </is>
       </c>
     </row>
     <row r="56" ht="40" customHeight="1">
       <c r="A56" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.cool_quiet.lose[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -2102,29 +2102,29 @@
       </c>
       <c r="C56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
         </is>
       </c>
       <c r="D56" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool_quiet.lose[1]</t>
+          <t xml:space="preserve">winnerLines.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">03 因縁・絆(Bond/Rivalry)イベント</t>
         </is>
       </c>
       <c r="F56" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……負けました。すみません。</t>
+          <t xml:space="preserve">……勝った。……信じられない</t>
         </is>
       </c>
     </row>
     <row r="57" ht="40" customHeight="1">
       <c r="A57" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.cool_quiet.lose[2]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
@@ -2134,29 +2134,29 @@
       </c>
       <c r="C57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
         </is>
       </c>
       <c r="D57" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool_quiet.lose[2]</t>
+          <t xml:space="preserve">awakening.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">03 因縁・絆(Bond/Rivalry)イベント</t>
         </is>
       </c>
       <c r="F57" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……だめでした。それだけです。</t>
+          <t xml:space="preserve">{nameB}が無言で{nameA}の前に立ちはだかった。その目は——もう、以前の{nameB}ではなかった</t>
         </is>
       </c>
     </row>
     <row r="58" ht="40" customHeight="1">
       <c r="A58" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.cool_quiet.lose[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.cool_quiet.lose[1]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="D58" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool_quiet.lose[3]</t>
+          <t xml:space="preserve">cool_quiet.lose[1]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr" s="2">
@@ -2181,14 +2181,14 @@
       </c>
       <c r="F58" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次は、勝ちます。</t>
+          <t xml:space="preserve">……負けました。すみません。</t>
         </is>
       </c>
     </row>
     <row r="59" ht="40" customHeight="1">
       <c r="A59" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.cool_quiet.petition[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.cool_quiet.lose[2]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="D59" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool_quiet.petition[1]</t>
+          <t xml:space="preserve">cool_quiet.lose[2]</t>
         </is>
       </c>
       <c r="E59" t="inlineStr" s="2">
@@ -2213,14 +2213,14 @@
       </c>
       <c r="F59" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……社長。あの人と。</t>
+          <t xml:space="preserve">……だめでした。それだけです。</t>
         </is>
       </c>
     </row>
     <row r="60" ht="40" customHeight="1">
       <c r="A60" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.cool_quiet.petition[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.cool_quiet.lose[3]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="D60" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool_quiet.petition[2]</t>
+          <t xml:space="preserve">cool_quiet.lose[3]</t>
         </is>
       </c>
       <c r="E60" t="inlineStr" s="2">
@@ -2245,14 +2245,14 @@
       </c>
       <c r="F60" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……願いが、ひとつ。あの人と。</t>
+          <t xml:space="preserve">……次は、勝ちます。</t>
         </is>
       </c>
     </row>
     <row r="61" ht="40" customHeight="1">
       <c r="A61" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.cool_quiet.petition[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.cool_quiet.petition[1]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="D61" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool_quiet.petition[3]</t>
+          <t xml:space="preserve">cool_quiet.petition[1]</t>
         </is>
       </c>
       <c r="E61" t="inlineStr" s="2">
@@ -2277,14 +2277,14 @@
       </c>
       <c r="F61" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……やりたい相手が、います。</t>
+          <t xml:space="preserve">……社長。あの人と。</t>
         </is>
       </c>
     </row>
     <row r="62" ht="40" customHeight="1">
       <c r="A62" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.cool_quiet.sendoff[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.cool_quiet.petition[2]</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="2">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="D62" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool_quiet.sendoff[1]</t>
+          <t xml:space="preserve">cool_quiet.petition[2]</t>
         </is>
       </c>
       <c r="E62" t="inlineStr" s="2">
@@ -2309,14 +2309,14 @@
       </c>
       <c r="F62" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ありがとうございます。行きます。</t>
+          <t xml:space="preserve">……願いが、ひとつ。あの人と。</t>
         </is>
       </c>
     </row>
     <row r="63" ht="40" customHeight="1">
       <c r="A63" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.cool_quiet.sendoff[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.cool_quiet.petition[3]</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="2">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="D63" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool_quiet.sendoff[2]</t>
+          <t xml:space="preserve">cool_quiet.petition[3]</t>
         </is>
       </c>
       <c r="E63" t="inlineStr" s="2">
@@ -2341,14 +2341,14 @@
       </c>
       <c r="F63" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……行ってきます。</t>
+          <t xml:space="preserve">……やりたい相手が、います。</t>
         </is>
       </c>
     </row>
     <row r="64" ht="40" customHeight="1">
       <c r="A64" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.cool_quiet.sendoff[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.cool_quiet.sendoff[1]</t>
         </is>
       </c>
       <c r="B64" t="inlineStr" s="2">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="D64" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool_quiet.sendoff[3]</t>
+          <t xml:space="preserve">cool_quiet.sendoff[1]</t>
         </is>
       </c>
       <c r="E64" t="inlineStr" s="2">
@@ -2373,14 +2373,14 @@
       </c>
       <c r="F64" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……感謝を。では。</t>
+          <t xml:space="preserve">……ありがとうございます。行きます。</t>
         </is>
       </c>
     </row>
     <row r="65" ht="40" customHeight="1">
       <c r="A65" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.cool_quiet.win[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.cool_quiet.sendoff[2]</t>
         </is>
       </c>
       <c r="B65" t="inlineStr" s="2">
@@ -2395,7 +2395,7 @@
       </c>
       <c r="D65" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool_quiet.win[1]</t>
+          <t xml:space="preserve">cool_quiet.sendoff[2]</t>
         </is>
       </c>
       <c r="E65" t="inlineStr" s="2">
@@ -2405,14 +2405,14 @@
       </c>
       <c r="F65" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝ちました。</t>
+          <t xml:space="preserve">……行ってきます。</t>
         </is>
       </c>
     </row>
     <row r="66" ht="40" customHeight="1">
       <c r="A66" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.cool_quiet.win[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.cool_quiet.sendoff[3]</t>
         </is>
       </c>
       <c r="B66" t="inlineStr" s="2">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="D66" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool_quiet.win[2]</t>
+          <t xml:space="preserve">cool_quiet.sendoff[3]</t>
         </is>
       </c>
       <c r="E66" t="inlineStr" s="2">
@@ -2437,14 +2437,14 @@
       </c>
       <c r="F66" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝ち。ありがとうございます。</t>
+          <t xml:space="preserve">……感謝を。では。</t>
         </is>
       </c>
     </row>
     <row r="67" ht="40" customHeight="1">
       <c r="A67" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.cool_quiet.win[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.cool_quiet.win[1]</t>
         </is>
       </c>
       <c r="B67" t="inlineStr" s="2">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="D67" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool_quiet.win[3]</t>
+          <t xml:space="preserve">cool_quiet.win[1]</t>
         </is>
       </c>
       <c r="E67" t="inlineStr" s="2">
@@ -2469,14 +2469,14 @@
       </c>
       <c r="F67" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……終わりました。報告まで。</t>
+          <t xml:space="preserve">……勝ちました。</t>
         </is>
       </c>
     </row>
     <row r="68" ht="40" customHeight="1">
       <c r="A68" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.cool_quiet._accept[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.cool_quiet.win[2]</t>
         </is>
       </c>
       <c r="B68" t="inlineStr" s="2">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="C68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D68" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool_quiet._accept[1]</t>
+          <t xml:space="preserve">cool_quiet.win[2]</t>
         </is>
       </c>
       <c r="E68" t="inlineStr" s="2">
@@ -2501,14 +2501,14 @@
       </c>
       <c r="F68" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……受ける。</t>
+          <t xml:space="preserve">……勝ち。ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="69" ht="40" customHeight="1">
       <c r="A69" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.cool_quiet._accept[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.cool_quiet.win[3]</t>
         </is>
       </c>
       <c r="B69" t="inlineStr" s="2">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="C69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D69" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool_quiet._accept[2]</t>
+          <t xml:space="preserve">cool_quiet.win[3]</t>
         </is>
       </c>
       <c r="E69" t="inlineStr" s="2">
@@ -2533,14 +2533,14 @@
       </c>
       <c r="F69" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……いい。</t>
+          <t xml:space="preserve">……終わりました。報告まで。</t>
         </is>
       </c>
     </row>
     <row r="70" ht="40" customHeight="1">
       <c r="A70" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.cool_quiet._accept[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.cool_quiet._accept[1]</t>
         </is>
       </c>
       <c r="B70" t="inlineStr" s="2">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="D70" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool_quiet._accept[3]</t>
+          <t xml:space="preserve">cool_quiet._accept[1]</t>
         </is>
       </c>
       <c r="E70" t="inlineStr" s="2">
@@ -2565,14 +2565,14 @@
       </c>
       <c r="F70" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……来い。</t>
+          <t xml:space="preserve">……受ける。</t>
         </is>
       </c>
     </row>
     <row r="71" ht="40" customHeight="1">
       <c r="A71" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.cool_quiet.draw[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.cool_quiet._accept[2]</t>
         </is>
       </c>
       <c r="B71" t="inlineStr" s="2">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="D71" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool_quiet.draw[1]</t>
+          <t xml:space="preserve">cool_quiet._accept[2]</t>
         </is>
       </c>
       <c r="E71" t="inlineStr" s="2">
@@ -2597,14 +2597,14 @@
       </c>
       <c r="F71" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……引き分け。</t>
+          <t xml:space="preserve">……いい。</t>
         </is>
       </c>
     </row>
     <row r="72" ht="40" customHeight="1">
       <c r="A72" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.cool_quiet.draw[2]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.cool_quiet._accept[3]</t>
         </is>
       </c>
       <c r="B72" t="inlineStr" s="2">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="D72" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool_quiet.draw[2]</t>
+          <t xml:space="preserve">cool_quiet._accept[3]</t>
         </is>
       </c>
       <c r="E72" t="inlineStr" s="2">
@@ -2629,14 +2629,14 @@
       </c>
       <c r="F72" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……また。</t>
+          <t xml:space="preserve">……来い。</t>
         </is>
       </c>
     </row>
     <row r="73" ht="40" customHeight="1">
       <c r="A73" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.cool_quiet.draw[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.cool_quiet.draw[1]</t>
         </is>
       </c>
       <c r="B73" t="inlineStr" s="2">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="D73" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool_quiet.draw[3]</t>
+          <t xml:space="preserve">cool_quiet.draw[1]</t>
         </is>
       </c>
       <c r="E73" t="inlineStr" s="2">
@@ -2661,14 +2661,14 @@
       </c>
       <c r="F73" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……足りない。</t>
+          <t xml:space="preserve">……決着つかず。</t>
         </is>
       </c>
     </row>
     <row r="74" ht="40" customHeight="1">
       <c r="A74" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.cool_quiet.lose[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.cool_quiet.draw[2]</t>
         </is>
       </c>
       <c r="B74" t="inlineStr" s="2">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="D74" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool_quiet.lose[1]</t>
+          <t xml:space="preserve">cool_quiet.draw[2]</t>
         </is>
       </c>
       <c r="E74" t="inlineStr" s="2">
@@ -2693,14 +2693,14 @@
       </c>
       <c r="F74" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……負けだ。</t>
+          <t xml:space="preserve">……また。</t>
         </is>
       </c>
     </row>
     <row r="75" ht="40" customHeight="1">
       <c r="A75" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.cool_quiet.lose[2]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.cool_quiet.draw[3]</t>
         </is>
       </c>
       <c r="B75" t="inlineStr" s="2">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="D75" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool_quiet.lose[2]</t>
+          <t xml:space="preserve">cool_quiet.draw[3]</t>
         </is>
       </c>
       <c r="E75" t="inlineStr" s="2">
@@ -2725,14 +2725,14 @@
       </c>
       <c r="F75" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……強い。</t>
+          <t xml:space="preserve">……足りない。</t>
         </is>
       </c>
     </row>
     <row r="76" ht="40" customHeight="1">
       <c r="A76" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.cool_quiet.lose[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.cool_quiet.lose[1]</t>
         </is>
       </c>
       <c r="B76" t="inlineStr" s="2">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="D76" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool_quiet.lose[3]</t>
+          <t xml:space="preserve">cool_quiet.lose[1]</t>
         </is>
       </c>
       <c r="E76" t="inlineStr" s="2">
@@ -2757,14 +2757,14 @@
       </c>
       <c r="F76" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そうか。</t>
+          <t xml:space="preserve">……負けだ。</t>
         </is>
       </c>
     </row>
     <row r="77" ht="40" customHeight="1">
       <c r="A77" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.cool_quiet.win[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.cool_quiet.lose[2]</t>
         </is>
       </c>
       <c r="B77" t="inlineStr" s="2">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="D77" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool_quiet.win[1]</t>
+          <t xml:space="preserve">cool_quiet.lose[2]</t>
         </is>
       </c>
       <c r="E77" t="inlineStr" s="2">
@@ -2789,14 +2789,14 @@
       </c>
       <c r="F77" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……終わりだ。</t>
+          <t xml:space="preserve">……強い。</t>
         </is>
       </c>
     </row>
     <row r="78" ht="40" customHeight="1">
       <c r="A78" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.cool_quiet.win[2]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.cool_quiet.lose[3]</t>
         </is>
       </c>
       <c r="B78" t="inlineStr" s="2">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="D78" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool_quiet.win[2]</t>
+          <t xml:space="preserve">cool_quiet.lose[3]</t>
         </is>
       </c>
       <c r="E78" t="inlineStr" s="2">
@@ -2821,14 +2821,14 @@
       </c>
       <c r="F78" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……当然。</t>
+          <t xml:space="preserve">……そうか。</t>
         </is>
       </c>
     </row>
     <row r="79" ht="40" customHeight="1">
       <c r="A79" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.cool_quiet.win[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.cool_quiet.win[1]</t>
         </is>
       </c>
       <c r="B79" t="inlineStr" s="2">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="D79" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool_quiet.win[3]</t>
+          <t xml:space="preserve">cool_quiet.win[1]</t>
         </is>
       </c>
       <c r="E79" t="inlineStr" s="2">
@@ -2853,14 +2853,14 @@
       </c>
       <c r="F79" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ここまで。</t>
+          <t xml:space="preserve">……終わりだ。</t>
         </is>
       </c>
     </row>
     <row r="80" ht="40" customHeight="1">
       <c r="A80" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.default.quiet.cool[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.cool_quiet.win[2]</t>
         </is>
       </c>
       <c r="B80" t="inlineStr" s="2">
@@ -2870,29 +2870,29 @@
       </c>
       <c r="C80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
         </is>
       </c>
       <c r="D80" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">default.quiet.cool[1]</t>
+          <t xml:space="preserve">cool_quiet.win[2]</t>
         </is>
       </c>
       <c r="E80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F80" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう少し</t>
+          <t xml:space="preserve">……当然。</t>
         </is>
       </c>
     </row>
     <row r="81" ht="40" customHeight="1">
       <c r="A81" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.former_champ.quiet.cool[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.cool_quiet.win[3]</t>
         </is>
       </c>
       <c r="B81" t="inlineStr" s="2">
@@ -2902,29 +2902,29 @@
       </c>
       <c r="C81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
         </is>
       </c>
       <c r="D81" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">former_champ.quiet.cool[1]</t>
+          <t xml:space="preserve">cool_quiet.win[3]</t>
         </is>
       </c>
       <c r="E81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F81" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう一度</t>
+          <t xml:space="preserve">……ここまで。</t>
         </is>
       </c>
     </row>
     <row r="82" ht="40" customHeight="1">
       <c r="A82" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.heel.quiet.cool[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B82" t="inlineStr" s="2">
@@ -2934,12 +2934,12 @@
       </c>
       <c r="C82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D82" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heel.quiet.cool[1]</t>
+          <t xml:space="preserve">accepted.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E82" t="inlineStr" s="2">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="F82" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい</t>
+          <t xml:space="preserve">…さよならだ</t>
         </is>
       </c>
     </row>
     <row r="83" ht="40" customHeight="1">
       <c r="A83" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.high_trust.quiet.cool[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.quiet.cool[2]</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="2">
@@ -2966,12 +2966,12 @@
       </c>
       <c r="C83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D83" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">high_trust.quiet.cool[1]</t>
+          <t xml:space="preserve">accepted.quiet.cool[2]</t>
         </is>
       </c>
       <c r="E83" t="inlineStr" s="2">
@@ -2981,14 +2981,14 @@
       </c>
       <c r="F83" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう少しだけ</t>
+          <t xml:space="preserve">…世話になった</t>
         </is>
       </c>
     </row>
     <row r="84" ht="40" customHeight="1">
       <c r="A84" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.quiet.cool[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="2">
@@ -2998,12 +2998,12 @@
       </c>
       <c r="C84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D84" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_former_champ.quiet.cool[1]</t>
+          <t xml:space="preserve">defended.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E84" t="inlineStr" s="2">
@@ -3013,14 +3013,14 @@
       </c>
       <c r="F84" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…十分だ</t>
+          <t xml:space="preserve">…残る</t>
         </is>
       </c>
     </row>
     <row r="85" ht="40" customHeight="1">
       <c r="A85" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.quiet.cool[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.quiet.cool[2]</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="2">
@@ -3030,12 +3030,12 @@
       </c>
       <c r="C85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D85" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_heel.quiet.cool[1]</t>
+          <t xml:space="preserve">defended.quiet.cool[2]</t>
         </is>
       </c>
       <c r="E85" t="inlineStr" s="2">
@@ -3045,14 +3045,14 @@
       </c>
       <c r="F85" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…潮時だ</t>
+          <t xml:space="preserve">…ありがとう</t>
         </is>
       </c>
     </row>
     <row r="86" ht="40" customHeight="1">
       <c r="A86" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.quiet.cool[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="2">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="C86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D86" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_no_title.quiet.cool[1]</t>
+          <t xml:space="preserve">defense_failed.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E86" t="inlineStr" s="2">
@@ -3077,14 +3077,14 @@
       </c>
       <c r="F86" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ああ</t>
+          <t xml:space="preserve">…すまない</t>
         </is>
       </c>
     </row>
     <row r="87" ht="40" customHeight="1">
       <c r="A87" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.quiet.cool[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.quiet.cool[2]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="2">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="C87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D87" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_terminal.quiet.cool[1]</t>
+          <t xml:space="preserve">defense_failed.quiet.cool[2]</t>
         </is>
       </c>
       <c r="E87" t="inlineStr" s="2">
@@ -3109,14 +3109,14 @@
       </c>
       <c r="F87" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…わかってる</t>
+          <t xml:space="preserve">…さよならだ</t>
         </is>
       </c>
     </row>
     <row r="88" ht="40" customHeight="1">
       <c r="A88" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.quiet.cool[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.default.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
@@ -3126,12 +3126,12 @@
       </c>
       <c r="C88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D88" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_winless.quiet.cool[1]</t>
+          <t xml:space="preserve">default.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E88" t="inlineStr" s="2">
@@ -3141,14 +3141,14 @@
       </c>
       <c r="F88" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうだな</t>
+          <t xml:space="preserve">…もう少し</t>
         </is>
       </c>
     </row>
     <row r="89" ht="40" customHeight="1">
       <c r="A89" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.quiet.cool[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.former_champ.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="C89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D89" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_champ.quiet.cool[1]</t>
+          <t xml:space="preserve">former_champ.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr" s="2">
@@ -3173,14 +3173,14 @@
       </c>
       <c r="F89" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…退かない</t>
+          <t xml:space="preserve">…もう一度</t>
         </is>
       </c>
     </row>
     <row r="90" ht="40" customHeight="1">
       <c r="A90" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.quiet.cool[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.heel.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
@@ -3190,12 +3190,12 @@
       </c>
       <c r="C90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D90" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_distrust.quiet.cool[1]</t>
+          <t xml:space="preserve">heel.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr" s="2">
@@ -3205,14 +3205,14 @@
       </c>
       <c r="F90" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうか</t>
+          <t xml:space="preserve">…いい</t>
         </is>
       </c>
     </row>
     <row r="91" ht="40" customHeight="1">
       <c r="A91" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.quiet.cool[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.high_trust.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
@@ -3222,12 +3222,12 @@
       </c>
       <c r="C91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D91" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_fighting.quiet.cool[1]</t>
+          <t xml:space="preserve">high_trust.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr" s="2">
@@ -3237,14 +3237,14 @@
       </c>
       <c r="F91" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…闘える</t>
+          <t xml:space="preserve">…もう少しだけ</t>
         </is>
       </c>
     </row>
     <row r="92" ht="40" customHeight="1">
       <c r="A92" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.quiet.cool[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="C92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D92" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_heel.quiet.cool[1]</t>
+          <t xml:space="preserve">accept_former_champ.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E92" t="inlineStr" s="2">
@@ -3269,14 +3269,14 @@
       </c>
       <c r="F92" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…辞めない</t>
+          <t xml:space="preserve">…十分だ</t>
         </is>
       </c>
     </row>
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.quiet.cool[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="C93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A1_champion.quiet.cool[1]</t>
+          <t xml:space="preserve">accept_heel.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E93" t="inlineStr" s="2">
@@ -3301,14 +3301,14 @@
       </c>
       <c r="F93" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…忘れない</t>
+          <t xml:space="preserve">…潮時だ</t>
         </is>
       </c>
     </row>
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.quiet.cool[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -3318,12 +3318,12 @@
       </c>
       <c r="C94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A2_uncrowned.quiet.cool[1]</t>
+          <t xml:space="preserve">accept_no_title.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr" s="2">
@@ -3333,14 +3333,14 @@
       </c>
       <c r="F94" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悔いはない</t>
+          <t xml:space="preserve">…ああ</t>
         </is>
       </c>
     </row>
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.quiet.cool[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -3350,12 +3350,12 @@
       </c>
       <c r="C95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A3_heel.quiet.cool[1]</t>
+          <t xml:space="preserve">accept_terminal.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr" s="2">
@@ -3365,14 +3365,14 @@
       </c>
       <c r="F95" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…じゃあな</t>
+          <t xml:space="preserve">…わかってる</t>
         </is>
       </c>
     </row>
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.quiet.cool[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="C96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A4_veteran.quiet.cool[1]</t>
+          <t xml:space="preserve">accept_winless.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr" s="2">
@@ -3397,14 +3397,14 @@
       </c>
       <c r="F96" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう</t>
+          <t xml:space="preserve">…そうだな</t>
         </is>
       </c>
     </row>
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B1_young.quiet.cool[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="C97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1_young.quiet.cool[1]</t>
+          <t xml:space="preserve">refuse_champ.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr" s="2">
@@ -3429,14 +3429,14 @@
       </c>
       <c r="F97" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まだ</t>
+          <t xml:space="preserve">…退かない</t>
         </is>
       </c>
     </row>
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.quiet.cool[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -3446,12 +3446,12 @@
       </c>
       <c r="C98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_prime.quiet.cool[1]</t>
+          <t xml:space="preserve">refuse_distrust.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr" s="2">
@@ -3461,14 +3461,14 @@
       </c>
       <c r="F98" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ</t>
+          <t xml:space="preserve">…そうか</t>
         </is>
       </c>
     </row>
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B3_older.quiet.cool[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -3478,12 +3478,12 @@
       </c>
       <c r="C99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3_older.quiet.cool[1]</t>
+          <t xml:space="preserve">refuse_fighting.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr" s="2">
@@ -3493,14 +3493,14 @@
       </c>
       <c r="F99" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…十分だ</t>
+          <t xml:space="preserve">…闘える</t>
         </is>
       </c>
     </row>
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.quiet.cool[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="C100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_champion_injury.quiet.cool[1]</t>
+          <t xml:space="preserve">refuse_heel.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr" s="2">
@@ -3525,14 +3525,14 @@
       </c>
       <c r="F100" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだだ</t>
+          <t xml:space="preserve">…辞めない</t>
         </is>
       </c>
     </row>
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3542,12 +3542,12 @@
       </c>
       <c r="C101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">A1_champion.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr" s="2">
@@ -3557,14 +3557,14 @@
       </c>
       <c r="F101" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…………（契約書にペンを走らせた）</t>
+          <t xml:space="preserve">…忘れない</t>
         </is>
       </c>
     </row>
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.quiet.cool[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3574,29 +3574,29 @@
       </c>
       <c r="C102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.quiet.cool[1]</t>
+          <t xml:space="preserve">A2_uncrowned.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F102" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう。…頑張る</t>
+          <t xml:space="preserve">…悔いはない</t>
         </is>
       </c>
     </row>
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.quiet.cool[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3606,29 +3606,29 @@
       </c>
       <c r="C103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.quiet.cool[1]</t>
+          <t xml:space="preserve">A3_heel.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F103" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…分かった。ありがとう</t>
+          <t xml:space="preserve">…じゃあな</t>
         </is>
       </c>
     </row>
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.quiet.cool[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3638,29 +3638,29 @@
       </c>
       <c r="C104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.quiet.cool[1]</t>
+          <t xml:space="preserve">A4_veteran.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F104" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう。…分かった</t>
+          <t xml:space="preserve">…ありがとう</t>
         </is>
       </c>
     </row>
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.quiet.cool[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3670,29 +3670,29 @@
       </c>
       <c r="C105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.quiet.cool[1]</t>
+          <t xml:space="preserve">B1_young.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F105" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長。{tenure}…給料の話。{record}…考えてほしい</t>
+          <t xml:space="preserve">……まだ</t>
         </is>
       </c>
     </row>
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.quiet.cool[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3702,29 +3702,29 @@
       </c>
       <c r="C106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.quiet.cool[1]</t>
+          <t xml:space="preserve">B2_prime.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F106" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう。……分かった</t>
+          <t xml:space="preserve">…まだ</t>
         </is>
       </c>
     </row>
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.quiet.cool[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3734,29 +3734,29 @@
       </c>
       <c r="C107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.quiet.cool[1]</t>
+          <t xml:space="preserve">B3_older.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F107" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…聞いてくれるんだ。{record}…ここにいる意味が、分からない</t>
+          <t xml:space="preserve">…十分だ</t>
         </is>
       </c>
     </row>
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.quiet.cool[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3766,29 +3766,29 @@
       </c>
       <c r="C108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.quiet.cool[1]</t>
+          <t xml:space="preserve">B4_champion_injury.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F108" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…{tenure}…出たい。…それだけ</t>
+          <t xml:space="preserve">…まだだ</t>
         </is>
       </c>
     </row>
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.quiet.cool[1]</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3798,29 +3798,29 @@
       </c>
       <c r="C109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES</t>
         </is>
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.quiet.cool[1]</t>
+          <t xml:space="preserve">quiet.cool[1]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F109" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…{tenure_farewell}{rivalry}…ありがとう</t>
+          <t xml:space="preserve">…………（契約書にペンを走らせた）</t>
         </is>
       </c>
     </row>
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.quiet.cool[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3835,7 +3835,7 @@
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.quiet.cool[1]</t>
+          <t xml:space="preserve">raise_accept.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="2">
@@ -3845,14 +3845,14 @@
       </c>
       <c r="F110" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ごめん。…もう決めた</t>
+          <t xml:space="preserve">…ありがとう。…頑張る</t>
         </is>
       </c>
     </row>
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.quiet.cool[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.quiet.cool[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
@@ -3877,14 +3877,14 @@
       </c>
       <c r="F111" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そこまで言うなら。…もう少しだけ</t>
+          <t xml:space="preserve">…分かった。ありがとう</t>
         </is>
       </c>
     </row>
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.blocked.quiet.cool[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="C112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">blocked.quiet.cool[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
@@ -3909,14 +3909,14 @@
       </c>
       <c r="F112" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…話にならない。断る</t>
+          <t xml:space="preserve">…そう。…分かった</t>
         </is>
       </c>
     </row>
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.fail.quiet.cool[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="C113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fail.quiet.cool[1]</t>
+          <t xml:space="preserve">raise_open.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
@@ -3941,14 +3941,14 @@
       </c>
       <c r="F113" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…断る</t>
+          <t xml:space="preserve">…社長。{tenure}…給料の話。{record}…考えてほしい</t>
         </is>
       </c>
     </row>
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.quiet.cool[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="C114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">start.quiet.cool[1]</t>
+          <t xml:space="preserve">raise_refuse.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -3973,14 +3973,14 @@
       </c>
       <c r="F114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…聞こう</t>
+          <t xml:space="preserve">…そう。……分かった</t>
         </is>
       </c>
     </row>
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.success.quiet.cool[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -3990,12 +3990,12 @@
       </c>
       <c r="C115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">success.quiet.cool[1]</t>
+          <t xml:space="preserve">transfer_listen.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -4005,270 +4005,270 @@
       </c>
       <c r="F115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…行く</t>
+          <t xml:space="preserve">…聞いてくれるんだ。{record}…ここにいる意味が、分からない</t>
         </is>
       </c>
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F01_LEADER_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F01_LEADER_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">transfer_open.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F116" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……別にいいよ、ついてきたいなら。</t>
+          <t xml:space="preserve">…{tenure}…出たい。…それだけ</t>
         </is>
       </c>
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F01_LEADER_LINES.quiet.cool[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F01_LEADER_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[2]</t>
+          <t xml:space="preserve">transfer_release.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……邪魔はしない。勝手についてくればいい。</t>
+          <t xml:space="preserve">…{tenure_farewell}{rivalry}…ありがとう</t>
         </is>
       </c>
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LEADER_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LEADER_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">transfer_retain_fail.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……交わる気はない。</t>
+          <t xml:space="preserve">…ごめん。…もう決めた</t>
         </is>
       </c>
     </row>
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F03_SURVIVOR_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F03_SURVIVOR_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">transfer_retain_success.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……何も言葉が出てこない。</t>
+          <t xml:space="preserve">…そこまで言うなら。…もう少しだけ</t>
         </is>
       </c>
     </row>
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F04_TARGET_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.blocked.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F04_TARGET_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">blocked.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F120" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もう、決めたから。</t>
+          <t xml:space="preserve">…話にならない。断る</t>
         </is>
       </c>
     </row>
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.fail.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">fail.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F121" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……静かに、離れたい。</t>
+          <t xml:space="preserve">…断る</t>
         </is>
       </c>
     </row>
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">start.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F122" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まあ、別にいいよ。</t>
+          <t xml:space="preserve">…聞こう</t>
         </is>
       </c>
     </row>
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F07_LEADER_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.success.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F07_LEADER_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">success.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F123" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ちゃんと見てほしい。それだけ。</t>
+          <t xml:space="preserve">…行く</t>
         </is>
       </c>
     </row>
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_LEADER_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">FACTION_F01_LEADER_LINES.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="C124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_LEADER_LINES</t>
+          <t xml:space="preserve">FACTION_F01_LEADER_LINES</t>
         </is>
       </c>
       <c r="D124" t="inlineStr" s="12">
@@ -4293,14 +4293,14 @@
       </c>
       <c r="F124" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……リングで、会う。</t>
+          <t xml:space="preserve">……別にいいよ、ついてきたいなら。</t>
         </is>
       </c>
     </row>
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.quiet.cool.hp_high[1]</t>
+          <t xml:space="preserve">FACTION_F01_LEADER_LINES.quiet.cool[2]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4310,12 +4310,12 @@
       </c>
       <c r="C125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
+          <t xml:space="preserve">FACTION_F01_LEADER_LINES</t>
         </is>
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool.hp_high[1]</t>
+          <t xml:space="preserve">quiet.cool[2]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
@@ -4325,14 +4325,14 @@
       </c>
       <c r="F125" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……負け。それだけ</t>
+          <t xml:space="preserve">……邪魔はしない。勝手についてくればいい。</t>
         </is>
       </c>
     </row>
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.quiet.cool.hp_mid[1]</t>
+          <t xml:space="preserve">FACTION_F02_LEADER_LINES.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="C126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LEADER_LINES</t>
         </is>
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool.hp_mid[1]</t>
+          <t xml:space="preserve">quiet.cool[1]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr" s="2">
@@ -4357,14 +4357,14 @@
       </c>
       <c r="F126" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……っ……</t>
+          <t xml:space="preserve">……交わる気はない。</t>
         </is>
       </c>
     </row>
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.quiet.cool.high[1]</t>
+          <t xml:space="preserve">FACTION_F03_SURVIVOR_LINES.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -4374,12 +4374,12 @@
       </c>
       <c r="C127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
+          <t xml:space="preserve">FACTION_F03_SURVIVOR_LINES</t>
         </is>
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool.high[1]</t>
+          <t xml:space="preserve">quiet.cool[1]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr" s="2">
@@ -4389,14 +4389,14 @@
       </c>
       <c r="F127" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……結果がすべて、だろ</t>
+          <t xml:space="preserve">……何も言葉が出てこない。</t>
         </is>
       </c>
     </row>
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.quiet.cool.high[1]</t>
+          <t xml:space="preserve">FACTION_F04_TARGET_LINES.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4406,12 +4406,12 @@
       </c>
       <c r="C128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
+          <t xml:space="preserve">FACTION_F04_TARGET_LINES</t>
         </is>
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool.high[1]</t>
+          <t xml:space="preserve">quiet.cool[1]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="2">
@@ -4421,14 +4421,14 @@
       </c>
       <c r="F128" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……話すことは、もうない</t>
+          <t xml:space="preserve">……もう、決めたから。</t>
         </is>
       </c>
     </row>
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.quiet.cool.high[2]</t>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="C129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES</t>
         </is>
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool.high[2]</t>
+          <t xml:space="preserve">quiet.cool[1]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr" s="2">
@@ -4453,14 +4453,14 @@
       </c>
       <c r="F129" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……決着、つけよう</t>
+          <t xml:space="preserve">……静かに、離れたい。</t>
         </is>
       </c>
     </row>
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.quiet.cool.high[1]</t>
+          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="C130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
+          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES</t>
         </is>
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool.high[1]</t>
+          <t xml:space="preserve">quiet.cool[1]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr" s="2">
@@ -4485,14 +4485,14 @@
       </c>
       <c r="F130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……いいだろう。受けて立つ</t>
+          <t xml:space="preserve">……まあ、別にいいよ。</t>
         </is>
       </c>
     </row>
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A.quiet.cool.high[1]</t>
+          <t xml:space="preserve">FACTION_F07_LEADER_LINES.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="C131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A</t>
+          <t xml:space="preserve">FACTION_F07_LEADER_LINES</t>
         </is>
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool.high[1]</t>
+          <t xml:space="preserve">quiet.cool[1]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr" s="2">
@@ -4517,14 +4517,14 @@
       </c>
       <c r="F131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……話すことは、もう何もない</t>
+          <t xml:space="preserve">……ちゃんと見てほしい。それだけ。</t>
         </is>
       </c>
     </row>
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_B.quiet.cool.high[1]</t>
+          <t xml:space="preserve">FACTION_F08_LEADER_LINES.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4534,12 +4534,12 @@
       </c>
       <c r="C132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_B</t>
+          <t xml:space="preserve">FACTION_F08_LEADER_LINES</t>
         </is>
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool.high[1]</t>
+          <t xml:space="preserve">quiet.cool[1]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr" s="2">
@@ -4549,270 +4549,270 @@
       </c>
       <c r="F132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……受ける</t>
+          <t xml:space="preserve">……リングで、会う。</t>
         </is>
       </c>
     </row>
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.quiet.cool.hp_high[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
         </is>
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">quiet.cool.hp_high[1]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…変わった</t>
+          <t xml:space="preserve">……負け。それだけ</t>
         </is>
       </c>
     </row>
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.quiet.cool.hp_mid[1]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
         </is>
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">quiet.cool.hp_mid[1]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（——見えた）</t>
+          <t xml:space="preserve">……っ……</t>
         </is>
       </c>
     </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.quiet.cool[1]</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.quiet.cool.high[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
         </is>
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.quiet.cool[1]</t>
+          <t xml:space="preserve">quiet.cool.high[1]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここまでだ</t>
+          <t xml:space="preserve">……結果がすべて、だろ</t>
         </is>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.quiet.cool[1]</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.quiet.cool.high[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
         </is>
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.quiet.cool[1]</t>
+          <t xml:space="preserve">quiet.cool.high[1]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ、止まらない</t>
+          <t xml:space="preserve">……話すことは、もうない</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.quiet.cool[1]</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.quiet.cool.high[2]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
         </is>
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.quiet.cool[1]</t>
+          <t xml:space="preserve">quiet.cool.high[2]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…実感はある</t>
+          <t xml:space="preserve">……決着、つけよう</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.quiet.cool[1]</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.quiet.cool.high[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
         </is>
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.quiet.cool[1]</t>
+          <t xml:space="preserve">quiet.cool.high[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この静けさが、答えだ</t>
+          <t xml:space="preserve">……いいだろう。受けて立つ</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.quiet.cool[1]</t>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A.quiet.cool.high[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A</t>
         </is>
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.quiet.cool[1]</t>
+          <t xml:space="preserve">quiet.cool.high[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…背負っていく。この声を</t>
+          <t xml:space="preserve">……話すことは、もう何もない</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_B.quiet.cool.high[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_B</t>
         </is>
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">quiet.cool.high[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……見えない</t>
+          <t xml:space="preserve">……受ける</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="C141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D141" t="inlineStr" s="12">
@@ -4837,14 +4837,14 @@
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…闘える</t>
+          <t xml:space="preserve">…変わった</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="C142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">BT_HINT_LINES</t>
         </is>
       </c>
       <c r="D142" t="inlineStr" s="12">
@@ -4869,14 +4869,14 @@
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……戻った</t>
+          <t xml:space="preserve">（——見えた）</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.quiet.cool[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4886,12 +4886,12 @@
       </c>
       <c r="C143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.quiet.cool[1]</t>
+          <t xml:space="preserve">fresh.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
@@ -4901,14 +4901,14 @@
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…動けない</t>
+          <t xml:space="preserve">…体は軽い。…今日は、かなり…やれる</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.quiet.cool[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4918,12 +4918,12 @@
       </c>
       <c r="C144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.quiet.cool[1]</t>
+          <t xml:space="preserve">heavy.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
@@ -4933,14 +4933,14 @@
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……鈍い</t>
+          <t xml:space="preserve">…重い。…やっても、抜けていくだけだ</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.quiet.cool[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="C145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.quiet.cool[1]</t>
+          <t xml:space="preserve">warm.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
@@ -4965,14 +4965,14 @@
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…遠い</t>
+          <t xml:space="preserve">…動けている。…ただ、深さがない</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.quiet.cool[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="C146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.quiet.cool[1]</t>
+          <t xml:space="preserve">cap_reached.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
@@ -4997,14 +4997,14 @@
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…心が、まだ</t>
+          <t xml:space="preserve">…ここまでだ</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.quiet.cool[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -5014,29 +5014,29 @@
       </c>
       <c r="C147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.quiet.cool[1]</t>
+          <t xml:space="preserve">ovr_elite.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一生の試合だった</t>
+          <t xml:space="preserve">…まだ、止まらない</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.quiet.cool[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5046,29 +5046,29 @@
       </c>
       <c r="C148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.quiet.cool[1]</t>
+          <t xml:space="preserve">ovr_growth.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ降りない</t>
+          <t xml:space="preserve">…実感はある</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.quiet.cool[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5078,29 +5078,29 @@
       </c>
       <c r="C149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.quiet.cool[1]</t>
+          <t xml:space="preserve">ovr_legend.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悔いはない。…ありがとう</t>
+          <t xml:space="preserve">…この静けさが、答えだ</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.quiet.cool[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5110,29 +5110,29 @@
       </c>
       <c r="C150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.quiet.cool[1]</t>
+          <t xml:space="preserve">pop_star.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…感謝します</t>
+          <t xml:space="preserve">…背負っていく。この声を</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.quiet.cool[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5142,29 +5142,29 @@
       </c>
       <c r="C151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.quiet.cool[1]</t>
+          <t xml:space="preserve">quiet.cool[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…積み重ねの結果だ</t>
+          <t xml:space="preserve">……見えない</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.quiet.cool[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5174,29 +5174,29 @@
       </c>
       <c r="C152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.quiet.cool[1]</t>
+          <t xml:space="preserve">quiet.cool[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…次</t>
+          <t xml:space="preserve">…闘える</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="C153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D153" t="inlineStr" s="12">
@@ -5216,19 +5216,19 @@
       </c>
       <c r="E153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…行きます</t>
+          <t xml:space="preserve">……戻った</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.quiet.cool[2]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5238,29 +5238,29 @@
       </c>
       <c r="C154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[2]</t>
+          <t xml:space="preserve">defeat.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ドームか。悪くない</t>
+          <t xml:space="preserve">…動けない</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.quiet.cool[3]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5270,29 +5270,29 @@
       </c>
       <c r="C155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[3]</t>
+          <t xml:space="preserve">injury_moderate_recovery.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……(視線だけで応える)</t>
+          <t xml:space="preserve">……鈍い</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5302,29 +5302,29 @@
       </c>
       <c r="C156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">injury_severe_recovery.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…満員</t>
+          <t xml:space="preserve">…遠い</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.quiet.cool[2]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5334,29 +5334,29 @@
       </c>
       <c r="C157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[2]</t>
+          <t xml:space="preserve">penalty_end.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…忘れない</t>
+          <t xml:space="preserve">…心が、まだ</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.quiet.cool[3]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="C158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[3]</t>
+          <t xml:space="preserve">bestMatch.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
@@ -5381,14 +5381,14 @@
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……(遠くを見ている)</t>
+          <t xml:space="preserve">…一生の試合だった</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.quiet.cool[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5398,29 +5398,29 @@
       </c>
       <c r="C159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.quiet.cool[1]</t>
+          <t xml:space="preserve">champion.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪くない。この調子で</t>
+          <t xml:space="preserve">…まだ降りない</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.quiet.cool[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5430,29 +5430,29 @@
       </c>
       <c r="C160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.quiet.cool[1]</t>
+          <t xml:space="preserve">hallOfFame.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪くない仲間だ</t>
+          <t xml:space="preserve">…悔いはない。…ありがとう</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.quiet.cool[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5462,29 +5462,29 @@
       </c>
       <c r="C161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.quiet.cool[1]</t>
+          <t xml:space="preserve">mediaAward.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…大丈夫だ。すぐ戻れる</t>
+          <t xml:space="preserve">…感謝します</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.quiet.cool[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5494,29 +5494,29 @@
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.quiet.cool[1]</t>
+          <t xml:space="preserve">mvp.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ファンの期待には応える</t>
+          <t xml:space="preserve">…積み重ねの結果だ</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.quiet.cool[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5526,29 +5526,29 @@
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.quiet.cool[1]</t>
+          <t xml:space="preserve">rookie.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（静かに出口を見ている）</t>
+          <t xml:space="preserve">…次</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.quiet.cool[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5558,29 +5558,29 @@
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">breakthrough.voice.quiet.cool[1]</t>
+          <t xml:space="preserve">quiet.cool[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…環境に恵まれた。それは認める</t>
+          <t xml:space="preserve">…行きます</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.quiet.cool[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.quiet.cool[2]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5590,29 +5590,29 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G2.voice.quiet.cool[1]</t>
+          <t xml:space="preserve">quiet.cool[2]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう。それだけのことだ</t>
+          <t xml:space="preserve">…ドームか。悪くない</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.quiet.cool[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.quiet.cool[3]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5622,29 +5622,29 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.voice.quiet.cool[1]</t>
+          <t xml:space="preserve">quiet.cool[3]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…チャンスは自分で作るものだと思っている</t>
+          <t xml:space="preserve">……(視線だけで応える)</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.quiet.cool[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5654,29 +5654,29 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R2.voice.quiet.cool[1]</t>
+          <t xml:space="preserve">quiet.cool[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…孤独には慣れている</t>
+          <t xml:space="preserve">…満員</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.quiet.cool[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.quiet.cool[2]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5686,29 +5686,29 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.modal.quiet.cool[1]</t>
+          <t xml:space="preserve">quiet.cool[2]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうか。…分かった</t>
+          <t xml:space="preserve">…忘れない</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.quiet.cool[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.quiet.cool[3]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5718,29 +5718,29 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R4.voice.quiet.cool[1]</t>
+          <t xml:space="preserve">quiet.cool[3]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…次も同じ結果とは限らない。気を引き締めろ、自分</t>
+          <t xml:space="preserve">……(遠くを見ている)</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.quiet.cool[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.voice.quiet.cool[1]</t>
+          <t xml:space="preserve">N1.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
@@ -5765,14 +5765,14 @@
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…敗因は分かっている。次までに修正する</t>
+          <t xml:space="preserve">…悪くない。この調子で</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.quiet.cool[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warVictory.voice.quiet.cool[1]</t>
+          <t xml:space="preserve">N2.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
@@ -5797,14 +5797,14 @@
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…当然の結果だ</t>
+          <t xml:space="preserve">…悪くない仲間だ</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.quiet.cool[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5814,29 +5814,29 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.quiet.cool[1]</t>
+          <t xml:space="preserve">N3.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがたい</t>
+          <t xml:space="preserve">…大丈夫だ。すぐ戻れる</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.quiet.cool[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5846,29 +5846,29 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.quiet.cool[1]</t>
+          <t xml:space="preserve">N4.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…追い込む</t>
+          <t xml:space="preserve">…ファンの期待には応える</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.quiet.cool[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5878,29 +5878,29 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.quiet.cool[1]</t>
+          <t xml:space="preserve">N5_low.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…分かった。応える</t>
+          <t xml:space="preserve">……（静かに出口を見ている）</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.quiet.cool[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5910,29 +5910,29 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.quiet.cool[1]</t>
+          <t xml:space="preserve">breakthrough.voice.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……分かった</t>
+          <t xml:space="preserve">…環境に恵まれた。それは認める</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.quiet.cool[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5942,29 +5942,29 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.quiet.cool[1]</t>
+          <t xml:space="preserve">G2.voice.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……やる</t>
+          <t xml:space="preserve">…そう。それだけのことだ</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.quiet.cool[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5974,29 +5974,29 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.quiet.cool[1]</t>
+          <t xml:space="preserve">G3.voice.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪くなかった</t>
+          <t xml:space="preserve">…チャンスは自分で作るものだと思っている</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.quiet.cool[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -6006,29 +6006,29 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.quiet.cool[1]</t>
+          <t xml:space="preserve">R2.voice.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…感謝する。少し休む</t>
+          <t xml:space="preserve">…孤独には慣れている</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.quiet.cool[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6038,29 +6038,29 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.quiet.cool[1]</t>
+          <t xml:space="preserve">R3.modal.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…感謝する。早く戻る</t>
+          <t xml:space="preserve">…そうか。…分かった</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.quiet.cool[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6070,29 +6070,29 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.quiet.cool[1]</t>
+          <t xml:space="preserve">R4.voice.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…吸収する。見ていてくれ</t>
+          <t xml:space="preserve">…次も同じ結果とは限らない。気を引き締めろ、自分</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.quiet.cool[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6102,29 +6102,29 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.quiet.cool[1]</t>
+          <t xml:space="preserve">R5.voice.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……やる</t>
+          <t xml:space="preserve">…敗因は分かっている。次までに修正する</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.quiet.cool[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6134,29 +6134,29 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.quiet.cool[1]</t>
+          <t xml:space="preserve">warVictory.voice.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…他所から来た。報告する</t>
+          <t xml:space="preserve">…当然の結果だ</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.quiet.cool[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.quiet.cool[1]</t>
+          <t xml:space="preserve">bonus.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
@@ -6181,14 +6181,14 @@
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（静かにテーピングを外している）</t>
+          <t xml:space="preserve">…ありがたい</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.quiet.cool[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.quiet.cool[1]</t>
+          <t xml:space="preserve">camp.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -6213,14 +6213,14 @@
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…タイトルマッチを。頼む</t>
+          <t xml:space="preserve">…追い込む</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.quiet.cool[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6230,12 +6230,12 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.quiet.cool[1]</t>
+          <t xml:space="preserve">encourage_high_trust.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -6245,14 +6245,14 @@
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あいつとの試合を。頼む</t>
+          <t xml:space="preserve">…分かった。応える</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.quiet.cool[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.quiet.cool[1]</t>
+          <t xml:space="preserve">encourage.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6277,14 +6277,14 @@
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…休む必要がある</t>
+          <t xml:space="preserve">……分かった</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.quiet.cool[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.quiet.cool[1]</t>
+          <t xml:space="preserve">media.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6309,14 +6309,14 @@
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もう、限界だ（静かに、しかし断固として）</t>
+          <t xml:space="preserve">……やる</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.quiet.cool[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6326,12 +6326,12 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.quiet.cool[1]</t>
+          <t xml:space="preserve">party.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6341,14 +6341,14 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（何も言わず、立ち去ろうとする）</t>
+          <t xml:space="preserve">…悪くなかった</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.quiet.cool[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6358,12 +6358,12 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.quiet.cool[1]</t>
+          <t xml:space="preserve">refresh_leave.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6373,14 +6373,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…鍛えたい。場所を貸してくれ</t>
+          <t xml:space="preserve">…感謝する。少し休む</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.quiet.cool[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.quiet.cool[1]</t>
+          <t xml:space="preserve">special_treatment.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6405,14 +6405,14 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…次の世代に、繋ぎたいものがある</t>
+          <t xml:space="preserve">…感謝する。早く戻る</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.quiet.cool[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6422,12 +6422,12 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.quiet.cool[1]</t>
+          <t xml:space="preserve">trainer.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6437,14 +6437,14 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…すぐ戻る</t>
+          <t xml:space="preserve">…吸収する。見ていてくれ</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.quiet.cool[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.quiet.cool[1]</t>
+          <t xml:space="preserve">E1.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6469,14 +6469,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あれとは合わない。それだけだ</t>
+          <t xml:space="preserve">……やる</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.quiet.cool[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6486,12 +6486,12 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.quiet.cool[1]</t>
+          <t xml:space="preserve">E6.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6501,14 +6501,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…私は間違っていない</t>
+          <t xml:space="preserve">…他所から来た。報告する</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.quiet.cool[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6518,12 +6518,12 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.quiet.cool[1]</t>
+          <t xml:space="preserve">S_boycott.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6533,14 +6533,14 @@
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…無駄口は叩かない。それがブランドには向いているかもな</t>
+          <t xml:space="preserve">………（静かにテーピングを外している）</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.quiet.cool[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.quiet.cool[1]</t>
+          <t xml:space="preserve">S_grumble.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6565,14 +6565,14 @@
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…カメラか。まぁ、やる</t>
+          <t xml:space="preserve">（無言のまま動かず、周囲だけが落ち着かなくなっている）</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.quiet.cool[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6582,12 +6582,12 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.quiet.cool[1]</t>
+          <t xml:space="preserve">S_sns.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6597,14 +6597,14 @@
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…来てくれた人には、ちゃんと応えたい</t>
+          <t xml:space="preserve">（SNSに点を三つ置いただけの投稿。ファンの憶測だけが広がっていく）</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.quiet.cool[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6614,12 +6614,12 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.quiet.cool[1]</t>
+          <t xml:space="preserve">S1.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6629,14 +6629,14 @@
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…余計なことはしない。ただ歩く。それだけだ</t>
+          <t xml:space="preserve">…タイトルマッチを。頼む</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.quiet.cool[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6646,12 +6646,12 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.quiet.cool[1]</t>
+          <t xml:space="preserve">S2.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6661,14 +6661,14 @@
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…写真か。余計なことはしないでくれ</t>
+          <t xml:space="preserve">…あいつとの試合を。頼む</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.quiet.cool[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6678,12 +6678,12 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.quiet.cool[1]</t>
+          <t xml:space="preserve">S3.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6693,14 +6693,14 @@
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…無駄なことは言わない。それだけだ</t>
+          <t xml:space="preserve">…休む必要がある</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.quiet.cool[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6710,12 +6710,12 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.quiet.cool[1]</t>
+          <t xml:space="preserve">S4_direct.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6725,14 +6725,14 @@
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やる。見ていてくれ</t>
+          <t xml:space="preserve">……もう、限界だ（静かに、しかし断固として）</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6742,29 +6742,29 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">S4_silent.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…戦わせてくれるなら、応える</t>
+          <t xml:space="preserve">……（何も言わず、立ち去ろうとする）</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6774,29 +6774,29 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">S5.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……よろしく</t>
+          <t xml:space="preserve">…鍛えたい。場所を貸してくれ</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.quiet.cool[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6806,29 +6806,29 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[2]</t>
+          <t xml:space="preserve">S6.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……始めよう</t>
+          <t xml:space="preserve">…次の世代に、繋ぎたいものがある</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6838,29 +6838,29 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">B1.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やる。見ていてくれ</t>
+          <t xml:space="preserve">…すぐ戻る</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6870,29 +6870,29 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">B2_fighter1.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やるべきことをやる</t>
+          <t xml:space="preserve">…あれとは合わない。それだけだ</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.quiet.cool[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6902,29 +6902,29 @@
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[2]</t>
+          <t xml:space="preserve">B2_fighter2.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……すぐ戻る</t>
+          <t xml:space="preserve">…私は間違っていない</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.quiet.cool[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6934,29 +6934,29 @@
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.quiet.cool[1]</t>
+          <t xml:space="preserve">B4_brand.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…戦わせてくれるなら、応える</t>
+          <t xml:space="preserve">…無駄口は叩かない。それがブランドには向いているかもな</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.quiet.cool[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6966,29 +6966,29 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.quiet.cool[1]</t>
+          <t xml:space="preserve">B4_cm.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……よろしく</t>
+          <t xml:space="preserve">…カメラか。まぁ、やる</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.quiet.cool[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6998,29 +6998,29 @@
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.quiet.cool[2]</t>
+          <t xml:space="preserve">B4_fan.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……始めよう</t>
+          <t xml:space="preserve">…来てくれた人には、ちゃんと応えたい</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.quiet.cool[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7030,29 +7030,29 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.quiet.cool[1]</t>
+          <t xml:space="preserve">B4_fashion.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やる。見ていてくれ</t>
+          <t xml:space="preserve">…余計なことはしない。ただ歩く。それだけだ</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.quiet.cool[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7062,29 +7062,29 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.quiet.cool[1]</t>
+          <t xml:space="preserve">B4_gravure.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やるべきことをやる</t>
+          <t xml:space="preserve">…写真か。余計なことはしないでくれ</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.quiet.cool[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7094,29 +7094,29 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.quiet.cool[2]</t>
+          <t xml:space="preserve">B4_variety.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……すぐ戻る</t>
+          <t xml:space="preserve">…無駄なことは言わない。それだけだ</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.quiet.cool[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7126,29 +7126,29 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.quiet.cool[1]</t>
+          <t xml:space="preserve">B4.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……(静かに立ち去る)</t>
+          <t xml:space="preserve">…やる。見ていてくれ</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.quiet.cool[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7158,12 +7158,12 @@
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.quiet.cool[2]</t>
+          <t xml:space="preserve">quiet.cool[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7173,14 +7173,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ありがとう</t>
+          <t xml:space="preserve">…戦わせてくれるなら、応える</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.quiet.cool[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.quiet.cool[1]</t>
+          <t xml:space="preserve">quiet.cool[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7205,14 +7205,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やるべきことはやる</t>
+          <t xml:space="preserve">……よろしく</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.quiet.cool[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.quiet.cool[2]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.quiet.cool[1]</t>
+          <t xml:space="preserve">quiet.cool[2]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7237,14 +7237,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…次で終わらせる</t>
+          <t xml:space="preserve">……始めよう</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.quiet.cool[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7254,12 +7254,12 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.quiet.cool[1]</t>
+          <t xml:space="preserve">quiet.cool[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7269,14 +7269,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…次も勝つ。それだけだ</t>
+          <t xml:space="preserve">…やる。見ていてくれ</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.quiet.cool[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.quiet.cool[1]</t>
+          <t xml:space="preserve">quiet.cool[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7301,14 +7301,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…認めよう。だが、終わりではない</t>
+          <t xml:space="preserve">…やるべきことをやる</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.quiet.cool[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.quiet.cool[2]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7318,12 +7318,12 @@
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.quiet.cool[1]</t>
+          <t xml:space="preserve">quiet.cool[2]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7333,14 +7333,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ようやくだ。この座は渡さない</t>
+          <t xml:space="preserve">……すぐ戻る</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7350,12 +7350,12 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7365,14 +7365,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……(静かに立ち去る)</t>
+          <t xml:space="preserve">……終わった。それだけだ。……それだけのはずだ</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.quiet.cool[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[2]</t>
+          <t xml:space="preserve">bitterPrematch.behind.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7397,14 +7397,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ありがとう</t>
+          <t xml:space="preserve">……終わっていない。……私の中では</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">draftInterest.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7429,14 +7429,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やるべきことはやる</t>
+          <t xml:space="preserve">…戦わせてくれるなら、応える</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7446,12 +7446,12 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">draftJoin.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7461,14 +7461,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…次で終わらせる</t>
+          <t xml:space="preserve">……よろしく</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.quiet.cool[2]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">draftJoin.quiet.cool[2]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7493,14 +7493,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…次も勝つ。それだけだ</t>
+          <t xml:space="preserve">……始めよう</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7510,12 +7510,12 @@
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">faGreeting.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7525,14 +7525,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…認めよう。だが、終わりではない</t>
+          <t xml:space="preserve">…拾われた。…なら、恩を返す</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">faSigning.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7557,14 +7557,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ようやくだ。この座は渡さない</t>
+          <t xml:space="preserve">…やる。見ていてくれ</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.quiet.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7574,29 +7574,29 @@
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.quiet.cool[1]</t>
+          <t xml:space="preserve">faWelcome.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……悪くない距離感だ</t>
+          <t xml:space="preserve">…やるべきことをやる</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.quiet.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7606,29 +7606,29 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.quiet.cool[1]</t>
+          <t xml:space="preserve">heatSelf.fresh.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……この人だけは、信じられる</t>
+          <t xml:space="preserve">…体は軽い。…今日は、かなり…やれる</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.quiet.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7638,29 +7638,29 @@
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.quiet.cool[1]</t>
+          <t xml:space="preserve">heatSelf.heavy.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……気になる。ただ、それだけだが</t>
+          <t xml:space="preserve">…重い。…やっても、抜けていくだけだ</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.quiet.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7670,29 +7670,29 @@
       </c>
       <c r="C230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.quiet.cool[1]</t>
+          <t xml:space="preserve">heatSelf.warm.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……超えなければ、先へ進めない</t>
+          <t xml:space="preserve">…動けている。…ただ、深さがない</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.quiet.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.quiet.cool[2]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7702,29 +7702,29 @@
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.quiet.cool[1]</t>
+          <t xml:space="preserve">injury.quiet.cool[2]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……この場所に、未来はあるのか</t>
+          <t xml:space="preserve">……すぐ戻る</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7734,29 +7734,29 @@
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">release.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……調子は落ち着いた。だが後退じゃない</t>
+          <t xml:space="preserve">……(静かに立ち去る)</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.quiet.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.quiet.cool[2]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7766,29 +7766,29 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.quiet.cool[1]</t>
+          <t xml:space="preserve">release.quiet.cool[2]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……最後。立てる。十分</t>
+          <t xml:space="preserve">……ありがとう</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.quiet.cool[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7798,29 +7798,29 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.quiet.cool[2]</t>
+          <t xml:space="preserve">rentalGreeting.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……傷は数えない。ただ、いく</t>
+          <t xml:space="preserve">…やるべきことはやる</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.quiet.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7830,29 +7830,29 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.quiet.cool[1]</t>
+          <t xml:space="preserve">scoutGreeting.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次</t>
+          <t xml:space="preserve">…期待には、応える</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.quiet.cool[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7862,29 +7862,29 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.quiet.cool[2]</t>
+          <t xml:space="preserve">titleChallengeLoss.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……倒す。残る</t>
+          <t xml:space="preserve">…次で終わらせる</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.quiet.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7894,29 +7894,29 @@
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.quiet.cool[1]</t>
+          <t xml:space="preserve">titleDefense.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……一人。まだ立ってる。次</t>
+          <t xml:space="preserve">…次も勝つ。それだけだ</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.quiet.cool[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7926,29 +7926,29 @@
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.quiet.cool[2]</t>
+          <t xml:space="preserve">titleLoss.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……退かない。出せ</t>
+          <t xml:space="preserve">…認めよう。だが、終わりではない</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.quiet.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7958,29 +7958,29 @@
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.quiet.cool[1]</t>
+          <t xml:space="preserve">titleWin.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……三人の結果。言葉は要らない</t>
+          <t xml:space="preserve">…ようやくだ。この座は渡さない</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.quiet.cool[2]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7990,29 +7990,29 @@
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.quiet.cool[2]</t>
+          <t xml:space="preserve">quiet.cool[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……一人では不可能だった。それは認める</t>
+          <t xml:space="preserve">……(静かに立ち去る)</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.quiet.cool[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.quiet.cool[2]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8022,29 +8022,29 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.quiet.cool[1]</t>
+          <t xml:space="preserve">quiet.cool[2]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……不十分だった。次がある</t>
+          <t xml:space="preserve">……ありがとう</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.quiet.cool[2]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8054,29 +8054,29 @@
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.quiet.cool[2]</t>
+          <t xml:space="preserve">quiet.cool[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……団体が負けた。それが全て。次に期す</t>
+          <t xml:space="preserve">…やるべきことはやる</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.quiet.cool[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8086,29 +8086,29 @@
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.quiet.cool[1]</t>
+          <t xml:space="preserve">quiet.cool[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……立っている。それが結果</t>
+          <t xml:space="preserve">…次で終わらせる</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.quiet.cool[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8118,29 +8118,29 @@
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.quiet.cool[2]</t>
+          <t xml:space="preserve">quiet.cool[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……数えてない。ただ、倒れなかった</t>
+          <t xml:space="preserve">…次も勝つ。それだけだ</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.quiet.cool[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8150,29 +8150,29 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.quiet.cool[1]</t>
+          <t xml:space="preserve">quiet.cool[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（トロフィーを静かに掲げる）</t>
+          <t xml:space="preserve">…認めよう。だが、終わりではない</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.quiet.cool[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8182,29 +8182,29 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.quiet.cool[2]</t>
+          <t xml:space="preserve">quiet.cool[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…………ありがとう</t>
+          <t xml:space="preserve">…ようやくだ。この座は渡さない</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.quiet.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8214,29 +8214,29 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.quiet.cool[1]</t>
+          <t xml:space="preserve">bond_39_down.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（無言で去る）</t>
+          <t xml:space="preserve">……終わりだ</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.quiet.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8246,29 +8246,29 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.quiet.cool[1]</t>
+          <t xml:space="preserve">bond_59_down.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（静かに頷く）</t>
+          <t xml:space="preserve">……遠い</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.quiet.cool[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.quiet.cool[2]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8278,29 +8278,29 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.quiet.cool[2]</t>
+          <t xml:space="preserve">bond_59_down.quiet.cool[2]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まだ</t>
+          <t xml:space="preserve">……もう、隣にいない</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.quiet.cool[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8310,29 +8310,29 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.quiet.cool[2]</t>
+          <t xml:space="preserve">bond_60_up.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（少し笑顔を見せる）</t>
+          <t xml:space="preserve">……悪くない距離感だ</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.quiet.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8342,29 +8342,29 @@
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.quiet.cool[1]</t>
+          <t xml:space="preserve">bond_80_up.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……最後</t>
+          <t xml:space="preserve">……この人だけは、信じられる</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.quiet.cool[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8374,29 +8374,29 @@
       </c>
       <c r="C252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.quiet.cool[2]</t>
+          <t xml:space="preserve">rivalry_29_down.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……全部、出す</t>
+          <t xml:space="preserve">……もう考えない</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.quiet.cool[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.quiet.cool[2]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8406,29 +8406,29 @@
       </c>
       <c r="C253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.quiet.cool[2]</t>
+          <t xml:space="preserve">rivalry_29_down.quiet.cool[2]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（拳を握る）</t>
+          <t xml:space="preserve">……風が止んだ</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.quiet.cool[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8438,29 +8438,29 @@
       </c>
       <c r="C254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.quiet.cool[2]</t>
+          <t xml:space="preserve">rivalry_30_up.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（静かに頷く）</t>
+          <t xml:space="preserve">……気になる。ただ、それだけだが</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8470,29 +8470,29 @@
       </c>
       <c r="C255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">rivalry_50_up.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…結果で語る</t>
+          <t xml:space="preserve">……超えなければ、先へ進めない</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8502,29 +8502,29 @@
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">rivalry_70_up.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（ベルトを静かに抱きしめる）</t>
+          <t xml:space="preserve">……あの相手がいる限り、立ち続ける</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.quiet.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.quiet.cool[2]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8534,29 +8534,29 @@
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">rivalry_70_up.quiet.cool[2]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……来い</t>
+          <t xml:space="preserve">……言葉はいらない。リングで話す</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.quiet.cool[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8566,29 +8566,29 @@
       </c>
       <c r="C258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[2]</t>
+          <t xml:space="preserve">trust_above_75.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（背を向ける）</t>
+          <t xml:space="preserve">……ここにいたい</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.quiet.cool[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.quiet.cool[2]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8598,29 +8598,29 @@
       </c>
       <c r="C259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.quiet.cool[2]</t>
+          <t xml:space="preserve">trust_above_75.quiet.cool[2]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（拳を握りしめる）</t>
+          <t xml:space="preserve">……この場所を守る</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.quiet.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8630,29 +8630,29 @@
       </c>
       <c r="C260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.quiet.cool[1]</t>
+          <t xml:space="preserve">trust_below_20.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（静かに頷く）</t>
+          <t xml:space="preserve">……（荷物をまとめている）</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.quiet.cool[2]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8662,29 +8662,29 @@
       </c>
       <c r="C261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">trust_below_20.quiet.cool[2]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……証明した。それだけ</t>
+          <t xml:space="preserve">……何も、残っていない</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.quiet.cool[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8694,29 +8694,29 @@
       </c>
       <c r="C262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[2]</t>
+          <t xml:space="preserve">trust_below_35.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……これがうちの力</t>
+          <t xml:space="preserve">……この場所に、未来はあるのか</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.quiet.cool[3]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8726,59 +8726,1115 @@
       </c>
       <c r="C263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[3]</t>
+          <t xml:space="preserve">quiet.cool[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（静かに頷く）</t>
+          <t xml:space="preserve">……調子は落ち着いた。だが後退じゃない</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.quiet.cool[1]</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.quiet.cool[1]</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……最後。立てる。十分</t>
+        </is>
+      </c>
+    </row>
+    <row r="265" ht="40" customHeight="1">
+      <c r="A265" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.quiet.cool[2]</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.quiet.cool[2]</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……傷は数えない。ただ、いく</t>
+        </is>
+      </c>
+    </row>
+    <row r="266" ht="40" customHeight="1">
+      <c r="A266" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.quiet.cool[1]</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.quiet.cool[1]</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……次</t>
+        </is>
+      </c>
+    </row>
+    <row r="267" ht="40" customHeight="1">
+      <c r="A267" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.quiet.cool[2]</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.quiet.cool[2]</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……倒す。残る</t>
+        </is>
+      </c>
+    </row>
+    <row r="268" ht="40" customHeight="1">
+      <c r="A268" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.quiet.cool[1]</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">survivor.quiet.cool[1]</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……一人。まだ立ってる。次</t>
+        </is>
+      </c>
+    </row>
+    <row r="269" ht="40" customHeight="1">
+      <c r="A269" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.quiet.cool[2]</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">survivor.quiet.cool[2]</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……退かない。出せ</t>
+        </is>
+      </c>
+    </row>
+    <row r="270" ht="40" customHeight="1">
+      <c r="A270" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.quiet.cool[1]</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.quiet.cool[1]</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……三人の結果。言葉は要らない</t>
+        </is>
+      </c>
+    </row>
+    <row r="271" ht="40" customHeight="1">
+      <c r="A271" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.quiet.cool[2]</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.quiet.cool[2]</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……一人では不可能だった。それは認める</t>
+        </is>
+      </c>
+    </row>
+    <row r="272" ht="40" customHeight="1">
+      <c r="A272" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.quiet.cool[1]</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">defiant.quiet.cool[1]</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……不十分だった。次がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="273" ht="40" customHeight="1">
+      <c r="A273" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.quiet.cool[2]</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">defiant.quiet.cool[2]</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……団体が負けた。それが全て。次に期す</t>
+        </is>
+      </c>
+    </row>
+    <row r="274" ht="40" customHeight="1">
+      <c r="A274" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.quiet.cool[1]</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.quiet.cool[1]</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……立っている。それが結果</t>
+        </is>
+      </c>
+    </row>
+    <row r="275" ht="40" customHeight="1">
+      <c r="A275" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.quiet.cool[2]</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.quiet.cool[2]</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……数えてない。ただ、倒れなかった</t>
+        </is>
+      </c>
+    </row>
+    <row r="276" ht="40" customHeight="1">
+      <c r="A276" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.quiet.cool[1]</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.quiet.cool[1]</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……（トロフィーを静かに掲げる）</t>
+        </is>
+      </c>
+    </row>
+    <row r="277" ht="40" customHeight="1">
+      <c r="A277" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.quiet.cool[2]</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.quiet.cool[2]</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…………ありがとう</t>
+        </is>
+      </c>
+    </row>
+    <row r="278" ht="40" customHeight="1">
+      <c r="A278" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.quiet.cool[1]</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postLose.quiet.cool[1]</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……（無言で去る）</t>
+        </is>
+      </c>
+    </row>
+    <row r="279" ht="40" customHeight="1">
+      <c r="A279" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.quiet.cool[1]</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postMatchWin.quiet.cool[1]</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……（静かに頷く）</t>
+        </is>
+      </c>
+    </row>
+    <row r="280" ht="40" customHeight="1">
+      <c r="A280" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.quiet.cool[2]</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postMatchWin.quiet.cool[2]</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……まだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="281" ht="40" customHeight="1">
+      <c r="A281" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.quiet.cool[2]</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postWin.quiet.cool[2]</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……（少し笑顔を見せる）</t>
+        </is>
+      </c>
+    </row>
+    <row r="282" ht="40" customHeight="1">
+      <c r="A282" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.quiet.cool[1]</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.quiet.cool[1]</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……最後</t>
+        </is>
+      </c>
+    </row>
+    <row r="283" ht="40" customHeight="1">
+      <c r="A283" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.quiet.cool[2]</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.quiet.cool[2]</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……全部、出す</t>
+        </is>
+      </c>
+    </row>
+    <row r="284" ht="40" customHeight="1">
+      <c r="A284" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.quiet.cool[2]</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.quiet.cool[2]</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……（拳を握る）</t>
+        </is>
+      </c>
+    </row>
+    <row r="285" ht="40" customHeight="1">
+      <c r="A285" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.quiet.cool[2]</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">summon.quiet.cool[2]</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……（静かに頷く）</t>
+        </is>
+      </c>
+    </row>
+    <row r="286" ht="40" customHeight="1">
+      <c r="A286" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.quiet.cool[1]</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">quiet.cool[1]</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…結果で語る</t>
+        </is>
+      </c>
+    </row>
+    <row r="287" ht="40" customHeight="1">
+      <c r="A287" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.quiet.cool[1]</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">quiet.cool[1]</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">………（ベルトを静かに抱きしめる）</t>
+        </is>
+      </c>
+    </row>
+    <row r="288" ht="40" customHeight="1">
+      <c r="A288" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.quiet.cool[1]</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">quiet.cool[1]</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……来い</t>
+        </is>
+      </c>
+    </row>
+    <row r="289" ht="40" customHeight="1">
+      <c r="A289" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.quiet.cool[2]</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">quiet.cool[2]</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……（背を向ける）</t>
+        </is>
+      </c>
+    </row>
+    <row r="290" ht="40" customHeight="1">
+      <c r="A290" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.quiet.cool[2]</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_lose.quiet.cool[2]</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……（拳を握りしめる）</t>
+        </is>
+      </c>
+    </row>
+    <row r="291" ht="40" customHeight="1">
+      <c r="A291" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.quiet.cool[1]</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.quiet.cool[1]</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……（静かに頷く）</t>
+        </is>
+      </c>
+    </row>
+    <row r="292" ht="40" customHeight="1">
+      <c r="A292" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.quiet.cool[1]</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">quiet.cool[1]</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……証明した。それだけ</t>
+        </is>
+      </c>
+    </row>
+    <row r="293" ht="40" customHeight="1">
+      <c r="A293" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.quiet.cool[2]</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">quiet.cool[2]</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……これがうちの力</t>
+        </is>
+      </c>
+    </row>
+    <row r="294" ht="40" customHeight="1">
+      <c r="A294" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.quiet.cool[3]</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">quiet.cool[3]</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……（静かに頷く）</t>
+        </is>
+      </c>
+    </row>
+    <row r="295" ht="40" customHeight="1">
+      <c r="A295" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">ENDING_LINES.fighter.quiet.cool[1]</t>
         </is>
       </c>
-      <c r="B264" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr" s="2">
+      <c r="B295" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr" s="12">
+      <c r="D295" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fighter.quiet.cool[1]</t>
         </is>
       </c>
-      <c r="E264" t="inlineStr" s="2">
+      <c r="E295" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
-      <c r="F264" t="inlineStr" s="3">
+      <c r="F295" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…ここまで来たか</t>
         </is>
       </c>
     </row>
+    <row r="296" ht="40" customHeight="1">
+      <c r="A296" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.quiet.cool[1]</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">quiet.cool[1]</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…拾われた。…なら、恩を返す</t>
+        </is>
+      </c>
+    </row>
+    <row r="297" ht="40" customHeight="1">
+      <c r="A297" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.quiet.cool[1]</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">quiet.cool[1]</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…期待には、応える</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H264"/>
+  <autoFilter ref="A1:H297"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/クール×寡黙.xlsx
+++ b/セリフ編集/キャラタイプ別/クール×寡黙.xlsx
@@ -306,7 +306,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H297"/>
+  <dimension ref="A1:H332"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -364,7 +364,7 @@
     <row r="2" ht="40" customHeight="1">
       <c r="A2" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.quiet.cool[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="2">
@@ -379,7 +379,7 @@
       </c>
       <c r="D2" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.quiet.cool[1]</t>
+          <t xml:space="preserve">atk.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr" s="2">
@@ -396,7 +396,7 @@
     <row r="3" ht="40" customHeight="1">
       <c r="A3" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.quiet.cool[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
@@ -411,7 +411,7 @@
       </c>
       <c r="D3" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.quiet.cool[2]</t>
+          <t xml:space="preserve">atk.cool.quiet[2]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr" s="2">
@@ -428,7 +428,7 @@
     <row r="4" ht="40" customHeight="1">
       <c r="A4" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.quiet.cool[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.cool.quiet[3]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
@@ -443,7 +443,7 @@
       </c>
       <c r="D4" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.quiet.cool[3]</t>
+          <t xml:space="preserve">atk.cool.quiet[3]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr" s="2">
@@ -460,7 +460,7 @@
     <row r="5" ht="40" customHeight="1">
       <c r="A5" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.quiet.cool[4]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.cool.quiet[4]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
@@ -475,7 +475,7 @@
       </c>
       <c r="D5" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.quiet.cool[4]</t>
+          <t xml:space="preserve">atk.cool.quiet[4]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr" s="2">
@@ -492,7 +492,7 @@
     <row r="6" ht="40" customHeight="1">
       <c r="A6" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.quiet.cool[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
@@ -507,7 +507,7 @@
       </c>
       <c r="D6" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.quiet.cool[2]</t>
+          <t xml:space="preserve">bigmove.cool.quiet[2]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr" s="2">
@@ -524,7 +524,7 @@
     <row r="7" ht="40" customHeight="1">
       <c r="A7" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.quiet.cool[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.cool.quiet[3]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
@@ -539,7 +539,7 @@
       </c>
       <c r="D7" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.quiet.cool[3]</t>
+          <t xml:space="preserve">bigmove.cool.quiet[3]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr" s="2">
@@ -556,7 +556,7 @@
     <row r="8" ht="40" customHeight="1">
       <c r="A8" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.quiet.cool[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
@@ -571,7 +571,7 @@
       </c>
       <c r="D8" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.quiet.cool[1]</t>
+          <t xml:space="preserve">climax.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr" s="2">
@@ -588,7 +588,7 @@
     <row r="9" ht="40" customHeight="1">
       <c r="A9" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.quiet.cool[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
@@ -603,7 +603,7 @@
       </c>
       <c r="D9" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.quiet.cool[2]</t>
+          <t xml:space="preserve">climax.cool.quiet[2]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr" s="2">
@@ -620,7 +620,7 @@
     <row r="10" ht="40" customHeight="1">
       <c r="A10" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
@@ -635,7 +635,7 @@
       </c>
       <c r="D10" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr" s="2">
@@ -652,7 +652,7 @@
     <row r="11" ht="40" customHeight="1">
       <c r="A11" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.quiet.cool[2]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
@@ -667,7 +667,7 @@
       </c>
       <c r="D11" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[2]</t>
+          <t xml:space="preserve">cool.quiet[2]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr" s="2">
@@ -684,7 +684,7 @@
     <row r="12" ht="40" customHeight="1">
       <c r="A12" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.quiet.cool[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
@@ -699,7 +699,7 @@
       </c>
       <c r="D12" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">badWinner.quiet.cool[1]</t>
+          <t xml:space="preserve">badWinner.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr" s="2">
@@ -716,7 +716,7 @@
     <row r="13" ht="40" customHeight="1">
       <c r="A13" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.quiet.cool[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
@@ -731,7 +731,7 @@
       </c>
       <c r="D13" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">goodWinner.quiet.cool[1]</t>
+          <t xml:space="preserve">goodWinner.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr" s="2">
@@ -748,7 +748,7 @@
     <row r="14" ht="40" customHeight="1">
       <c r="A14" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.quiet.cool[2]</t>
+          <t xml:space="preserve">FIRST_MEET_LINES.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
@@ -763,7 +763,7 @@
       </c>
       <c r="D14" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[2]</t>
+          <t xml:space="preserve">cool.quiet[2]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr" s="2">
@@ -780,7 +780,7 @@
     <row r="15" ht="40" customHeight="1">
       <c r="A15" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.quiet.cool[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
@@ -795,7 +795,7 @@
       </c>
       <c r="D15" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.quiet.cool[1]</t>
+          <t xml:space="preserve">competition_won.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr" s="2">
@@ -812,7 +812,7 @@
     <row r="16" ht="40" customHeight="1">
       <c r="A16" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.quiet.cool[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
@@ -827,7 +827,7 @@
       </c>
       <c r="D16" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.quiet.cool[2]</t>
+          <t xml:space="preserve">competition_won.cool.quiet[2]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr" s="2">
@@ -844,7 +844,7 @@
     <row r="17" ht="40" customHeight="1">
       <c r="A17" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.quiet.cool[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
@@ -859,7 +859,7 @@
       </c>
       <c r="D17" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">direct.quiet.cool[1]</t>
+          <t xml:space="preserve">direct.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr" s="2">
@@ -876,7 +876,7 @@
     <row r="18" ht="40" customHeight="1">
       <c r="A18" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.quiet.cool[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
@@ -891,7 +891,7 @@
       </c>
       <c r="D18" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">direct.quiet.cool[2]</t>
+          <t xml:space="preserve">direct.cool.quiet[2]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr" s="2">
@@ -908,7 +908,7 @@
     <row r="19" ht="40" customHeight="1">
       <c r="A19" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.quiet.cool[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
@@ -923,7 +923,7 @@
       </c>
       <c r="D19" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fa_signing.quiet.cool[1]</t>
+          <t xml:space="preserve">fa_signing.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr" s="2">
@@ -940,7 +940,7 @@
     <row r="20" ht="40" customHeight="1">
       <c r="A20" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.quiet.cool[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
@@ -955,7 +955,7 @@
       </c>
       <c r="D20" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fa_signing.quiet.cool[2]</t>
+          <t xml:space="preserve">fa_signing.cool.quiet[2]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr" s="2">
@@ -972,7 +972,7 @@
     <row r="21" ht="40" customHeight="1">
       <c r="A21" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.quiet.cool.hit[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.cool.quiet.hit[1]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
@@ -987,7 +987,7 @@
       </c>
       <c r="D21" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool.hit[1]</t>
+          <t xml:space="preserve">cool.quiet.hit[1]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr" s="2">
@@ -1004,7 +1004,7 @@
     <row r="22" ht="40" customHeight="1">
       <c r="A22" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.quiet.cool.hit[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.cool.quiet.hit[2]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="D22" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool.hit[2]</t>
+          <t xml:space="preserve">cool.quiet.hit[2]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr" s="2">
@@ -1036,7 +1036,7 @@
     <row r="23" ht="40" customHeight="1">
       <c r="A23" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.quiet.cool.win[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.cool.quiet.win[1]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="D23" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool.win[1]</t>
+          <t xml:space="preserve">cool.quiet.win[1]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr" s="2">
@@ -1068,7 +1068,7 @@
     <row r="24" ht="40" customHeight="1">
       <c r="A24" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.quiet.cool.win[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.cool.quiet.win[2]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="D24" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool.win[2]</t>
+          <t xml:space="preserve">cool.quiet.win[2]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr" s="2">
@@ -1100,7 +1100,7 @@
     <row r="25" ht="40" customHeight="1">
       <c r="A25" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="D25" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr" s="2">
@@ -1132,7 +1132,7 @@
     <row r="26" ht="40" customHeight="1">
       <c r="A26" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.quiet.cool[2]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="D26" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[2]</t>
+          <t xml:space="preserve">cool.quiet[2]</t>
         </is>
       </c>
       <c r="E26" t="inlineStr" s="2">
@@ -1164,7 +1164,7 @@
     <row r="27" ht="40" customHeight="1">
       <c r="A27" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="D27" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr" s="2">
@@ -1196,7 +1196,7 @@
     <row r="28" ht="40" customHeight="1">
       <c r="A28" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.quiet.cool[2]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="D28" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[2]</t>
+          <t xml:space="preserve">cool.quiet[2]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr" s="2">
@@ -1228,7 +1228,7 @@
     <row r="29" ht="40" customHeight="1">
       <c r="A29" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.quiet.cool[3]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.cool.quiet[3]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="D29" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[3]</t>
+          <t xml:space="preserve">cool.quiet[3]</t>
         </is>
       </c>
       <c r="E29" t="inlineStr" s="2">
@@ -1260,7 +1260,7 @@
     <row r="30" ht="40" customHeight="1">
       <c r="A30" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="D30" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr" s="2">
@@ -1292,7 +1292,7 @@
     <row r="31" ht="40" customHeight="1">
       <c r="A31" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.quiet.cool[2]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="D31" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[2]</t>
+          <t xml:space="preserve">cool.quiet[2]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr" s="2">
@@ -1324,7 +1324,7 @@
     <row r="32" ht="40" customHeight="1">
       <c r="A32" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.quiet.cool[3]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.cool.quiet[3]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="D32" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[3]</t>
+          <t xml:space="preserve">cool.quiet[3]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr" s="2">
@@ -1356,7 +1356,7 @@
     <row r="33" ht="40" customHeight="1">
       <c r="A33" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="D33" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E33" t="inlineStr" s="2">
@@ -1388,7 +1388,7 @@
     <row r="34" ht="40" customHeight="1">
       <c r="A34" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.quiet.cool[2]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="D34" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[2]</t>
+          <t xml:space="preserve">cool.quiet[2]</t>
         </is>
       </c>
       <c r="E34" t="inlineStr" s="2">
@@ -1420,7 +1420,7 @@
     <row r="35" ht="40" customHeight="1">
       <c r="A35" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.quiet.cool[3]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.cool.quiet[3]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="D35" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[3]</t>
+          <t xml:space="preserve">cool.quiet[3]</t>
         </is>
       </c>
       <c r="E35" t="inlineStr" s="2">
@@ -1452,7 +1452,7 @@
     <row r="36" ht="40" customHeight="1">
       <c r="A36" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="D36" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr" s="2">
@@ -1484,7 +1484,7 @@
     <row r="37" ht="40" customHeight="1">
       <c r="A37" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.quiet.cool[2]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="D37" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[2]</t>
+          <t xml:space="preserve">cool.quiet[2]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr" s="2">
@@ -1516,7 +1516,7 @@
     <row r="38" ht="40" customHeight="1">
       <c r="A38" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_WIN_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="D38" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E38" t="inlineStr" s="2">
@@ -1548,7 +1548,7 @@
     <row r="39" ht="40" customHeight="1">
       <c r="A39" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_WIN_LINES.quiet.cool[2]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="D39" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[2]</t>
+          <t xml:space="preserve">cool.quiet[2]</t>
         </is>
       </c>
       <c r="E39" t="inlineStr" s="2">
@@ -1580,7 +1580,7 @@
     <row r="40" ht="40" customHeight="1">
       <c r="A40" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.quiet.cool[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="D40" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ahead.quiet.cool[1]</t>
+          <t xml:space="preserve">ahead.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E40" t="inlineStr" s="2">
@@ -1612,7 +1612,7 @@
     <row r="41" ht="40" customHeight="1">
       <c r="A41" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.quiet.cool[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="D41" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">behind.quiet.cool[1]</t>
+          <t xml:space="preserve">behind.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr" s="2">
@@ -1644,7 +1644,7 @@
     <row r="42" ht="40" customHeight="1">
       <c r="A42" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.quiet.cool[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="D42" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.quiet.cool[1]</t>
+          <t xml:space="preserve">loser.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E42" t="inlineStr" s="2">
@@ -1676,7 +1676,7 @@
     <row r="43" ht="40" customHeight="1">
       <c r="A43" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.quiet.cool[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="D43" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.quiet.cool[1]</t>
+          <t xml:space="preserve">winner.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E43" t="inlineStr" s="2">
@@ -1708,7 +1708,7 @@
     <row r="44" ht="40" customHeight="1">
       <c r="A44" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.quiet.cool[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="D44" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.quiet.cool[1]</t>
+          <t xml:space="preserve">loser.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E44" t="inlineStr" s="2">
@@ -1740,7 +1740,7 @@
     <row r="45" ht="40" customHeight="1">
       <c r="A45" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.quiet.cool[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="D45" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.quiet.cool[1]</t>
+          <t xml:space="preserve">winner.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E45" t="inlineStr" s="2">
@@ -1772,7 +1772,7 @@
     <row r="46" ht="40" customHeight="1">
       <c r="A46" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.quiet.cool[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="D46" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.quiet.cool[1]</t>
+          <t xml:space="preserve">attacker.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E46" t="inlineStr" s="2">
@@ -1804,7 +1804,7 @@
     <row r="47" ht="40" customHeight="1">
       <c r="A47" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.quiet.cool[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="D47" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.quiet.cool[1]</t>
+          <t xml:space="preserve">defender.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E47" t="inlineStr" s="2">
@@ -1836,7 +1836,7 @@
     <row r="48" ht="40" customHeight="1">
       <c r="A48" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.quiet.cool[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="D48" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.quiet.cool[1]</t>
+          <t xml:space="preserve">defender.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E48" t="inlineStr" s="2">
@@ -1868,7 +1868,7 @@
     <row r="49" ht="40" customHeight="1">
       <c r="A49" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.quiet.cool[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="D49" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.quiet.cool[1]</t>
+          <t xml:space="preserve">attacker.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E49" t="inlineStr" s="2">
@@ -1900,7 +1900,7 @@
     <row r="50" ht="40" customHeight="1">
       <c r="A50" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.quiet.cool[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="D50" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.quiet.cool[1]</t>
+          <t xml:space="preserve">defender.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E50" t="inlineStr" s="2">
@@ -1932,7 +1932,7 @@
     <row r="51" ht="40" customHeight="1">
       <c r="A51" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.quiet.cool[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="D51" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.quiet.cool[1]</t>
+          <t xml:space="preserve">loserLines.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E51" t="inlineStr" s="2">
@@ -1964,7 +1964,7 @@
     <row r="52" ht="40" customHeight="1">
       <c r="A52" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.quiet.cool[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="D52" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.quiet.cool[1]</t>
+          <t xml:space="preserve">winnerLines.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E52" t="inlineStr" s="2">
@@ -1996,7 +1996,7 @@
     <row r="53" ht="40" customHeight="1">
       <c r="A53" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.quiet.cool[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="D53" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.quiet.cool[1]</t>
+          <t xml:space="preserve">loser.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E53" t="inlineStr" s="2">
@@ -2028,7 +2028,7 @@
     <row r="54" ht="40" customHeight="1">
       <c r="A54" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.quiet.cool[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="D54" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.quiet.cool[1]</t>
+          <t xml:space="preserve">winner.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E54" t="inlineStr" s="2">
@@ -2060,7 +2060,7 @@
     <row r="55" ht="40" customHeight="1">
       <c r="A55" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.quiet.cool[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="D55" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.quiet.cool[1]</t>
+          <t xml:space="preserve">loserLines.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E55" t="inlineStr" s="2">
@@ -2092,7 +2092,7 @@
     <row r="56" ht="40" customHeight="1">
       <c r="A56" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.quiet.cool[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="D56" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.quiet.cool[1]</t>
+          <t xml:space="preserve">winnerLines.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E56" t="inlineStr" s="2">
@@ -2124,7 +2124,7 @@
     <row r="57" ht="40" customHeight="1">
       <c r="A57" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.quiet.cool[1]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="D57" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">awakening.quiet.cool[1]</t>
+          <t xml:space="preserve">awakening.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr" s="2">
@@ -2924,7 +2924,7 @@
     <row r="82" ht="40" customHeight="1">
       <c r="A82" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.quiet.cool[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B82" t="inlineStr" s="2">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="D82" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.quiet.cool[1]</t>
+          <t xml:space="preserve">accepted.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E82" t="inlineStr" s="2">
@@ -2956,7 +2956,7 @@
     <row r="83" ht="40" customHeight="1">
       <c r="A83" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.quiet.cool[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="2">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="D83" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.quiet.cool[2]</t>
+          <t xml:space="preserve">accepted.cool.quiet[2]</t>
         </is>
       </c>
       <c r="E83" t="inlineStr" s="2">
@@ -2988,7 +2988,7 @@
     <row r="84" ht="40" customHeight="1">
       <c r="A84" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.quiet.cool[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="2">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="D84" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.quiet.cool[1]</t>
+          <t xml:space="preserve">defended.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E84" t="inlineStr" s="2">
@@ -3020,7 +3020,7 @@
     <row r="85" ht="40" customHeight="1">
       <c r="A85" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.quiet.cool[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="2">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="D85" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.quiet.cool[2]</t>
+          <t xml:space="preserve">defended.cool.quiet[2]</t>
         </is>
       </c>
       <c r="E85" t="inlineStr" s="2">
@@ -3052,7 +3052,7 @@
     <row r="86" ht="40" customHeight="1">
       <c r="A86" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.quiet.cool[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="2">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="D86" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.quiet.cool[1]</t>
+          <t xml:space="preserve">defense_failed.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E86" t="inlineStr" s="2">
@@ -3084,7 +3084,7 @@
     <row r="87" ht="40" customHeight="1">
       <c r="A87" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.quiet.cool[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="2">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="D87" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.quiet.cool[2]</t>
+          <t xml:space="preserve">defense_failed.cool.quiet[2]</t>
         </is>
       </c>
       <c r="E87" t="inlineStr" s="2">
@@ -3116,7 +3116,7 @@
     <row r="88" ht="40" customHeight="1">
       <c r="A88" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.default.quiet.cool[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.default.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="D88" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">default.quiet.cool[1]</t>
+          <t xml:space="preserve">default.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E88" t="inlineStr" s="2">
@@ -3148,7 +3148,7 @@
     <row r="89" ht="40" customHeight="1">
       <c r="A89" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.former_champ.quiet.cool[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.former_champ.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="D89" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">former_champ.quiet.cool[1]</t>
+          <t xml:space="preserve">former_champ.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr" s="2">
@@ -3180,7 +3180,7 @@
     <row r="90" ht="40" customHeight="1">
       <c r="A90" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.heel.quiet.cool[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.heel.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="D90" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heel.quiet.cool[1]</t>
+          <t xml:space="preserve">heel.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr" s="2">
@@ -3212,7 +3212,7 @@
     <row r="91" ht="40" customHeight="1">
       <c r="A91" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.high_trust.quiet.cool[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.high_trust.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="D91" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">high_trust.quiet.cool[1]</t>
+          <t xml:space="preserve">high_trust.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr" s="2">
@@ -3244,7 +3244,7 @@
     <row r="92" ht="40" customHeight="1">
       <c r="A92" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.quiet.cool[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="D92" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_former_champ.quiet.cool[1]</t>
+          <t xml:space="preserve">accept_former_champ.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E92" t="inlineStr" s="2">
@@ -3276,7 +3276,7 @@
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.quiet.cool[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_heel.quiet.cool[1]</t>
+          <t xml:space="preserve">accept_heel.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E93" t="inlineStr" s="2">
@@ -3308,7 +3308,7 @@
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.quiet.cool[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_no_title.quiet.cool[1]</t>
+          <t xml:space="preserve">accept_no_title.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr" s="2">
@@ -3340,7 +3340,7 @@
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.quiet.cool[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_terminal.quiet.cool[1]</t>
+          <t xml:space="preserve">accept_terminal.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr" s="2">
@@ -3372,7 +3372,7 @@
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.quiet.cool[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_winless.quiet.cool[1]</t>
+          <t xml:space="preserve">accept_winless.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr" s="2">
@@ -3404,7 +3404,7 @@
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.quiet.cool[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_champ.quiet.cool[1]</t>
+          <t xml:space="preserve">refuse_champ.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr" s="2">
@@ -3436,7 +3436,7 @@
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.quiet.cool[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_distrust.quiet.cool[1]</t>
+          <t xml:space="preserve">refuse_distrust.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr" s="2">
@@ -3468,7 +3468,7 @@
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.quiet.cool[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_fighting.quiet.cool[1]</t>
+          <t xml:space="preserve">refuse_fighting.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr" s="2">
@@ -3500,7 +3500,7 @@
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.quiet.cool[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_heel.quiet.cool[1]</t>
+          <t xml:space="preserve">refuse_heel.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr" s="2">
@@ -3532,7 +3532,7 @@
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.quiet.cool[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A1_champion.quiet.cool[1]</t>
+          <t xml:space="preserve">A1_champion.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr" s="2">
@@ -3564,7 +3564,7 @@
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.quiet.cool[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A2_uncrowned.quiet.cool[1]</t>
+          <t xml:space="preserve">A2_uncrowned.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr" s="2">
@@ -3596,7 +3596,7 @@
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.quiet.cool[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A3_heel.quiet.cool[1]</t>
+          <t xml:space="preserve">A3_heel.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr" s="2">
@@ -3628,7 +3628,7 @@
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.quiet.cool[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A4_veteran.quiet.cool[1]</t>
+          <t xml:space="preserve">A4_veteran.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr" s="2">
@@ -3660,7 +3660,7 @@
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B1_young.quiet.cool[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1_young.quiet.cool[1]</t>
+          <t xml:space="preserve">B1_young.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="2">
@@ -3692,7 +3692,7 @@
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.quiet.cool[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_prime.quiet.cool[1]</t>
+          <t xml:space="preserve">B2_prime.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="2">
@@ -3724,7 +3724,7 @@
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B3_older.quiet.cool[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3_older.quiet.cool[1]</t>
+          <t xml:space="preserve">B3_older.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="2">
@@ -3756,7 +3756,7 @@
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.quiet.cool[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3771,7 +3771,7 @@
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_champion_injury.quiet.cool[1]</t>
+          <t xml:space="preserve">B4_champion_injury.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="2">
@@ -3788,7 +3788,7 @@
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="2">
@@ -3820,7 +3820,7 @@
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.quiet.cool[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3835,7 +3835,7 @@
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.quiet.cool[1]</t>
+          <t xml:space="preserve">raise_accept.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="2">
@@ -3852,7 +3852,7 @@
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.quiet.cool[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.quiet.cool[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
@@ -3884,7 +3884,7 @@
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.quiet.cool[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.quiet.cool[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
@@ -3916,7 +3916,7 @@
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.quiet.cool[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.quiet.cool[1]</t>
+          <t xml:space="preserve">raise_open.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
@@ -3948,7 +3948,7 @@
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.quiet.cool[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.quiet.cool[1]</t>
+          <t xml:space="preserve">raise_refuse.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -3980,7 +3980,7 @@
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.quiet.cool[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.quiet.cool[1]</t>
+          <t xml:space="preserve">sudden_departure.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -4005,14 +4005,14 @@
       </c>
       <c r="F115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…聞いてくれるんだ。{record}…ここにいる意味が、分からない</t>
+          <t xml:space="preserve">……すみません。……もう、限界です</t>
         </is>
       </c>
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.quiet.cool[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.quiet.cool[1]</t>
+          <t xml:space="preserve">sudden_departure.cool.quiet[2]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
@@ -4037,14 +4037,14 @@
       </c>
       <c r="F116" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…{tenure}…出たい。…それだけ</t>
+          <t xml:space="preserve">……黙って消えようかと思った。……一応、挨拶だけ</t>
         </is>
       </c>
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.quiet.cool[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.quiet.cool[1]</t>
+          <t xml:space="preserve">transfer_listen.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
@@ -4069,14 +4069,14 @@
       </c>
       <c r="F117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…{tenure_farewell}{rivalry}…ありがとう</t>
+          <t xml:space="preserve">…聞いてくれるんだ。{record}…ここにいる意味が、分からない</t>
         </is>
       </c>
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.quiet.cool[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.quiet.cool[1]</t>
+          <t xml:space="preserve">transfer_open.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
@@ -4101,14 +4101,14 @@
       </c>
       <c r="F118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ごめん。…もう決めた</t>
+          <t xml:space="preserve">…{tenure}…出たい。…それだけ</t>
         </is>
       </c>
     </row>
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.quiet.cool[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4123,7 +4123,7 @@
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.quiet.cool[1]</t>
+          <t xml:space="preserve">transfer_release.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
@@ -4133,14 +4133,14 @@
       </c>
       <c r="F119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そこまで言うなら。…もう少しだけ</t>
+          <t xml:space="preserve">…{tenure_farewell}{rivalry}…ありがとう</t>
         </is>
       </c>
     </row>
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.blocked.quiet.cool[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4150,12 +4150,12 @@
       </c>
       <c r="C120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">blocked.quiet.cool[1]</t>
+          <t xml:space="preserve">transfer_retain_fail.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
@@ -4165,14 +4165,14 @@
       </c>
       <c r="F120" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…話にならない。断る</t>
+          <t xml:space="preserve">…ごめん。…もう決めた</t>
         </is>
       </c>
     </row>
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.fail.quiet.cool[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="C121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fail.quiet.cool[1]</t>
+          <t xml:space="preserve">transfer_retain_success.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
@@ -4197,14 +4197,14 @@
       </c>
       <c r="F121" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…断る</t>
+          <t xml:space="preserve">…そこまで言うなら。…もう少しだけ</t>
         </is>
       </c>
     </row>
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.quiet.cool[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.blocked.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">start.quiet.cool[1]</t>
+          <t xml:space="preserve">blocked.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
@@ -4229,14 +4229,14 @@
       </c>
       <c r="F122" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…聞こう</t>
+          <t xml:space="preserve">…話にならない。断る</t>
         </is>
       </c>
     </row>
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.success.quiet.cool[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.fail.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">success.quiet.cool[1]</t>
+          <t xml:space="preserve">fail.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
@@ -4261,93 +4261,93 @@
       </c>
       <c r="F123" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…行く</t>
+          <t xml:space="preserve">…断る</t>
         </is>
       </c>
     </row>
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F01_LEADER_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F01_LEADER_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">start.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F124" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……別にいいよ、ついてきたいなら。</t>
+          <t xml:space="preserve">…聞こう</t>
         </is>
       </c>
     </row>
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F01_LEADER_LINES.quiet.cool[2]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.success.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F01_LEADER_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[2]</t>
+          <t xml:space="preserve">success.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F125" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……邪魔はしない。勝手についてくればいい。</t>
+          <t xml:space="preserve">…行く</t>
         </is>
       </c>
     </row>
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LEADER_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LEADER_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr" s="2">
@@ -4357,29 +4357,29 @@
       </c>
       <c r="F126" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……交わる気はない。</t>
+          <t xml:space="preserve">…社長、私たちのこと、気にかけていただけますか。</t>
         </is>
       </c>
     </row>
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F03_SURVIVOR_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F03_SURVIVOR_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr" s="2">
@@ -4389,29 +4389,29 @@
       </c>
       <c r="F127" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……何も言葉が出てこない。</t>
+          <t xml:space="preserve">…社長、次のメイン、私たちに回せませんか。</t>
         </is>
       </c>
     </row>
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F04_TARGET_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F04_TARGET_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="2">
@@ -4421,29 +4421,29 @@
       </c>
       <c r="F128" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もう、決めたから。</t>
+          <t xml:space="preserve">…社長、給与のこと、相談があります。</t>
         </is>
       </c>
     </row>
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr" s="2">
@@ -4453,29 +4453,29 @@
       </c>
       <c r="F129" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……静かに、離れたい。</t>
+          <t xml:space="preserve">…社長、私たちの仕事、見ていますか。</t>
         </is>
       </c>
     </row>
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr" s="2">
@@ -4485,29 +4485,29 @@
       </c>
       <c r="F130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まあ、別にいいよ。</t>
+          <t xml:space="preserve">…ありがとうございます。…見ていてくれたんですね。</t>
         </is>
       </c>
     </row>
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F07_LEADER_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F07_LEADER_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr" s="2">
@@ -4517,29 +4517,29 @@
       </c>
       <c r="F131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ちゃんと見てほしい。それだけ。</t>
+          <t xml:space="preserve">…はい、わかりました。</t>
         </is>
       </c>
     </row>
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_LEADER_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_LEADER_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr" s="2">
@@ -4549,29 +4549,29 @@
       </c>
       <c r="F132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……リングで、会う。</t>
+          <t xml:space="preserve">…ありがとうございます。受け取ります。</t>
         </is>
       </c>
     </row>
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.quiet.cool.hp_high[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool.hp_high[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr" s="2">
@@ -4581,29 +4581,29 @@
       </c>
       <c r="F133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……負け。それだけ</t>
+          <t xml:space="preserve">…ありがとうございます。やります。</t>
         </is>
       </c>
     </row>
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.quiet.cool.hp_mid[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool.hp_mid[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
@@ -4613,29 +4613,29 @@
       </c>
       <c r="F134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……っ……</t>
+          <t xml:space="preserve">…はい、わかりました。</t>
         </is>
       </c>
     </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.quiet.cool.high[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool.high[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
@@ -4645,29 +4645,29 @@
       </c>
       <c r="F135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……結果がすべて、だろ</t>
+          <t xml:space="preserve">…ありがとうございます。受け取ります。</t>
         </is>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.quiet.cool.high[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool.high[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
@@ -4677,29 +4677,29 @@
       </c>
       <c r="F136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……話すことは、もうない</t>
+          <t xml:space="preserve">…ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.quiet.cool.high[2]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool.high[2]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
@@ -4709,29 +4709,29 @@
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……決着、つけよう</t>
+          <t xml:space="preserve">…はい、わかりました。</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.quiet.cool.high[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool.high[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
@@ -4741,29 +4741,29 @@
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……いいだろう。受けて立つ</t>
+          <t xml:space="preserve">…ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A.quiet.cool.high[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool.high[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
@@ -4773,29 +4773,29 @@
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……話すことは、もう何もない</t>
+          <t xml:space="preserve">…ありがとうございます。…見ていてくれたんですね。</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_B.quiet.cool.high[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_B</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool.high[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
@@ -4805,14 +4805,14 @@
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……受ける</t>
+          <t xml:space="preserve">…はい、わかりました。</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4822,29 +4822,29 @@
       </c>
       <c r="C141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…変わった</t>
+          <t xml:space="preserve">…ありがとうございます。受け取ります。</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4854,29 +4854,29 @@
       </c>
       <c r="C142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（——見えた）</t>
+          <t xml:space="preserve">…はい、わかりました。</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.quiet.cool[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4886,29 +4886,29 @@
       </c>
       <c r="C143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fresh.quiet.cool[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…体は軽い。…今日は、かなり…やれる</t>
+          <t xml:space="preserve">…ありがとうございます。…でも、少し、考えます。</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.quiet.cool[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4918,29 +4918,29 @@
       </c>
       <c r="C144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heavy.quiet.cool[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…重い。…やっても、抜けていくだけだ</t>
+          <t xml:space="preserve">…はい、わかりました。</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.quiet.cool[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4950,29 +4950,29 @@
       </c>
       <c r="C145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warm.quiet.cool[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…動けている。…ただ、深さがない</t>
+          <t xml:space="preserve">…ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.quiet.cool[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4982,29 +4982,29 @@
       </c>
       <c r="C146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.quiet.cool[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここまでだ</t>
+          <t xml:space="preserve">…はい、わかりました。</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.quiet.cool[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -5014,29 +5014,29 @@
       </c>
       <c r="C147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.quiet.cool[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ、止まらない</t>
+          <t xml:space="preserve">…ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.quiet.cool[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5046,29 +5046,29 @@
       </c>
       <c r="C148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.quiet.cool[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…実感はある</t>
+          <t xml:space="preserve">…申し訳ありません。…出ます。</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.quiet.cool[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5078,29 +5078,29 @@
       </c>
       <c r="C149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.quiet.cool[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この静けさが、答えだ</t>
+          <t xml:space="preserve">…ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.quiet.cool[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5110,29 +5110,29 @@
       </c>
       <c r="C150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.quiet.cool[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…背負っていく。この声を</t>
+          <t xml:space="preserve">…ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5142,29 +5142,29 @@
       </c>
       <c r="C151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……見えない</t>
+          <t xml:space="preserve">…ありがとうございます。…休みます。</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5174,29 +5174,29 @@
       </c>
       <c r="C152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…闘える</t>
+          <t xml:space="preserve">…はい、平気です。</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5206,29 +5206,29 @@
       </c>
       <c r="C153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……戻った</t>
+          <t xml:space="preserve">…ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.quiet.cool[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5238,29 +5238,29 @@
       </c>
       <c r="C154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.quiet.cool[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…動けない</t>
+          <t xml:space="preserve">…はい、わかりました。</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.quiet.cool[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5270,29 +5270,29 @@
       </c>
       <c r="C155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.quiet.cool[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……鈍い</t>
+          <t xml:space="preserve">…ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.quiet.cool[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5302,29 +5302,29 @@
       </c>
       <c r="C156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.quiet.cool[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…遠い</t>
+          <t xml:space="preserve">…ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.quiet.cool[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5334,29 +5334,29 @@
       </c>
       <c r="C157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.quiet.cool[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…心が、まだ</t>
+          <t xml:space="preserve">…はい、わかりました。</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.quiet.cool[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5366,29 +5366,29 @@
       </c>
       <c r="C158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.quiet.cool[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一生の試合だった</t>
+          <t xml:space="preserve">（…何も言わず、目を伏せた）</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.quiet.cool[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5398,29 +5398,29 @@
       </c>
       <c r="C159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.quiet.cool[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ降りない</t>
+          <t xml:space="preserve">…ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.quiet.cool[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5430,29 +5430,29 @@
       </c>
       <c r="C160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.quiet.cool[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悔いはない。…ありがとう</t>
+          <t xml:space="preserve">…はい、加減します。</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.quiet.cool[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5462,29 +5462,29 @@
       </c>
       <c r="C161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.quiet.cool[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…感謝します</t>
+          <t xml:space="preserve">…ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.quiet.cool[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5494,29 +5494,29 @@
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.quiet.cool[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…積み重ねの結果だ</t>
+          <t xml:space="preserve">…ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.quiet.cool[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.quiet.attack.cool</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5526,29 +5526,29 @@
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.quiet.cool[1]</t>
+          <t xml:space="preserve">quiet.attack.cool</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…次</t>
+          <t xml:space="preserve">……戻れない</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.quiet.defend.cool</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5558,381 +5558,381 @@
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">quiet.defend.cool</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…行きます</t>
+          <t xml:space="preserve">……望むなら</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.quiet.cool[2]</t>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[2]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ドームか。悪くない</t>
+          <t xml:space="preserve">……静かに、離れたい。</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.quiet.cool[3]</t>
+          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[3]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……(視線だけで応える)</t>
+          <t xml:space="preserve">……まあ、別にいいよ。</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">FACTION_F08_LEADER_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">FACTION_F08_LEADER_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…満員</t>
+          <t xml:space="preserve">……リングで、会う。</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.quiet.cool[2]</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.cool.quiet.hp_high[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[2]</t>
+          <t xml:space="preserve">cool.quiet.hp_high[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…忘れない</t>
+          <t xml:space="preserve">……負け。それだけ</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.quiet.cool[3]</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.cool.quiet.hp_mid[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[3]</t>
+          <t xml:space="preserve">cool.quiet.hp_mid[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……(遠くを見ている)</t>
+          <t xml:space="preserve">……っ……</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.quiet.cool[1]</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.cool.quiet.high[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.quiet.cool[1]</t>
+          <t xml:space="preserve">cool.quiet.high[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪くない。この調子で</t>
+          <t xml:space="preserve">……結果がすべて、だろ</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.quiet.cool[1]</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.cool.quiet.high[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.quiet.cool[1]</t>
+          <t xml:space="preserve">cool.quiet.high[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪くない仲間だ</t>
+          <t xml:space="preserve">……話すことは、もうない</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.quiet.cool[1]</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.cool.quiet.high[2]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.quiet.cool[1]</t>
+          <t xml:space="preserve">cool.quiet.high[2]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…大丈夫だ。すぐ戻れる</t>
+          <t xml:space="preserve">……決着、つけよう</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.quiet.cool[1]</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.cool.quiet.high[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.quiet.cool[1]</t>
+          <t xml:space="preserve">cool.quiet.high[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ファンの期待には応える</t>
+          <t xml:space="preserve">……いいだろう。受けて立つ</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.quiet.cool[1]</t>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A.cool.quiet.high[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.quiet.cool[1]</t>
+          <t xml:space="preserve">cool.quiet.high[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（静かに出口を見ている）</t>
+          <t xml:space="preserve">……話すことは、もう何もない</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.quiet.cool[1]</t>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_B.cool.quiet.high[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_B</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">breakthrough.voice.quiet.cool[1]</t>
+          <t xml:space="preserve">cool.quiet.high[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…環境に恵まれた。それは認める</t>
+          <t xml:space="preserve">……受ける</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.quiet.cool[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5942,29 +5942,29 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G2.voice.quiet.cool[1]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう。それだけのことだ</t>
+          <t xml:space="preserve">…変わった</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.quiet.cool[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5974,29 +5974,29 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">BT_HINT_LINES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.voice.quiet.cool[1]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…チャンスは自分で作るものだと思っている</t>
+          <t xml:space="preserve">（——見えた）</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.quiet.cool[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -6006,29 +6006,29 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R2.voice.quiet.cool[1]</t>
+          <t xml:space="preserve">fresh.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…孤独には慣れている</t>
+          <t xml:space="preserve">…体は軽い。…今日は、かなり…やれる</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.quiet.cool[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6038,29 +6038,29 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.modal.quiet.cool[1]</t>
+          <t xml:space="preserve">heavy.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうか。…分かった</t>
+          <t xml:space="preserve">…重い。…やっても、抜けていくだけだ</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.quiet.cool[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6070,29 +6070,29 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R4.voice.quiet.cool[1]</t>
+          <t xml:space="preserve">warm.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…次も同じ結果とは限らない。気を引き締めろ、自分</t>
+          <t xml:space="preserve">…動けている。…ただ、深さがない</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.quiet.cool[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6102,29 +6102,29 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.voice.quiet.cool[1]</t>
+          <t xml:space="preserve">cap_reached.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…敗因は分かっている。次までに修正する</t>
+          <t xml:space="preserve">…ここまでだ</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.quiet.cool[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6134,29 +6134,29 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warVictory.voice.quiet.cool[1]</t>
+          <t xml:space="preserve">ovr_elite.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…当然の結果だ</t>
+          <t xml:space="preserve">…まだ、止まらない</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.quiet.cool[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6166,29 +6166,29 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.quiet.cool[1]</t>
+          <t xml:space="preserve">ovr_growth.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがたい</t>
+          <t xml:space="preserve">…実感はある</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.quiet.cool[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6198,29 +6198,29 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.quiet.cool[1]</t>
+          <t xml:space="preserve">ovr_legend.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…追い込む</t>
+          <t xml:space="preserve">…この静けさが、答えだ</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.quiet.cool[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6230,29 +6230,29 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.quiet.cool[1]</t>
+          <t xml:space="preserve">pop_star.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…分かった。応える</t>
+          <t xml:space="preserve">…背負っていく。この声を</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.quiet.cool[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6262,29 +6262,29 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.quiet.cool[1]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……分かった</t>
+          <t xml:space="preserve">……見えない</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.quiet.cool[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6294,29 +6294,29 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.quiet.cool[1]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……やる</t>
+          <t xml:space="preserve">…闘える</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.quiet.cool[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6326,29 +6326,29 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.quiet.cool[1]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪くなかった</t>
+          <t xml:space="preserve">……戻った</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.quiet.cool[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6358,29 +6358,29 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.quiet.cool[1]</t>
+          <t xml:space="preserve">defeat.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…感謝する。少し休む</t>
+          <t xml:space="preserve">…動けない</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.quiet.cool[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6390,29 +6390,29 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.quiet.cool[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…感謝する。早く戻る</t>
+          <t xml:space="preserve">……鈍い</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.quiet.cool[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6422,29 +6422,29 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.quiet.cool[1]</t>
+          <t xml:space="preserve">injury_severe_recovery.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…吸収する。見ていてくれ</t>
+          <t xml:space="preserve">…遠い</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.quiet.cool[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6454,29 +6454,29 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.quiet.cool[1]</t>
+          <t xml:space="preserve">penalty_end.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……やる</t>
+          <t xml:space="preserve">…心が、まだ</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.quiet.cool[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6486,29 +6486,29 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.quiet.cool[1]</t>
+          <t xml:space="preserve">bestMatch.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…他所から来た。報告する</t>
+          <t xml:space="preserve">…一生の試合だった</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.quiet.cool[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6518,29 +6518,29 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.quiet.cool[1]</t>
+          <t xml:space="preserve">champion.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（静かにテーピングを外している）</t>
+          <t xml:space="preserve">…まだ降りない</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.quiet.cool[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6550,29 +6550,29 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.quiet.cool[1]</t>
+          <t xml:space="preserve">hallOfFame.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（無言のまま動かず、周囲だけが落ち着かなくなっている）</t>
+          <t xml:space="preserve">…悔いはない。…ありがとう</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.quiet.cool[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6582,29 +6582,29 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.quiet.cool[1]</t>
+          <t xml:space="preserve">mediaAward.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに点を三つ置いただけの投稿。ファンの憶測だけが広がっていく）</t>
+          <t xml:space="preserve">…感謝します</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.quiet.cool[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6614,29 +6614,29 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.quiet.cool[1]</t>
+          <t xml:space="preserve">mvp.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…タイトルマッチを。頼む</t>
+          <t xml:space="preserve">…積み重ねの結果だ</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.quiet.cool[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6646,29 +6646,29 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.quiet.cool[1]</t>
+          <t xml:space="preserve">rookie.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あいつとの試合を。頼む</t>
+          <t xml:space="preserve">…次</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.quiet.cool[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6678,29 +6678,29 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.quiet.cool[1]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…休む必要がある</t>
+          <t xml:space="preserve">…行きます</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.quiet.cool[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6710,29 +6710,29 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.quiet.cool[1]</t>
+          <t xml:space="preserve">cool.quiet[2]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もう、限界だ（静かに、しかし断固として）</t>
+          <t xml:space="preserve">…ドームか。悪くない</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.quiet.cool[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.cool.quiet[3]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6742,29 +6742,29 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.quiet.cool[1]</t>
+          <t xml:space="preserve">cool.quiet[3]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（何も言わず、立ち去ろうとする）</t>
+          <t xml:space="preserve">……(視線だけで応える)</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.quiet.cool[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6774,29 +6774,29 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.quiet.cool[1]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…鍛えたい。場所を貸してくれ</t>
+          <t xml:space="preserve">…満員</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.quiet.cool[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6806,29 +6806,29 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.quiet.cool[1]</t>
+          <t xml:space="preserve">cool.quiet[2]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…次の世代に、繋ぎたいものがある</t>
+          <t xml:space="preserve">…忘れない</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.quiet.cool[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.cool.quiet[3]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6838,29 +6838,29 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.quiet.cool[1]</t>
+          <t xml:space="preserve">cool.quiet[3]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…すぐ戻る</t>
+          <t xml:space="preserve">……(遠くを見ている)</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.quiet.cool[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6870,29 +6870,29 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.quiet.cool[1]</t>
+          <t xml:space="preserve">N1.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あれとは合わない。それだけだ</t>
+          <t xml:space="preserve">…悪くない。この調子で</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.quiet.cool[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6902,29 +6902,29 @@
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.quiet.cool[1]</t>
+          <t xml:space="preserve">N2.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…私は間違っていない</t>
+          <t xml:space="preserve">…悪くない仲間だ</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.quiet.cool[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6934,29 +6934,29 @@
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.quiet.cool[1]</t>
+          <t xml:space="preserve">N3.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…無駄口は叩かない。それがブランドには向いているかもな</t>
+          <t xml:space="preserve">…大丈夫だ。すぐ戻れる</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.quiet.cool[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6966,29 +6966,29 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.quiet.cool[1]</t>
+          <t xml:space="preserve">N4.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…カメラか。まぁ、やる</t>
+          <t xml:space="preserve">…ファンの期待には応える</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.quiet.cool[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6998,29 +6998,29 @@
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.quiet.cool[1]</t>
+          <t xml:space="preserve">N5_low.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…来てくれた人には、ちゃんと応えたい</t>
+          <t xml:space="preserve">……（静かに出口を見ている）</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.quiet.cool[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7030,29 +7030,29 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.quiet.cool[1]</t>
+          <t xml:space="preserve">breakthrough.voice.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…余計なことはしない。ただ歩く。それだけだ</t>
+          <t xml:space="preserve">…環境に恵まれた。それは認める</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.quiet.cool[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7062,29 +7062,29 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.quiet.cool[1]</t>
+          <t xml:space="preserve">G2.voice.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…写真か。余計なことはしないでくれ</t>
+          <t xml:space="preserve">…そう。それだけのことだ</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.quiet.cool[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7094,29 +7094,29 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.quiet.cool[1]</t>
+          <t xml:space="preserve">G3.voice.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…無駄なことは言わない。それだけだ</t>
+          <t xml:space="preserve">…チャンスは自分で作るものだと思っている</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.quiet.cool[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7126,29 +7126,29 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.quiet.cool[1]</t>
+          <t xml:space="preserve">R2.voice.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やる。見ていてくれ</t>
+          <t xml:space="preserve">…孤独には慣れている</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7158,29 +7158,29 @@
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">R3.modal.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…戦わせてくれるなら、応える</t>
+          <t xml:space="preserve">…そうか。…分かった</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7190,29 +7190,29 @@
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">R4.voice.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……よろしく</t>
+          <t xml:space="preserve">…次も同じ結果とは限らない。気を引き締めろ、自分</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.quiet.cool[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7222,29 +7222,29 @@
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[2]</t>
+          <t xml:space="preserve">R5.voice.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……始めよう</t>
+          <t xml:space="preserve">…敗因は分かっている。次までに修正する</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7254,29 +7254,29 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">warVictory.voice.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やる。見ていてくれ</t>
+          <t xml:space="preserve">…当然の結果だ</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7286,29 +7286,29 @@
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">bonus.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やるべきことをやる</t>
+          <t xml:space="preserve">…ありがたい</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.quiet.cool[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7318,29 +7318,29 @@
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[2]</t>
+          <t xml:space="preserve">camp.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……すぐ戻る</t>
+          <t xml:space="preserve">…追い込む</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.quiet.cool[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7350,29 +7350,29 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.quiet.cool[1]</t>
+          <t xml:space="preserve">encourage_high_trust.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……終わった。それだけだ。……それだけのはずだ</t>
+          <t xml:space="preserve">…分かった。応える</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.quiet.cool[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7382,29 +7382,29 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.quiet.cool[1]</t>
+          <t xml:space="preserve">encourage.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……終わっていない。……私の中では</t>
+          <t xml:space="preserve">……分かった</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.quiet.cool[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7414,29 +7414,29 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.quiet.cool[1]</t>
+          <t xml:space="preserve">media.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…戦わせてくれるなら、応える</t>
+          <t xml:space="preserve">……やる</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.quiet.cool[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7446,29 +7446,29 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.quiet.cool[1]</t>
+          <t xml:space="preserve">party.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……よろしく</t>
+          <t xml:space="preserve">…悪くなかった</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.quiet.cool[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7478,29 +7478,29 @@
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.quiet.cool[2]</t>
+          <t xml:space="preserve">refresh_leave.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……始めよう</t>
+          <t xml:space="preserve">…感謝する。少し休む</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.quiet.cool[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7510,29 +7510,29 @@
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.quiet.cool[1]</t>
+          <t xml:space="preserve">special_treatment.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…拾われた。…なら、恩を返す</t>
+          <t xml:space="preserve">…感謝する。早く戻る</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.quiet.cool[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7542,29 +7542,29 @@
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.quiet.cool[1]</t>
+          <t xml:space="preserve">trainer.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やる。見ていてくれ</t>
+          <t xml:space="preserve">…吸収する。見ていてくれ</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.quiet.cool[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7574,29 +7574,29 @@
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.quiet.cool[1]</t>
+          <t xml:space="preserve">E1.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やるべきことをやる</t>
+          <t xml:space="preserve">……やる</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.quiet.cool[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7606,29 +7606,29 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.fresh.quiet.cool[1]</t>
+          <t xml:space="preserve">E6.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…体は軽い。…今日は、かなり…やれる</t>
+          <t xml:space="preserve">…他所から来た。報告する</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.quiet.cool[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7638,29 +7638,29 @@
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.heavy.quiet.cool[1]</t>
+          <t xml:space="preserve">S_boycott.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…重い。…やっても、抜けていくだけだ</t>
+          <t xml:space="preserve">………（静かにテーピングを外している）</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.quiet.cool[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7670,29 +7670,29 @@
       </c>
       <c r="C230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.warm.quiet.cool[1]</t>
+          <t xml:space="preserve">S_grumble.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…動けている。…ただ、深さがない</t>
+          <t xml:space="preserve">（無言のまま動かず、周囲だけが落ち着かなくなっている）</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.quiet.cool[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7702,29 +7702,29 @@
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.quiet.cool[2]</t>
+          <t xml:space="preserve">S_sns.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……すぐ戻る</t>
+          <t xml:space="preserve">（SNSに点を三つ置いただけの投稿。ファンの憶測だけが広がっていく）</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.quiet.cool[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7734,29 +7734,29 @@
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.quiet.cool[1]</t>
+          <t xml:space="preserve">S1.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……(静かに立ち去る)</t>
+          <t xml:space="preserve">…タイトルマッチを。頼む</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.quiet.cool[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7766,29 +7766,29 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.quiet.cool[2]</t>
+          <t xml:space="preserve">S2.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ありがとう</t>
+          <t xml:space="preserve">…あいつとの試合を。頼む</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.quiet.cool[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7798,29 +7798,29 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.quiet.cool[1]</t>
+          <t xml:space="preserve">S3.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やるべきことはやる</t>
+          <t xml:space="preserve">…休む必要がある</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.quiet.cool[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7830,29 +7830,29 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.quiet.cool[1]</t>
+          <t xml:space="preserve">S4_direct.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…期待には、応える</t>
+          <t xml:space="preserve">……もう、限界だ（静かに、しかし断固として）</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.quiet.cool[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7862,29 +7862,29 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.quiet.cool[1]</t>
+          <t xml:space="preserve">S4_silent.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…次で終わらせる</t>
+          <t xml:space="preserve">……（何も言わず、立ち去ろうとする）</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.quiet.cool[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7894,29 +7894,29 @@
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.quiet.cool[1]</t>
+          <t xml:space="preserve">S5.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…次も勝つ。それだけだ</t>
+          <t xml:space="preserve">…鍛えたい。場所を貸してくれ</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.quiet.cool[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7926,29 +7926,29 @@
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.quiet.cool[1]</t>
+          <t xml:space="preserve">S6.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…認めよう。だが、終わりではない</t>
+          <t xml:space="preserve">…次の世代に、繋ぎたいものがある</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.quiet.cool[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7958,29 +7958,29 @@
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.quiet.cool[1]</t>
+          <t xml:space="preserve">B1.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ようやくだ。この座は渡さない</t>
+          <t xml:space="preserve">…すぐ戻る</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7990,29 +7990,29 @@
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">B2_fighter1.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……(静かに立ち去る)</t>
+          <t xml:space="preserve">…あれとは合わない。それだけだ</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.quiet.cool[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8022,29 +8022,29 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[2]</t>
+          <t xml:space="preserve">B2_fighter2.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ありがとう</t>
+          <t xml:space="preserve">…私は間違っていない</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8054,29 +8054,29 @@
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">B4_brand.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やるべきことはやる</t>
+          <t xml:space="preserve">…無駄口は叩かない。それがブランドには向いているかもな</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8086,29 +8086,29 @@
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">B4_cm.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…次で終わらせる</t>
+          <t xml:space="preserve">…カメラか。まぁ、やる</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8118,29 +8118,29 @@
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">B4_fan.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…次も勝つ。それだけだ</t>
+          <t xml:space="preserve">…来てくれた人には、ちゃんと応えたい</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8150,29 +8150,29 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">B4_fashion.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…認めよう。だが、終わりではない</t>
+          <t xml:space="preserve">…余計なことはしない。ただ歩く。それだけだ</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8182,29 +8182,29 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">B4_gravure.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ようやくだ。この座は渡さない</t>
+          <t xml:space="preserve">…写真か。余計なことはしないでくれ</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.quiet.cool[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8214,29 +8214,29 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.quiet.cool[1]</t>
+          <t xml:space="preserve">B4_variety.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……終わりだ</t>
+          <t xml:space="preserve">…無駄なことは言わない。それだけだ</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.quiet.cool[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8246,29 +8246,29 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.quiet.cool[1]</t>
+          <t xml:space="preserve">B4.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……遠い</t>
+          <t xml:space="preserve">…やる。見ていてくれ</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.quiet.cool[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8278,29 +8278,29 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.quiet.cool[2]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もう、隣にいない</t>
+          <t xml:space="preserve">…戦わせてくれるなら、応える</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.quiet.cool[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8310,29 +8310,29 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.quiet.cool[1]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……悪くない距離感だ</t>
+          <t xml:space="preserve">……よろしく</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.quiet.cool[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8342,29 +8342,29 @@
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.quiet.cool[1]</t>
+          <t xml:space="preserve">cool.quiet[2]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……この人だけは、信じられる</t>
+          <t xml:space="preserve">……始めよう</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.quiet.cool[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8374,29 +8374,29 @@
       </c>
       <c r="C252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.quiet.cool[1]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もう考えない</t>
+          <t xml:space="preserve">…やる。見ていてくれ</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.quiet.cool[2]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8406,29 +8406,29 @@
       </c>
       <c r="C253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.quiet.cool[2]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……風が止んだ</t>
+          <t xml:space="preserve">…やるべきことをやる</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.quiet.cool[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8438,29 +8438,29 @@
       </c>
       <c r="C254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.quiet.cool[1]</t>
+          <t xml:space="preserve">cool.quiet[2]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……気になる。ただ、それだけだが</t>
+          <t xml:space="preserve">……すぐ戻る</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.quiet.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8470,29 +8470,29 @@
       </c>
       <c r="C255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.quiet.cool[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……超えなければ、先へ進めない</t>
+          <t xml:space="preserve">……終わった。それだけだ。……それだけのはずだ</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.quiet.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8502,29 +8502,29 @@
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.quiet.cool[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……あの相手がいる限り、立ち続ける</t>
+          <t xml:space="preserve">……終わっていない。……私の中では</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.quiet.cool[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8534,29 +8534,29 @@
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.quiet.cool[2]</t>
+          <t xml:space="preserve">draftInterest.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……言葉はいらない。リングで話す</t>
+          <t xml:space="preserve">…戦わせてくれるなら、応える</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.quiet.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8566,29 +8566,29 @@
       </c>
       <c r="C258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.quiet.cool[1]</t>
+          <t xml:space="preserve">draftJoin.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ここにいたい</t>
+          <t xml:space="preserve">……よろしく</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.quiet.cool[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8598,29 +8598,29 @@
       </c>
       <c r="C259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.quiet.cool[2]</t>
+          <t xml:space="preserve">draftJoin.cool.quiet[2]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……この場所を守る</t>
+          <t xml:space="preserve">……始めよう</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.quiet.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8630,29 +8630,29 @@
       </c>
       <c r="C260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.quiet.cool[1]</t>
+          <t xml:space="preserve">faGreeting.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（荷物をまとめている）</t>
+          <t xml:space="preserve">…拾われた。…なら、恩を返す</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.quiet.cool[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8662,29 +8662,29 @@
       </c>
       <c r="C261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.quiet.cool[2]</t>
+          <t xml:space="preserve">faSigning.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……何も、残っていない</t>
+          <t xml:space="preserve">…やる。見ていてくれ</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.quiet.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8694,29 +8694,29 @@
       </c>
       <c r="C262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.quiet.cool[1]</t>
+          <t xml:space="preserve">faWelcome.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……この場所に、未来はあるのか</t>
+          <t xml:space="preserve">…やるべきことをやる</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8726,29 +8726,29 @@
       </c>
       <c r="C263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">heatSelf.fresh.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……調子は落ち着いた。だが後退じゃない</t>
+          <t xml:space="preserve">…体は軽い。…今日は、かなり…やれる</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.quiet.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8758,29 +8758,29 @@
       </c>
       <c r="C264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.quiet.cool[1]</t>
+          <t xml:space="preserve">heatSelf.heavy.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……最後。立てる。十分</t>
+          <t xml:space="preserve">…重い。…やっても、抜けていくだけだ</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.quiet.cool[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8790,29 +8790,29 @@
       </c>
       <c r="C265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.quiet.cool[2]</t>
+          <t xml:space="preserve">heatSelf.warm.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……傷は数えない。ただ、いく</t>
+          <t xml:space="preserve">…動けている。…ただ、深さがない</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.quiet.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8822,29 +8822,29 @@
       </c>
       <c r="C266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.quiet.cool[1]</t>
+          <t xml:space="preserve">injury.cool.quiet[2]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次</t>
+          <t xml:space="preserve">……すぐ戻る</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.quiet.cool[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8854,29 +8854,29 @@
       </c>
       <c r="C267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.quiet.cool[2]</t>
+          <t xml:space="preserve">release.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……倒す。残る</t>
+          <t xml:space="preserve">……(静かに立ち去る)</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.quiet.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8886,29 +8886,29 @@
       </c>
       <c r="C268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.quiet.cool[1]</t>
+          <t xml:space="preserve">release.cool.quiet[2]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……一人。まだ立ってる。次</t>
+          <t xml:space="preserve">……ありがとう</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.quiet.cool[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8918,29 +8918,29 @@
       </c>
       <c r="C269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.quiet.cool[2]</t>
+          <t xml:space="preserve">rentalGreeting.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……退かない。出せ</t>
+          <t xml:space="preserve">…やるべきことはやる</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.quiet.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8950,29 +8950,29 @@
       </c>
       <c r="C270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.quiet.cool[1]</t>
+          <t xml:space="preserve">scoutGreeting.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……三人の結果。言葉は要らない</t>
+          <t xml:space="preserve">…期待には、応える</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.quiet.cool[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8982,29 +8982,29 @@
       </c>
       <c r="C271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.quiet.cool[2]</t>
+          <t xml:space="preserve">titleChallengeLoss.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……一人では不可能だった。それは認める</t>
+          <t xml:space="preserve">…次で終わらせる</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.quiet.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -9014,29 +9014,29 @@
       </c>
       <c r="C272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.quiet.cool[1]</t>
+          <t xml:space="preserve">titleDefense.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……不十分だった。次がある</t>
+          <t xml:space="preserve">…次も勝つ。それだけだ</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.quiet.cool[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9046,29 +9046,29 @@
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.quiet.cool[2]</t>
+          <t xml:space="preserve">titleLoss.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……団体が負けた。それが全て。次に期す</t>
+          <t xml:space="preserve">…認めよう。だが、終わりではない</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.quiet.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9078,29 +9078,29 @@
       </c>
       <c r="C274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.quiet.cool[1]</t>
+          <t xml:space="preserve">titleWin.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……立っている。それが結果</t>
+          <t xml:space="preserve">…ようやくだ。この座は渡さない</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.quiet.cool[2]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9110,29 +9110,29 @@
       </c>
       <c r="C275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.quiet.cool[2]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……数えてない。ただ、倒れなかった</t>
+          <t xml:space="preserve">……(静かに立ち去る)</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.quiet.cool[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9142,29 +9142,29 @@
       </c>
       <c r="C276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.quiet.cool[1]</t>
+          <t xml:space="preserve">cool.quiet[2]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（トロフィーを静かに掲げる）</t>
+          <t xml:space="preserve">……ありがとう</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.quiet.cool[2]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9174,29 +9174,29 @@
       </c>
       <c r="C277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.quiet.cool[2]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…………ありがとう</t>
+          <t xml:space="preserve">…やるべきことはやる</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.quiet.cool[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9206,29 +9206,29 @@
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.quiet.cool[1]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（無言で去る）</t>
+          <t xml:space="preserve">…次で終わらせる</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.quiet.cool[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9238,29 +9238,29 @@
       </c>
       <c r="C279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.quiet.cool[1]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（静かに頷く）</t>
+          <t xml:space="preserve">…次も勝つ。それだけだ</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.quiet.cool[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9270,29 +9270,29 @@
       </c>
       <c r="C280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.quiet.cool[2]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まだ</t>
+          <t xml:space="preserve">…認めよう。だが、終わりではない</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.quiet.cool[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9302,29 +9302,29 @@
       </c>
       <c r="C281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.quiet.cool[2]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（少し笑顔を見せる）</t>
+          <t xml:space="preserve">…ようやくだ。この座は渡さない</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.quiet.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9334,29 +9334,29 @@
       </c>
       <c r="C282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.quiet.cool[1]</t>
+          <t xml:space="preserve">bond_39_down.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……最後</t>
+          <t xml:space="preserve">……終わりだ</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.quiet.cool[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9366,29 +9366,29 @@
       </c>
       <c r="C283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.quiet.cool[2]</t>
+          <t xml:space="preserve">bond_59_down.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……全部、出す</t>
+          <t xml:space="preserve">……遠い</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.quiet.cool[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.quiet.cool[2]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9398,29 +9398,29 @@
       </c>
       <c r="C284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.quiet.cool[2]</t>
+          <t xml:space="preserve">bond_59_down.quiet.cool[2]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（拳を握る）</t>
+          <t xml:space="preserve">……もう、隣にいない</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.quiet.cool[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9430,29 +9430,29 @@
       </c>
       <c r="C285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.quiet.cool[2]</t>
+          <t xml:space="preserve">bond_60_up.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（静かに頷く）</t>
+          <t xml:space="preserve">……悪くない距離感だ</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9462,29 +9462,29 @@
       </c>
       <c r="C286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">bond_80_up.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…結果で語る</t>
+          <t xml:space="preserve">……この人だけは、信じられる</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9494,29 +9494,29 @@
       </c>
       <c r="C287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">rivalry_29_down.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（ベルトを静かに抱きしめる）</t>
+          <t xml:space="preserve">……もう考えない</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.quiet.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.quiet.cool[2]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9526,29 +9526,29 @@
       </c>
       <c r="C288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">rivalry_29_down.quiet.cool[2]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……来い</t>
+          <t xml:space="preserve">……風が止んだ</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.quiet.cool[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9558,29 +9558,29 @@
       </c>
       <c r="C289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[2]</t>
+          <t xml:space="preserve">rivalry_30_up.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（背を向ける）</t>
+          <t xml:space="preserve">……気になる。ただ、それだけだが</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.quiet.cool[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9590,29 +9590,29 @@
       </c>
       <c r="C290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.quiet.cool[2]</t>
+          <t xml:space="preserve">rivalry_50_up.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（拳を握りしめる）</t>
+          <t xml:space="preserve">……超えなければ、先へ進めない</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.quiet.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9622,29 +9622,29 @@
       </c>
       <c r="C291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.quiet.cool[1]</t>
+          <t xml:space="preserve">rivalry_70_up.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（静かに頷く）</t>
+          <t xml:space="preserve">……あの相手がいる限り、立ち続ける</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.quiet.cool[2]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9654,29 +9654,29 @@
       </c>
       <c r="C292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">rivalry_70_up.quiet.cool[2]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……証明した。それだけ</t>
+          <t xml:space="preserve">……言葉はいらない。リングで話す</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.quiet.cool[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9686,29 +9686,29 @@
       </c>
       <c r="C293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[2]</t>
+          <t xml:space="preserve">trust_above_75.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……これがうちの力</t>
+          <t xml:space="preserve">……ここにいたい</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.quiet.cool[3]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.quiet.cool[2]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9718,29 +9718,29 @@
       </c>
       <c r="C294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[3]</t>
+          <t xml:space="preserve">trust_above_75.quiet.cool[2]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（静かに頷く）</t>
+          <t xml:space="preserve">……この場所を守る</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.quiet.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9750,29 +9750,29 @@
       </c>
       <c r="C295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.quiet.cool[1]</t>
+          <t xml:space="preserve">trust_below_20.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここまで来たか</t>
+          <t xml:space="preserve">……（荷物をまとめている）</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.quiet.cool[2]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9782,29 +9782,29 @@
       </c>
       <c r="C296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
+          <t xml:space="preserve">trust_below_20.quiet.cool[2]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…拾われた。…なら、恩を返す</t>
+          <t xml:space="preserve">……何も、残っていない</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.quiet.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9814,27 +9814,1147 @@
       </c>
       <c r="C297" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_below_35.quiet.cool[1]</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……この場所に、未来はあるのか</t>
+        </is>
+      </c>
+    </row>
+    <row r="298" ht="40" customHeight="1">
+      <c r="A298" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.cool.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">cool.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……調子は落ち着いた。だが後退じゃない</t>
+        </is>
+      </c>
+    </row>
+    <row r="299" ht="40" customHeight="1">
+      <c r="A299" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.cool.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.cool.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……最後。立てる。十分</t>
+        </is>
+      </c>
+    </row>
+    <row r="300" ht="40" customHeight="1">
+      <c r="A300" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.cool.quiet[2]</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.cool.quiet[2]</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……傷は数えない。ただ、いく</t>
+        </is>
+      </c>
+    </row>
+    <row r="301" ht="40" customHeight="1">
+      <c r="A301" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.cool.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.cool.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……次</t>
+        </is>
+      </c>
+    </row>
+    <row r="302" ht="40" customHeight="1">
+      <c r="A302" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.cool.quiet[2]</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.cool.quiet[2]</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……倒す。残る</t>
+        </is>
+      </c>
+    </row>
+    <row r="303" ht="40" customHeight="1">
+      <c r="A303" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.cool.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">survivor.cool.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……一人。まだ立ってる。次</t>
+        </is>
+      </c>
+    </row>
+    <row r="304" ht="40" customHeight="1">
+      <c r="A304" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.cool.quiet[2]</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">survivor.cool.quiet[2]</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……退かない。出せ</t>
+        </is>
+      </c>
+    </row>
+    <row r="305" ht="40" customHeight="1">
+      <c r="A305" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.cool.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.cool.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……三人の結果。言葉は要らない</t>
+        </is>
+      </c>
+    </row>
+    <row r="306" ht="40" customHeight="1">
+      <c r="A306" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.cool.quiet[2]</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.cool.quiet[2]</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……一人では不可能だった。それは認める</t>
+        </is>
+      </c>
+    </row>
+    <row r="307" ht="40" customHeight="1">
+      <c r="A307" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.cool.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">defiant.cool.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……不十分だった。次がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="308" ht="40" customHeight="1">
+      <c r="A308" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.cool.quiet[2]</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">defiant.cool.quiet[2]</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……団体が負けた。それが全て。次に期す</t>
+        </is>
+      </c>
+    </row>
+    <row r="309" ht="40" customHeight="1">
+      <c r="A309" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.cool.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.cool.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……立っている。それが結果</t>
+        </is>
+      </c>
+    </row>
+    <row r="310" ht="40" customHeight="1">
+      <c r="A310" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.cool.quiet[2]</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.cool.quiet[2]</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……数えてない。ただ、倒れなかった</t>
+        </is>
+      </c>
+    </row>
+    <row r="311" ht="40" customHeight="1">
+      <c r="A311" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.cool.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.cool.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……（トロフィーを静かに掲げる）</t>
+        </is>
+      </c>
+    </row>
+    <row r="312" ht="40" customHeight="1">
+      <c r="A312" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.cool.quiet[2]</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.cool.quiet[2]</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…………ありがとう</t>
+        </is>
+      </c>
+    </row>
+    <row r="313" ht="40" customHeight="1">
+      <c r="A313" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.cool.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postLose.cool.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……（無言で去る）</t>
+        </is>
+      </c>
+    </row>
+    <row r="314" ht="40" customHeight="1">
+      <c r="A314" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.cool.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postMatchWin.cool.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……（静かに頷く）</t>
+        </is>
+      </c>
+    </row>
+    <row r="315" ht="40" customHeight="1">
+      <c r="A315" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.cool.quiet[2]</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postMatchWin.cool.quiet[2]</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……まだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="316" ht="40" customHeight="1">
+      <c r="A316" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.cool.quiet[2]</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postWin.cool.quiet[2]</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……（少し笑顔を見せる）</t>
+        </is>
+      </c>
+    </row>
+    <row r="317" ht="40" customHeight="1">
+      <c r="A317" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.cool.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.cool.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……最後</t>
+        </is>
+      </c>
+    </row>
+    <row r="318" ht="40" customHeight="1">
+      <c r="A318" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.cool.quiet[2]</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.cool.quiet[2]</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……全部、出す</t>
+        </is>
+      </c>
+    </row>
+    <row r="319" ht="40" customHeight="1">
+      <c r="A319" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.cool.quiet[2]</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.cool.quiet[2]</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……（拳を握る）</t>
+        </is>
+      </c>
+    </row>
+    <row r="320" ht="40" customHeight="1">
+      <c r="A320" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.cool.quiet[2]</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">summon.cool.quiet[2]</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……（静かに頷く）</t>
+        </is>
+      </c>
+    </row>
+    <row r="321" ht="40" customHeight="1">
+      <c r="A321" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.cool.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">cool.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…結果で語る</t>
+        </is>
+      </c>
+    </row>
+    <row r="322" ht="40" customHeight="1">
+      <c r="A322" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.cool.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">cool.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">………（ベルトを静かに抱きしめる）</t>
+        </is>
+      </c>
+    </row>
+    <row r="323" ht="40" customHeight="1">
+      <c r="A323" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.cool.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">cool.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……来い</t>
+        </is>
+      </c>
+    </row>
+    <row r="324" ht="40" customHeight="1">
+      <c r="A324" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.cool.quiet[2]</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">cool.quiet[2]</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……（背を向ける）</t>
+        </is>
+      </c>
+    </row>
+    <row r="325" ht="40" customHeight="1">
+      <c r="A325" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.cool.quiet[2]</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_lose.cool.quiet[2]</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……（拳を握りしめる）</t>
+        </is>
+      </c>
+    </row>
+    <row r="326" ht="40" customHeight="1">
+      <c r="A326" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.cool.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.cool.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……（静かに頷く）</t>
+        </is>
+      </c>
+    </row>
+    <row r="327" ht="40" customHeight="1">
+      <c r="A327" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.cool.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">cool.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……証明した。それだけ</t>
+        </is>
+      </c>
+    </row>
+    <row r="328" ht="40" customHeight="1">
+      <c r="A328" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.cool.quiet[2]</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">cool.quiet[2]</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……これがうちの力</t>
+        </is>
+      </c>
+    </row>
+    <row r="329" ht="40" customHeight="1">
+      <c r="A329" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.cool.quiet[3]</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">cool.quiet[3]</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……（静かに頷く）</t>
+        </is>
+      </c>
+    </row>
+    <row r="330" ht="40" customHeight="1">
+      <c r="A330" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.cool.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.cool.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ここまで来たか</t>
+        </is>
+      </c>
+    </row>
+    <row r="331" ht="40" customHeight="1">
+      <c r="A331" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.cool.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">cool.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…拾われた。…なら、恩を返す</t>
+        </is>
+      </c>
+    </row>
+    <row r="332" ht="40" customHeight="1">
+      <c r="A332" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.cool.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D297" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">quiet.cool[1]</t>
-        </is>
-      </c>
-      <c r="E297" t="inlineStr" s="2">
+      <c r="D332" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">cool.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F297" t="inlineStr" s="3">
+      <c r="F332" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…期待には、応える</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H297"/>
+  <autoFilter ref="A1:H332"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/クール×寡黙.xlsx
+++ b/セリフ編集/キャラタイプ別/クール×寡黙.xlsx
@@ -306,7 +306,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H332"/>
+  <dimension ref="A1:H334"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -485,7 +485,7 @@
       </c>
       <c r="F5" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……見ててて</t>
+          <t xml:space="preserve">……見てて</t>
         </is>
       </c>
     </row>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="F37" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……悔しい。{partner}にも。</t>
+          <t xml:space="preserve">……{partner}に、勝ち星を渡せなかった。……次</t>
         </is>
       </c>
     </row>
@@ -3621,7 +3621,7 @@
       </c>
       <c r="F103" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…じゃあな</t>
+          <t xml:space="preserve">…じゃあ</t>
         </is>
       </c>
     </row>
@@ -5765,7 +5765,7 @@
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……結果がすべて、だろ</t>
+          <t xml:space="preserve">……結果がすべて、だ</t>
         </is>
       </c>
     </row>
@@ -6476,7 +6476,7 @@
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.cool.quiet[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.cool.quiet[1]</t>
+          <t xml:space="preserve">autumnWarChampion.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6501,14 +6501,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一生の試合だった</t>
+          <t xml:space="preserve">全員の勝利だ。</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.cool.quiet[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6523,7 +6523,7 @@
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.cool.quiet[1]</t>
+          <t xml:space="preserve">bestMatch.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6533,14 +6533,14 @@
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ降りない</t>
+          <t xml:space="preserve">…一生の試合だった</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.cool.quiet[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6555,7 +6555,7 @@
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.cool.quiet[1]</t>
+          <t xml:space="preserve">champion.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6565,14 +6565,14 @@
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悔いはない。…ありがとう</t>
+          <t xml:space="preserve">…まだ降りない</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.cool.quiet[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6587,7 +6587,7 @@
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.cool.quiet[1]</t>
+          <t xml:space="preserve">hallOfFame.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6597,14 +6597,14 @@
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…感謝します</t>
+          <t xml:space="preserve">…悔いはない。…ありがとう</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.cool.quiet[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.cool.quiet[1]</t>
+          <t xml:space="preserve">mediaAward.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6629,14 +6629,14 @@
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…積み重ねの結果だ</t>
+          <t xml:space="preserve">…感謝します</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.cool.quiet[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.cool.quiet[1]</t>
+          <t xml:space="preserve">mvp.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6661,14 +6661,14 @@
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…次</t>
+          <t xml:space="preserve">…積み重ねの結果だ</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.cool.quiet[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6678,12 +6678,12 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[1]</t>
+          <t xml:space="preserve">rookie.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6693,14 +6693,14 @@
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…行きます</t>
+          <t xml:space="preserve">…次</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.cool.quiet[2]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6710,12 +6710,12 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[2]</t>
+          <t xml:space="preserve">springTagChampion.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6725,14 +6725,14 @@
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ドームか。悪くない</t>
+          <t xml:space="preserve">相棒のおかげだ。</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.cool.quiet[3]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[3]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6757,14 +6757,14 @@
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……(視線だけで応える)</t>
+          <t xml:space="preserve">…行きます</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.cool.quiet[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[1]</t>
+          <t xml:space="preserve">cool.quiet[2]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6789,14 +6789,14 @@
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…満員</t>
+          <t xml:space="preserve">…ドームか。悪くない</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.cool.quiet[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.cool.quiet[3]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6806,12 +6806,12 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[2]</t>
+          <t xml:space="preserve">cool.quiet[3]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6821,14 +6821,14 @@
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…忘れない</t>
+          <t xml:space="preserve">……（視線だけで応える）</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.cool.quiet[3]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6843,7 +6843,7 @@
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[3]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6853,14 +6853,14 @@
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……(遠くを見ている)</t>
+          <t xml:space="preserve">…満員</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.cool.quiet[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6870,29 +6870,29 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.cool.quiet[1]</t>
+          <t xml:space="preserve">cool.quiet[2]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪くない。この調子で</t>
+          <t xml:space="preserve">…忘れない</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.cool.quiet[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.cool.quiet[3]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6902,29 +6902,29 @@
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.cool.quiet[1]</t>
+          <t xml:space="preserve">cool.quiet[3]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪くない仲間だ</t>
+          <t xml:space="preserve">……（遠くを見ている）</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.cool.quiet[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.cool.quiet[1]</t>
+          <t xml:space="preserve">N1.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6949,14 +6949,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…大丈夫だ。すぐ戻れる</t>
+          <t xml:space="preserve">…悪くない。この調子で</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.cool.quiet[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.cool.quiet[1]</t>
+          <t xml:space="preserve">N2.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -6981,14 +6981,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ファンの期待には応える</t>
+          <t xml:space="preserve">…悪くない仲間だ</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.cool.quiet[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.cool.quiet[1]</t>
+          <t xml:space="preserve">N3.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -7013,14 +7013,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（静かに出口を見ている）</t>
+          <t xml:space="preserve">…大丈夫だ。すぐ戻れる</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.cool.quiet[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7030,12 +7030,12 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">breakthrough.voice.cool.quiet[1]</t>
+          <t xml:space="preserve">N4.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7045,14 +7045,14 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…環境に恵まれた。それは認める</t>
+          <t xml:space="preserve">…ファンの期待には応える</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.cool.quiet[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7062,12 +7062,12 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G2.voice.cool.quiet[1]</t>
+          <t xml:space="preserve">N5_low.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7077,14 +7077,14 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう。それだけのことだ</t>
+          <t xml:space="preserve">……（静かに出口を見ている）</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.cool.quiet[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7099,7 +7099,7 @@
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.voice.cool.quiet[1]</t>
+          <t xml:space="preserve">breakthrough.voice.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7109,14 +7109,14 @@
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…チャンスは自分で作るものだと思っている</t>
+          <t xml:space="preserve">…環境に恵まれた。それは認める</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.cool.quiet[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7131,7 +7131,7 @@
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R2.voice.cool.quiet[1]</t>
+          <t xml:space="preserve">G2.voice.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7141,14 +7141,14 @@
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…孤独には慣れている</t>
+          <t xml:space="preserve">…そう。それだけのことだ</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.cool.quiet[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7163,7 +7163,7 @@
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.modal.cool.quiet[1]</t>
+          <t xml:space="preserve">G3.voice.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7173,14 +7173,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうか。…分かった</t>
+          <t xml:space="preserve">…チャンスは自分で作るものだと思っている</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.cool.quiet[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7195,7 +7195,7 @@
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R4.voice.cool.quiet[1]</t>
+          <t xml:space="preserve">R2.voice.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7205,14 +7205,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…次も同じ結果とは限らない。気を引き締めろ、自分</t>
+          <t xml:space="preserve">…孤独には慣れている</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.cool.quiet[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7227,7 +7227,7 @@
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.voice.cool.quiet[1]</t>
+          <t xml:space="preserve">R3.modal.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7237,14 +7237,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…敗因は分かっている。次までに修正する</t>
+          <t xml:space="preserve">…そうか。…分かった</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.cool.quiet[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warVictory.voice.cool.quiet[1]</t>
+          <t xml:space="preserve">R4.voice.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7269,14 +7269,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…当然の結果だ</t>
+          <t xml:space="preserve">…次も同じ結果とは限らない。気を引き締めろ、自分</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.cool.quiet[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7286,29 +7286,29 @@
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.cool.quiet[1]</t>
+          <t xml:space="preserve">R5.voice.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがたい</t>
+          <t xml:space="preserve">…敗因は分かっている。次までに修正する</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.cool.quiet[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7318,29 +7318,29 @@
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.cool.quiet[1]</t>
+          <t xml:space="preserve">warVictory.voice.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…追い込む</t>
+          <t xml:space="preserve">…当然の結果だ</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.cool.quiet[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7355,7 +7355,7 @@
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.cool.quiet[1]</t>
+          <t xml:space="preserve">bonus.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7365,14 +7365,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…分かった。応える</t>
+          <t xml:space="preserve">…ありがたい</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.cool.quiet[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7387,7 +7387,7 @@
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.cool.quiet[1]</t>
+          <t xml:space="preserve">camp.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7397,14 +7397,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……分かった</t>
+          <t xml:space="preserve">…追い込む</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.cool.quiet[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.cool.quiet[1]</t>
+          <t xml:space="preserve">encourage_high_trust.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7429,14 +7429,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……やる</t>
+          <t xml:space="preserve">…分かった。応える</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.cool.quiet[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.cool.quiet[1]</t>
+          <t xml:space="preserve">encourage.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7461,14 +7461,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪くなかった</t>
+          <t xml:space="preserve">……分かった</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.cool.quiet[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.cool.quiet[1]</t>
+          <t xml:space="preserve">media.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7493,14 +7493,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…感謝する。少し休む</t>
+          <t xml:space="preserve">……やる</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.cool.quiet[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7515,7 +7515,7 @@
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.cool.quiet[1]</t>
+          <t xml:space="preserve">party.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7525,14 +7525,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…感謝する。早く戻る</t>
+          <t xml:space="preserve">…悪くなかった</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.cool.quiet[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7547,7 +7547,7 @@
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.cool.quiet[1]</t>
+          <t xml:space="preserve">refresh_leave.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7557,14 +7557,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…吸収する。見ていてくれ</t>
+          <t xml:space="preserve">…感謝する。少し休む</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.cool.quiet[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.cool.quiet[1]</t>
+          <t xml:space="preserve">special_treatment.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7589,14 +7589,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……やる</t>
+          <t xml:space="preserve">…感謝する。早く戻る</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.cool.quiet[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.cool.quiet[1]</t>
+          <t xml:space="preserve">trainer.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7621,14 +7621,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…他所から来た。報告する</t>
+          <t xml:space="preserve">…吸収する。見ていてくれ</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.cool.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.cool.quiet[1]</t>
+          <t xml:space="preserve">E1.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7653,14 +7653,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（静かにテーピングを外している）</t>
+          <t xml:space="preserve">……やる</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.cool.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7675,7 +7675,7 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.cool.quiet[1]</t>
+          <t xml:space="preserve">E6.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7685,14 +7685,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（無言のまま動かず、周囲だけが落ち着かなくなっている）</t>
+          <t xml:space="preserve">…他所から来た。報告する</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.cool.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7707,7 +7707,7 @@
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.cool.quiet[1]</t>
+          <t xml:space="preserve">S_boycott.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7717,14 +7717,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに点を三つ置いただけの投稿。ファンの憶測だけが広がっていく）</t>
+          <t xml:space="preserve">………（静かにテーピングを外している）</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.cool.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7739,7 +7739,7 @@
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.cool.quiet[1]</t>
+          <t xml:space="preserve">S_grumble.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7749,14 +7749,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…タイトルマッチを。頼む</t>
+          <t xml:space="preserve">（無言のまま動かず、周囲だけが落ち着かなくなっている）</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.cool.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.cool.quiet[1]</t>
+          <t xml:space="preserve">S_sns.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7781,14 +7781,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あいつとの試合を。頼む</t>
+          <t xml:space="preserve">（SNSに点を三つ置いただけの投稿。ファンの憶測だけが広がっていく）</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.cool.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.cool.quiet[1]</t>
+          <t xml:space="preserve">S1.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7813,14 +7813,14 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…休む必要がある</t>
+          <t xml:space="preserve">…タイトルマッチを。頼む</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.cool.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7835,7 +7835,7 @@
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.cool.quiet[1]</t>
+          <t xml:space="preserve">S2.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7845,14 +7845,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もう、限界だ（静かに、しかし断固として）</t>
+          <t xml:space="preserve">…あいつとの試合を。頼む</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.cool.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7867,7 +7867,7 @@
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.cool.quiet[1]</t>
+          <t xml:space="preserve">S3.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7877,14 +7877,14 @@
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（何も言わず、立ち去ろうとする）</t>
+          <t xml:space="preserve">…休む必要がある</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.cool.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7899,7 +7899,7 @@
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.cool.quiet[1]</t>
+          <t xml:space="preserve">S4_direct.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -7909,14 +7909,14 @@
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…鍛えたい。場所を貸してくれ</t>
+          <t xml:space="preserve">……もう、限界だ（静かに、しかし断固として）</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.cool.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7931,7 +7931,7 @@
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.cool.quiet[1]</t>
+          <t xml:space="preserve">S4_silent.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7941,14 +7941,14 @@
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…次の世代に、繋ぎたいものがある</t>
+          <t xml:space="preserve">……（何も言わず、立ち去ろうとする）</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.cool.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.cool.quiet[1]</t>
+          <t xml:space="preserve">S5.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7973,14 +7973,14 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…すぐ戻る</t>
+          <t xml:space="preserve">…鍛えたい。場所を貸してくれ</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.cool.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7990,12 +7990,12 @@
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.cool.quiet[1]</t>
+          <t xml:space="preserve">S6.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -8005,14 +8005,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あれとは合わない。それだけだ</t>
+          <t xml:space="preserve">…次の世代に、繋ぎたいものがある</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.cool.quiet[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8027,7 +8027,7 @@
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.cool.quiet[1]</t>
+          <t xml:space="preserve">B1.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -8037,14 +8037,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…私は間違っていない</t>
+          <t xml:space="preserve">…すぐ戻る</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.cool.quiet[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8059,7 +8059,7 @@
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.cool.quiet[1]</t>
+          <t xml:space="preserve">B2_fighter1.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8069,14 +8069,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…無駄口は叩かない。それがブランドには向いているかもな</t>
+          <t xml:space="preserve">…あれとは合わない。それだけだ</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.cool.quiet[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.cool.quiet[1]</t>
+          <t xml:space="preserve">B2_fighter2.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8101,14 +8101,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…カメラか。まぁ、やる</t>
+          <t xml:space="preserve">…私は間違っていない</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.cool.quiet[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8123,7 +8123,7 @@
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.cool.quiet[1]</t>
+          <t xml:space="preserve">B4_brand.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8133,14 +8133,14 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…来てくれた人には、ちゃんと応えたい</t>
+          <t xml:space="preserve">…無駄口は叩かない。それがブランドには向いているかも</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.cool.quiet[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8155,7 +8155,7 @@
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.cool.quiet[1]</t>
+          <t xml:space="preserve">B4_cm.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8165,14 +8165,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…余計なことはしない。ただ歩く。それだけだ</t>
+          <t xml:space="preserve">…カメラか。まぁ、やる</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.cool.quiet[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8187,7 +8187,7 @@
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.cool.quiet[1]</t>
+          <t xml:space="preserve">B4_fan.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8197,14 +8197,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…写真か。余計なことはしないでくれ</t>
+          <t xml:space="preserve">…来てくれた人には、ちゃんと応えたい</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.cool.quiet[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8219,7 +8219,7 @@
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.cool.quiet[1]</t>
+          <t xml:space="preserve">B4_fashion.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8229,14 +8229,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…無駄なことは言わない。それだけだ</t>
+          <t xml:space="preserve">…余計なことはしない。ただ歩く。それだけだ</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.cool.quiet[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8251,7 +8251,7 @@
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.cool.quiet[1]</t>
+          <t xml:space="preserve">B4_gravure.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8261,14 +8261,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やる。見ていてくれ</t>
+          <t xml:space="preserve">…写真か。余計なことはしないでくれ</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.cool.quiet[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8278,29 +8278,29 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[1]</t>
+          <t xml:space="preserve">B4_variety.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…戦わせてくれるなら、応える</t>
+          <t xml:space="preserve">…無駄なことは言わない。それだけだ</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.cool.quiet[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8310,29 +8310,29 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[1]</t>
+          <t xml:space="preserve">B4.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……よろしく</t>
+          <t xml:space="preserve">…やる。見ていてくれ</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.cool.quiet[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8342,12 +8342,12 @@
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[2]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8357,14 +8357,14 @@
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……始めよう</t>
+          <t xml:space="preserve">…戦わせてくれるなら、応える</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.cool.quiet[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8374,7 +8374,7 @@
       </c>
       <c r="C252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D252" t="inlineStr" s="12">
@@ -8389,14 +8389,14 @@
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やる。見ていてくれ</t>
+          <t xml:space="preserve">……よろしく</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.cool.quiet[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="C253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[1]</t>
+          <t xml:space="preserve">cool.quiet[2]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8421,14 +8421,14 @@
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やるべきことをやる</t>
+          <t xml:space="preserve">……始めよう</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.cool.quiet[2]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="C254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[2]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8453,14 +8453,14 @@
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……すぐ戻る</t>
+          <t xml:space="preserve">…やる。見ていてくれ</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.cool.quiet[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8470,12 +8470,12 @@
       </c>
       <c r="C255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.cool.quiet[1]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8485,14 +8485,14 @@
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……終わった。それだけだ。……それだけのはずだ</t>
+          <t xml:space="preserve">…やるべきことをやる</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.cool.quiet[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.cool.quiet[1]</t>
+          <t xml:space="preserve">cool.quiet[2]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8517,14 +8517,14 @@
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……終わっていない。……私の中では</t>
+          <t xml:space="preserve">……すぐ戻る</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.cool.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8539,7 +8539,7 @@
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.cool.quiet[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8549,14 +8549,14 @@
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…戦わせてくれるなら、応える</t>
+          <t xml:space="preserve">……終わった。それだけだ。……それだけのはずだ</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.cool.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.cool.quiet[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8581,14 +8581,14 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……よろしく</t>
+          <t xml:space="preserve">……終わっていない。……私の中では</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.cool.quiet[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8603,7 +8603,7 @@
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.cool.quiet[2]</t>
+          <t xml:space="preserve">draftInterest.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8613,14 +8613,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……始めよう</t>
+          <t xml:space="preserve">…戦わせてくれるなら、応える</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.cool.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8635,7 +8635,7 @@
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.cool.quiet[1]</t>
+          <t xml:space="preserve">draftJoin.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8645,14 +8645,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…拾われた。…なら、恩を返す</t>
+          <t xml:space="preserve">……よろしく</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.cool.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8667,7 +8667,7 @@
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.cool.quiet[1]</t>
+          <t xml:space="preserve">draftJoin.cool.quiet[2]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8677,14 +8677,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やる。見ていてくれ</t>
+          <t xml:space="preserve">……始めよう</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.cool.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8699,7 +8699,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.cool.quiet[1]</t>
+          <t xml:space="preserve">faGreeting.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8709,14 +8709,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やるべきことをやる</t>
+          <t xml:space="preserve">……ここでやる。……結果で返す</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.cool.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.fresh.cool.quiet[1]</t>
+          <t xml:space="preserve">faSigning.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8741,14 +8741,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…体は軽い。…今日は、かなり…やれる</t>
+          <t xml:space="preserve">…やる。見ていてくれ</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.cool.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8763,7 +8763,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.heavy.cool.quiet[1]</t>
+          <t xml:space="preserve">faWelcome.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8773,14 +8773,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…重い。…やっても、抜けていくだけだ</t>
+          <t xml:space="preserve">…やるべきことをやる</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.cool.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8795,7 +8795,7 @@
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.warm.cool.quiet[1]</t>
+          <t xml:space="preserve">heatSelf.fresh.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8805,14 +8805,14 @@
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…動けている。…ただ、深さがない</t>
+          <t xml:space="preserve">…体は軽い。…今日は、かなり…やれる</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.cool.quiet[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8827,7 +8827,7 @@
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.cool.quiet[2]</t>
+          <t xml:space="preserve">heatSelf.heavy.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8837,14 +8837,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……すぐ戻る</t>
+          <t xml:space="preserve">…重い。…やっても、抜けていくだけだ</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.cool.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.cool.quiet[1]</t>
+          <t xml:space="preserve">heatSelf.warm.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8869,14 +8869,14 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……(静かに立ち去る)</t>
+          <t xml:space="preserve">…動けている。…ただ、深さがない</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.cool.quiet[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8891,7 +8891,7 @@
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.cool.quiet[2]</t>
+          <t xml:space="preserve">injury.cool.quiet[2]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -8901,14 +8901,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ありがとう</t>
+          <t xml:space="preserve">……すぐ戻る</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.cool.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8923,7 +8923,7 @@
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.cool.quiet[1]</t>
+          <t xml:space="preserve">release.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -8933,14 +8933,14 @@
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やるべきことはやる</t>
+          <t xml:space="preserve">……（静かに立ち去る）</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.cool.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.cool.quiet[1]</t>
+          <t xml:space="preserve">release.cool.quiet[2]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -8965,14 +8965,14 @@
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…期待には、応える</t>
+          <t xml:space="preserve">……ありがとう</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.cool.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8987,7 +8987,7 @@
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.cool.quiet[1]</t>
+          <t xml:space="preserve">rentalGreeting.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -8997,14 +8997,14 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…次で終わらせる</t>
+          <t xml:space="preserve">…やるべきことはやる</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.cool.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -9019,7 +9019,7 @@
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.cool.quiet[1]</t>
+          <t xml:space="preserve">scoutGreeting.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -9029,14 +9029,14 @@
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…次も勝つ。それだけだ</t>
+          <t xml:space="preserve">…期待には、応える</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.cool.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9051,7 +9051,7 @@
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.cool.quiet[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9061,14 +9061,14 @@
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…認めよう。だが、終わりではない</t>
+          <t xml:space="preserve">…次で終わらせる</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.cool.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9083,7 +9083,7 @@
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.cool.quiet[1]</t>
+          <t xml:space="preserve">titleDefense.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9093,14 +9093,14 @@
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ようやくだ。この座は渡さない</t>
+          <t xml:space="preserve">…次も勝つ。それだけだ</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.cool.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9110,12 +9110,12 @@
       </c>
       <c r="C275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[1]</t>
+          <t xml:space="preserve">titleLoss.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9125,14 +9125,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……(静かに立ち去る)</t>
+          <t xml:space="preserve">…認めよう。だが、終わりではない</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.cool.quiet[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="C276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[2]</t>
+          <t xml:space="preserve">titleWin.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9157,14 +9157,14 @@
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ありがとう</t>
+          <t xml:space="preserve">…ようやくだ。この座は渡さない</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.cool.quiet[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9174,7 +9174,7 @@
       </c>
       <c r="C277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D277" t="inlineStr" s="12">
@@ -9189,14 +9189,14 @@
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やるべきことはやる</t>
+          <t xml:space="preserve">……（静かに立ち去る）</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.cool.quiet[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9206,12 +9206,12 @@
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[1]</t>
+          <t xml:space="preserve">cool.quiet[2]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9221,14 +9221,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…次で終わらせる</t>
+          <t xml:space="preserve">……ありがとう</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.cool.quiet[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9238,7 +9238,7 @@
       </c>
       <c r="C279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="12">
@@ -9253,14 +9253,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…次も勝つ。それだけだ</t>
+          <t xml:space="preserve">…やるべきことはやる</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.cool.quiet[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9270,7 +9270,7 @@
       </c>
       <c r="C280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D280" t="inlineStr" s="12">
@@ -9285,14 +9285,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…認めよう。だが、終わりではない</t>
+          <t xml:space="preserve">…次で終わらせる</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.cool.quiet[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9302,7 +9302,7 @@
       </c>
       <c r="C281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D281" t="inlineStr" s="12">
@@ -9317,14 +9317,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ようやくだ。この座は渡さない</t>
+          <t xml:space="preserve">…次も勝つ。それだけだ</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.quiet.cool[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9334,29 +9334,29 @@
       </c>
       <c r="C282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.quiet.cool[1]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……終わりだ</t>
+          <t xml:space="preserve">…認めよう。だが、終わりではない</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.quiet.cool[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9366,29 +9366,29 @@
       </c>
       <c r="C283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.quiet.cool[1]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……遠い</t>
+          <t xml:space="preserve">…ようやくだ。この座は渡さない</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.quiet.cool[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9403,7 +9403,7 @@
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.quiet.cool[2]</t>
+          <t xml:space="preserve">bond_39_down.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9413,14 +9413,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もう、隣にいない</t>
+          <t xml:space="preserve">……終わりだ</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.quiet.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9435,7 +9435,7 @@
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.quiet.cool[1]</t>
+          <t xml:space="preserve">bond_59_down.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9445,14 +9445,14 @@
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……悪くない距離感だ</t>
+          <t xml:space="preserve">……遠い</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.quiet.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.quiet.cool[2]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9467,7 +9467,7 @@
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.quiet.cool[1]</t>
+          <t xml:space="preserve">bond_59_down.quiet.cool[2]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9477,14 +9477,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……この人だけは、信じられる</t>
+          <t xml:space="preserve">……もう、隣にいない</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.quiet.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9499,7 +9499,7 @@
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.quiet.cool[1]</t>
+          <t xml:space="preserve">bond_60_up.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9509,14 +9509,14 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もう考えない</t>
+          <t xml:space="preserve">……悪くない距離感だ</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.quiet.cool[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9531,7 +9531,7 @@
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.quiet.cool[2]</t>
+          <t xml:space="preserve">bond_80_up.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9541,14 +9541,14 @@
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……風が止んだ</t>
+          <t xml:space="preserve">……この人だけは、信じられる</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.quiet.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9563,7 +9563,7 @@
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.quiet.cool[1]</t>
+          <t xml:space="preserve">rivalry_29_down.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9573,14 +9573,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……気になる。ただ、それだけだが</t>
+          <t xml:space="preserve">……もう考えない</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.quiet.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.quiet.cool[2]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9595,7 +9595,7 @@
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.quiet.cool[1]</t>
+          <t xml:space="preserve">rivalry_29_down.quiet.cool[2]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9605,14 +9605,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……超えなければ、先へ進めない</t>
+          <t xml:space="preserve">……風が止んだ</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.quiet.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.quiet.cool[1]</t>
+          <t xml:space="preserve">rivalry_30_up.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9637,14 +9637,14 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……あの相手がいる限り、立ち続ける</t>
+          <t xml:space="preserve">……気になる。ただ、それだけだが</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.quiet.cool[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9659,7 +9659,7 @@
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.quiet.cool[2]</t>
+          <t xml:space="preserve">rivalry_50_up.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9669,14 +9669,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……言葉はいらない。リングで話す</t>
+          <t xml:space="preserve">……超えなければ、先へ進めない</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.quiet.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9691,7 +9691,7 @@
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.quiet.cool[1]</t>
+          <t xml:space="preserve">rivalry_70_up.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9701,14 +9701,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ここにいたい</t>
+          <t xml:space="preserve">……あの相手がいる限り、立ち続ける</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.quiet.cool[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.quiet.cool[2]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9723,7 +9723,7 @@
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.quiet.cool[2]</t>
+          <t xml:space="preserve">rivalry_70_up.quiet.cool[2]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9733,14 +9733,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……この場所を守る</t>
+          <t xml:space="preserve">……言葉はいらない。リングで話す</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.quiet.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9755,7 +9755,7 @@
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.quiet.cool[1]</t>
+          <t xml:space="preserve">trust_above_75.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9765,14 +9765,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（荷物をまとめている）</t>
+          <t xml:space="preserve">……ここにいたい</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.quiet.cool[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.quiet.cool[2]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9787,7 +9787,7 @@
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.quiet.cool[2]</t>
+          <t xml:space="preserve">trust_above_75.quiet.cool[2]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9797,14 +9797,14 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……何も、残っていない</t>
+          <t xml:space="preserve">……この場所を守る</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.quiet.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9819,7 +9819,7 @@
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.quiet.cool[1]</t>
+          <t xml:space="preserve">trust_below_20.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9829,14 +9829,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……この場所に、未来はあるのか</t>
+          <t xml:space="preserve">……（荷物をまとめている）</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.cool.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.quiet.cool[2]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9846,12 +9846,12 @@
       </c>
       <c r="C298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[1]</t>
+          <t xml:space="preserve">trust_below_20.quiet.cool[2]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -9861,14 +9861,14 @@
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……調子は落ち着いた。だが後退じゃない</t>
+          <t xml:space="preserve">……何も、残っていない</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.cool.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9878,29 +9878,29 @@
       </c>
       <c r="C299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.cool.quiet[1]</t>
+          <t xml:space="preserve">trust_below_35.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……最後。立てる。十分</t>
+          <t xml:space="preserve">……この場所に、未来はあるのか</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.cool.quiet[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9910,29 +9910,29 @@
       </c>
       <c r="C300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.cool.quiet[2]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……傷は数えない。ただ、いく</t>
+          <t xml:space="preserve">……調子は落ち着いた。だが後退じゃない</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.cool.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9947,7 +9947,7 @@
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.cool.quiet[1]</t>
+          <t xml:space="preserve">preFinal.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -9957,14 +9957,14 @@
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次</t>
+          <t xml:space="preserve">……最後。立てる。十分</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.cool.quiet[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -9979,7 +9979,7 @@
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.cool.quiet[2]</t>
+          <t xml:space="preserve">preFinal.cool.quiet[2]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
@@ -9989,14 +9989,14 @@
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……倒す。残る</t>
+          <t xml:space="preserve">……傷は数えない。ただ、いく</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.cool.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -10011,7 +10011,7 @@
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.cool.quiet[1]</t>
+          <t xml:space="preserve">preMatch.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
@@ -10021,14 +10021,14 @@
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……一人。まだ立ってる。次</t>
+          <t xml:space="preserve">……次</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.cool.quiet[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -10043,7 +10043,7 @@
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.cool.quiet[2]</t>
+          <t xml:space="preserve">preMatch.cool.quiet[2]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
@@ -10053,14 +10053,14 @@
       </c>
       <c r="F304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……退かない。出せ</t>
+          <t xml:space="preserve">……倒す。残る</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.cool.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10070,12 +10070,12 @@
       </c>
       <c r="C305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.cool.quiet[1]</t>
+          <t xml:space="preserve">survivor.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">
@@ -10085,14 +10085,14 @@
       </c>
       <c r="F305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……三人の結果。言葉は要らない</t>
+          <t xml:space="preserve">……一人。まだ立ってる。次</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.cool.quiet[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -10102,12 +10102,12 @@
       </c>
       <c r="C306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.cool.quiet[2]</t>
+          <t xml:space="preserve">survivor.cool.quiet[2]</t>
         </is>
       </c>
       <c r="E306" t="inlineStr" s="2">
@@ -10117,14 +10117,14 @@
       </c>
       <c r="F306" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……一人では不可能だった。それは認める</t>
+          <t xml:space="preserve">……退かない。出せ</t>
         </is>
       </c>
     </row>
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.cool.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="D307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.cool.quiet[1]</t>
+          <t xml:space="preserve">champion.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E307" t="inlineStr" s="2">
@@ -10149,14 +10149,14 @@
       </c>
       <c r="F307" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……不十分だった。次がある</t>
+          <t xml:space="preserve">……三人の結果。言葉は要らない</t>
         </is>
       </c>
     </row>
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.cool.quiet[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -10171,7 +10171,7 @@
       </c>
       <c r="D308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.cool.quiet[2]</t>
+          <t xml:space="preserve">champion.cool.quiet[2]</t>
         </is>
       </c>
       <c r="E308" t="inlineStr" s="2">
@@ -10181,14 +10181,14 @@
       </c>
       <c r="F308" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……団体が負けた。それが全て。次に期す</t>
+          <t xml:space="preserve">……一人では不可能だった。それは認める</t>
         </is>
       </c>
     </row>
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.cool.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -10203,7 +10203,7 @@
       </c>
       <c r="D309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.cool.quiet[1]</t>
+          <t xml:space="preserve">defiant.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E309" t="inlineStr" s="2">
@@ -10213,14 +10213,14 @@
       </c>
       <c r="F309" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……立っている。それが結果</t>
+          <t xml:space="preserve">……不十分だった。次がある</t>
         </is>
       </c>
     </row>
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.cool.quiet[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -10235,7 +10235,7 @@
       </c>
       <c r="D310" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.cool.quiet[2]</t>
+          <t xml:space="preserve">defiant.cool.quiet[2]</t>
         </is>
       </c>
       <c r="E310" t="inlineStr" s="2">
@@ -10245,14 +10245,14 @@
       </c>
       <c r="F310" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……数えてない。ただ、倒れなかった</t>
+          <t xml:space="preserve">……団体が負けた。それが全て。次に期す</t>
         </is>
       </c>
     </row>
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.cool.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -10262,12 +10262,12 @@
       </c>
       <c r="C311" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D311" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.cool.quiet[1]</t>
+          <t xml:space="preserve">gauntlet.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E311" t="inlineStr" s="2">
@@ -10277,14 +10277,14 @@
       </c>
       <c r="F311" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（トロフィーを静かに掲げる）</t>
+          <t xml:space="preserve">……立っている。それが結果</t>
         </is>
       </c>
     </row>
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.cool.quiet[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10294,12 +10294,12 @@
       </c>
       <c r="C312" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.cool.quiet[2]</t>
+          <t xml:space="preserve">gauntlet.cool.quiet[2]</t>
         </is>
       </c>
       <c r="E312" t="inlineStr" s="2">
@@ -10309,14 +10309,14 @@
       </c>
       <c r="F312" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…………ありがとう</t>
+          <t xml:space="preserve">……数えてない。ただ、倒れなかった</t>
         </is>
       </c>
     </row>
     <row r="313" ht="40" customHeight="1">
       <c r="A313" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.cool.quiet[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -10331,7 +10331,7 @@
       </c>
       <c r="D313" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.cool.quiet[1]</t>
+          <t xml:space="preserve">champion.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E313" t="inlineStr" s="2">
@@ -10341,14 +10341,14 @@
       </c>
       <c r="F313" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（無言で去る）</t>
+          <t xml:space="preserve">……（トロフィーを静かに掲げる）</t>
         </is>
       </c>
     </row>
     <row r="314" ht="40" customHeight="1">
       <c r="A314" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.cool.quiet[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="D314" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.cool.quiet[1]</t>
+          <t xml:space="preserve">champion.cool.quiet[2]</t>
         </is>
       </c>
       <c r="E314" t="inlineStr" s="2">
@@ -10373,14 +10373,14 @@
       </c>
       <c r="F314" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（静かに頷く）</t>
+          <t xml:space="preserve">…………ありがとう</t>
         </is>
       </c>
     </row>
     <row r="315" ht="40" customHeight="1">
       <c r="A315" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.cool.quiet[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
@@ -10395,7 +10395,7 @@
       </c>
       <c r="D315" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.cool.quiet[2]</t>
+          <t xml:space="preserve">postLose.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E315" t="inlineStr" s="2">
@@ -10405,14 +10405,14 @@
       </c>
       <c r="F315" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まだ</t>
+          <t xml:space="preserve">……（無言で去る）</t>
         </is>
       </c>
     </row>
     <row r="316" ht="40" customHeight="1">
       <c r="A316" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.cool.quiet[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B316" t="inlineStr" s="2">
@@ -10427,7 +10427,7 @@
       </c>
       <c r="D316" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.cool.quiet[2]</t>
+          <t xml:space="preserve">postMatchWin.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E316" t="inlineStr" s="2">
@@ -10437,14 +10437,14 @@
       </c>
       <c r="F316" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（少し笑顔を見せる）</t>
+          <t xml:space="preserve">……（静かに頷く）</t>
         </is>
       </c>
     </row>
     <row r="317" ht="40" customHeight="1">
       <c r="A317" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.cool.quiet[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B317" t="inlineStr" s="2">
@@ -10459,7 +10459,7 @@
       </c>
       <c r="D317" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.cool.quiet[1]</t>
+          <t xml:space="preserve">postMatchWin.cool.quiet[2]</t>
         </is>
       </c>
       <c r="E317" t="inlineStr" s="2">
@@ -10469,14 +10469,14 @@
       </c>
       <c r="F317" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……最後</t>
+          <t xml:space="preserve">……まだ</t>
         </is>
       </c>
     </row>
     <row r="318" ht="40" customHeight="1">
       <c r="A318" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.cool.quiet[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B318" t="inlineStr" s="2">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="D318" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.cool.quiet[2]</t>
+          <t xml:space="preserve">postWin.cool.quiet[2]</t>
         </is>
       </c>
       <c r="E318" t="inlineStr" s="2">
@@ -10501,14 +10501,14 @@
       </c>
       <c r="F318" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……全部、出す</t>
+          <t xml:space="preserve">……（少し笑顔を見せる）</t>
         </is>
       </c>
     </row>
     <row r="319" ht="40" customHeight="1">
       <c r="A319" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.cool.quiet[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B319" t="inlineStr" s="2">
@@ -10523,7 +10523,7 @@
       </c>
       <c r="D319" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.cool.quiet[2]</t>
+          <t xml:space="preserve">preFinal.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E319" t="inlineStr" s="2">
@@ -10533,14 +10533,14 @@
       </c>
       <c r="F319" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（拳を握る）</t>
+          <t xml:space="preserve">……最後</t>
         </is>
       </c>
     </row>
     <row r="320" ht="40" customHeight="1">
       <c r="A320" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.cool.quiet[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B320" t="inlineStr" s="2">
@@ -10555,7 +10555,7 @@
       </c>
       <c r="D320" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.cool.quiet[2]</t>
+          <t xml:space="preserve">preFinal.cool.quiet[2]</t>
         </is>
       </c>
       <c r="E320" t="inlineStr" s="2">
@@ -10565,14 +10565,14 @@
       </c>
       <c r="F320" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（静かに頷く）</t>
+          <t xml:space="preserve">……全部、出す</t>
         </is>
       </c>
     </row>
     <row r="321" ht="40" customHeight="1">
       <c r="A321" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.cool.quiet[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B321" t="inlineStr" s="2">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="C321" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D321" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[1]</t>
+          <t xml:space="preserve">preMatch.cool.quiet[2]</t>
         </is>
       </c>
       <c r="E321" t="inlineStr" s="2">
@@ -10597,14 +10597,14 @@
       </c>
       <c r="F321" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…結果で語る</t>
+          <t xml:space="preserve">……（拳を握る）</t>
         </is>
       </c>
     </row>
     <row r="322" ht="40" customHeight="1">
       <c r="A322" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.cool.quiet[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B322" t="inlineStr" s="2">
@@ -10614,12 +10614,12 @@
       </c>
       <c r="C322" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D322" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[1]</t>
+          <t xml:space="preserve">summon.cool.quiet[2]</t>
         </is>
       </c>
       <c r="E322" t="inlineStr" s="2">
@@ -10629,14 +10629,14 @@
       </c>
       <c r="F322" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（ベルトを静かに抱きしめる）</t>
+          <t xml:space="preserve">……（静かに頷く）</t>
         </is>
       </c>
     </row>
     <row r="323" ht="40" customHeight="1">
       <c r="A323" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.cool.quiet[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B323" t="inlineStr" s="2">
@@ -10646,7 +10646,7 @@
       </c>
       <c r="C323" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D323" t="inlineStr" s="12">
@@ -10661,14 +10661,14 @@
       </c>
       <c r="F323" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……来い</t>
+          <t xml:space="preserve">…結果で語る</t>
         </is>
       </c>
     </row>
     <row r="324" ht="40" customHeight="1">
       <c r="A324" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.cool.quiet[2]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B324" t="inlineStr" s="2">
@@ -10678,12 +10678,12 @@
       </c>
       <c r="C324" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D324" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[2]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E324" t="inlineStr" s="2">
@@ -10693,14 +10693,14 @@
       </c>
       <c r="F324" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（背を向ける）</t>
+          <t xml:space="preserve">………（ベルトを静かに抱きしめる）</t>
         </is>
       </c>
     </row>
     <row r="325" ht="40" customHeight="1">
       <c r="A325" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.cool.quiet[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B325" t="inlineStr" s="2">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="C325" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D325" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.cool.quiet[2]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E325" t="inlineStr" s="2">
@@ -10725,14 +10725,14 @@
       </c>
       <c r="F325" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（拳を握りしめる）</t>
+          <t xml:space="preserve">……来い</t>
         </is>
       </c>
     </row>
     <row r="326" ht="40" customHeight="1">
       <c r="A326" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.cool.quiet[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B326" t="inlineStr" s="2">
@@ -10742,12 +10742,12 @@
       </c>
       <c r="C326" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D326" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.cool.quiet[1]</t>
+          <t xml:space="preserve">cool.quiet[2]</t>
         </is>
       </c>
       <c r="E326" t="inlineStr" s="2">
@@ -10757,14 +10757,14 @@
       </c>
       <c r="F326" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（静かに頷く）</t>
+          <t xml:space="preserve">……（背を向ける）</t>
         </is>
       </c>
     </row>
     <row r="327" ht="40" customHeight="1">
       <c r="A327" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.cool.quiet[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B327" t="inlineStr" s="2">
@@ -10774,12 +10774,12 @@
       </c>
       <c r="C327" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D327" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[1]</t>
+          <t xml:space="preserve">result_lose.cool.quiet[2]</t>
         </is>
       </c>
       <c r="E327" t="inlineStr" s="2">
@@ -10789,14 +10789,14 @@
       </c>
       <c r="F327" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……証明した。それだけ</t>
+          <t xml:space="preserve">……（拳を握りしめる）</t>
         </is>
       </c>
     </row>
     <row r="328" ht="40" customHeight="1">
       <c r="A328" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.cool.quiet[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B328" t="inlineStr" s="2">
@@ -10806,12 +10806,12 @@
       </c>
       <c r="C328" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D328" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[2]</t>
+          <t xml:space="preserve">result_win.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E328" t="inlineStr" s="2">
@@ -10821,14 +10821,14 @@
       </c>
       <c r="F328" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……これがうちの力</t>
+          <t xml:space="preserve">……（静かに頷く）</t>
         </is>
       </c>
     </row>
     <row r="329" ht="40" customHeight="1">
       <c r="A329" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.cool.quiet[3]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B329" t="inlineStr" s="2">
@@ -10843,7 +10843,7 @@
       </c>
       <c r="D329" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[3]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E329" t="inlineStr" s="2">
@@ -10853,14 +10853,14 @@
       </c>
       <c r="F329" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（静かに頷く）</t>
+          <t xml:space="preserve">……証明した。それだけ</t>
         </is>
       </c>
     </row>
     <row r="330" ht="40" customHeight="1">
       <c r="A330" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.cool.quiet[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B330" t="inlineStr" s="2">
@@ -10870,29 +10870,29 @@
       </c>
       <c r="C330" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D330" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.cool.quiet[1]</t>
+          <t xml:space="preserve">cool.quiet[2]</t>
         </is>
       </c>
       <c r="E330" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F330" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここまで来たか</t>
+          <t xml:space="preserve">……これがうちの力</t>
         </is>
       </c>
     </row>
     <row r="331" ht="40" customHeight="1">
       <c r="A331" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.cool.quiet[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.cool.quiet[3]</t>
         </is>
       </c>
       <c r="B331" t="inlineStr" s="2">
@@ -10902,59 +10902,123 @@
       </c>
       <c r="C331" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D331" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[1]</t>
+          <t xml:space="preserve">cool.quiet[3]</t>
         </is>
       </c>
       <c r="E331" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F331" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…拾われた。…なら、恩を返す</t>
+          <t xml:space="preserve">……（静かに頷く）</t>
         </is>
       </c>
     </row>
     <row r="332" ht="40" customHeight="1">
       <c r="A332" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.cool.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.cool.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ここまで来たか</t>
+        </is>
+      </c>
+    </row>
+    <row r="333" ht="40" customHeight="1">
+      <c r="A333" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.cool.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">cool.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……ここでやる。……結果で返す</t>
+        </is>
+      </c>
+    </row>
+    <row r="334" ht="40" customHeight="1">
+      <c r="A334" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.cool.quiet[1]</t>
         </is>
       </c>
-      <c r="B332" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr" s="2">
+      <c r="B334" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D332" t="inlineStr" s="12">
+      <c r="D334" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
-      <c r="E332" t="inlineStr" s="2">
+      <c r="E334" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F332" t="inlineStr" s="3">
+      <c r="F334" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…期待には、応える</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H332"/>
+  <autoFilter ref="A1:H334"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/クール×寡黙.xlsx
+++ b/セリフ編集/キャラタイプ別/クール×寡黙.xlsx
@@ -306,7 +306,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H334"/>
+  <dimension ref="A1:H341"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -3820,7 +3820,7 @@
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.cool.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_accept.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3835,7 +3835,7 @@
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.cool.quiet[1]</t>
+          <t xml:space="preserve">decline_accept.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="2">
@@ -3845,14 +3845,14 @@
       </c>
       <c r="F110" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう。…頑張る</t>
+          <t xml:space="preserve">……分かった。……戻すだけ</t>
         </is>
       </c>
     </row>
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.cool.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_hold.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.cool.quiet[1]</t>
+          <t xml:space="preserve">decline_hold.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
@@ -3877,14 +3877,14 @@
       </c>
       <c r="F111" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…分かった。ありがとう</t>
+          <t xml:space="preserve">……なんで。……いや。……ありがとう</t>
         </is>
       </c>
     </row>
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.cool.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_open.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.cool.quiet[1]</t>
+          <t xml:space="preserve">decline_open.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
@@ -3909,14 +3909,14 @@
       </c>
       <c r="F112" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう。…分かった</t>
+          <t xml:space="preserve">……そう。……数字どおり、か</t>
         </is>
       </c>
     </row>
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.cool.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_strict.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.cool.quiet[1]</t>
+          <t xml:space="preserve">decline_strict.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
@@ -3941,14 +3941,14 @@
       </c>
       <c r="F113" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長。{tenure}…給料の話。{record}…考えてほしい</t>
+          <t xml:space="preserve">……そう。……もういい</t>
         </is>
       </c>
     </row>
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.cool.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_accept.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.cool.quiet[1]</t>
+          <t xml:space="preserve">decline_voluntary_accept.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -3973,14 +3973,14 @@
       </c>
       <c r="F114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう。……分かった</t>
+          <t xml:space="preserve">……それでいい。……身軽になった</t>
         </is>
       </c>
     </row>
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.cool.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_hold.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.cool.quiet[1]</t>
+          <t xml:space="preserve">decline_voluntary_hold.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -4005,14 +4005,14 @@
       </c>
       <c r="F115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……すみません。……もう、限界です</t>
+          <t xml:space="preserve">……聞いてた？ ……下げてって言った。……いや。……ありがとう</t>
         </is>
       </c>
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.cool.quiet[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_open.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.cool.quiet[2]</t>
+          <t xml:space="preserve">decline_voluntary_open.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
@@ -4037,14 +4037,14 @@
       </c>
       <c r="F116" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……黙って消えようかと思った。……一応、挨拶だけ</t>
+          <t xml:space="preserve">……下げていい。……もう、そういう歳だ</t>
         </is>
       </c>
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.cool.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.cool.quiet[1]</t>
+          <t xml:space="preserve">raise_accept.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
@@ -4069,14 +4069,14 @@
       </c>
       <c r="F117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…聞いてくれるんだ。{record}…ここにいる意味が、分からない</t>
+          <t xml:space="preserve">…ありがとう。…頑張る</t>
         </is>
       </c>
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.cool.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.cool.quiet[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
@@ -4101,14 +4101,14 @@
       </c>
       <c r="F118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…{tenure}…出たい。…それだけ</t>
+          <t xml:space="preserve">…分かった。ありがとう</t>
         </is>
       </c>
     </row>
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.cool.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4123,7 +4123,7 @@
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.cool.quiet[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
@@ -4133,14 +4133,14 @@
       </c>
       <c r="F119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…{tenure_farewell}{rivalry}…ありがとう</t>
+          <t xml:space="preserve">…そう。…分かった</t>
         </is>
       </c>
     </row>
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.cool.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.cool.quiet[1]</t>
+          <t xml:space="preserve">raise_open.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
@@ -4165,14 +4165,14 @@
       </c>
       <c r="F120" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ごめん。…もう決めた</t>
+          <t xml:space="preserve">…社長。{tenure}…給料の話。{record}…考えてほしい</t>
         </is>
       </c>
     </row>
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.cool.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.cool.quiet[1]</t>
+          <t xml:space="preserve">raise_refuse.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
@@ -4197,14 +4197,14 @@
       </c>
       <c r="F121" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そこまで言うなら。…もう少しだけ</t>
+          <t xml:space="preserve">…そう。……分かった</t>
         </is>
       </c>
     </row>
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.blocked.cool.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="C122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">blocked.cool.quiet[1]</t>
+          <t xml:space="preserve">sudden_departure.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
@@ -4229,14 +4229,14 @@
       </c>
       <c r="F122" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…話にならない。断る</t>
+          <t xml:space="preserve">……すみません。……もう、限界です</t>
         </is>
       </c>
     </row>
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.fail.cool.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4246,12 +4246,12 @@
       </c>
       <c r="C123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fail.cool.quiet[1]</t>
+          <t xml:space="preserve">sudden_departure.cool.quiet[2]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
@@ -4261,14 +4261,14 @@
       </c>
       <c r="F123" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…断る</t>
+          <t xml:space="preserve">……黙って消えようかと思った。……一応、挨拶だけ</t>
         </is>
       </c>
     </row>
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.cool.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4278,12 +4278,12 @@
       </c>
       <c r="C124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">start.cool.quiet[1]</t>
+          <t xml:space="preserve">transfer_listen.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
@@ -4293,14 +4293,14 @@
       </c>
       <c r="F124" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…聞こう</t>
+          <t xml:space="preserve">…聞いてくれるんだ。{record}…ここにいる意味が、分からない</t>
         </is>
       </c>
     </row>
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.success.cool.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4310,12 +4310,12 @@
       </c>
       <c r="C125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">success.cool.quiet[1]</t>
+          <t xml:space="preserve">transfer_open.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
@@ -4325,14 +4325,14 @@
       </c>
       <c r="F125" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…行く</t>
+          <t xml:space="preserve">…{tenure}…出たい。…それだけ</t>
         </is>
       </c>
     </row>
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.cool.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -4342,29 +4342,29 @@
       </c>
       <c r="C126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.cool.quiet[1]</t>
+          <t xml:space="preserve">transfer_release.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F126" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、私たちのこと、気にかけていただけますか。</t>
+          <t xml:space="preserve">…{tenure_farewell}{rivalry}…ありがとう</t>
         </is>
       </c>
     </row>
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.cool.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -4374,29 +4374,29 @@
       </c>
       <c r="C127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.cool.quiet[1]</t>
+          <t xml:space="preserve">transfer_retain_fail.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F127" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、次のメイン、私たちに回せませんか。</t>
+          <t xml:space="preserve">…ごめん。…もう決めた</t>
         </is>
       </c>
     </row>
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.cool.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4406,29 +4406,29 @@
       </c>
       <c r="C128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.cool.quiet[1]</t>
+          <t xml:space="preserve">transfer_retain_success.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F128" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、給与のこと、相談があります。</t>
+          <t xml:space="preserve">…そこまで言うなら。…もう少しだけ</t>
         </is>
       </c>
     </row>
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.cool.quiet[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.blocked.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4438,29 +4438,29 @@
       </c>
       <c r="C129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.cool.quiet[1]</t>
+          <t xml:space="preserve">blocked.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F129" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、私たちの仕事、見ていますか。</t>
+          <t xml:space="preserve">…話にならない。断る</t>
         </is>
       </c>
     </row>
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.cool.quiet[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.fail.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4470,29 +4470,29 @@
       </c>
       <c r="C130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.cool.quiet[1]</t>
+          <t xml:space="preserve">fail.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…見ていてくれたんですね。</t>
+          <t xml:space="preserve">…断る</t>
         </is>
       </c>
     </row>
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.cool.quiet[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4502,29 +4502,29 @@
       </c>
       <c r="C131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.cool.quiet[1]</t>
+          <t xml:space="preserve">start.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい、わかりました。</t>
+          <t xml:space="preserve">…聞こう</t>
         </is>
       </c>
     </row>
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.cool.quiet[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.success.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4534,29 +4534,29 @@
       </c>
       <c r="C132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.cool.quiet[1]</t>
+          <t xml:space="preserve">success.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。受け取ります。</t>
+          <t xml:space="preserve">…行く</t>
         </is>
       </c>
     </row>
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.cool.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.cool.quiet[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr" s="2">
@@ -4581,14 +4581,14 @@
       </c>
       <c r="F133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。やります。</t>
+          <t xml:space="preserve">…社長、私たちのこと、気にかけていただけますか。</t>
         </is>
       </c>
     </row>
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.cool.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4603,7 +4603,7 @@
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.cool.quiet[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
@@ -4613,14 +4613,14 @@
       </c>
       <c r="F134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい、わかりました。</t>
+          <t xml:space="preserve">…社長、次のメイン、私たちに回せませんか。</t>
         </is>
       </c>
     </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.cool.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.cool.quiet[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
@@ -4645,14 +4645,14 @@
       </c>
       <c r="F135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。受け取ります。</t>
+          <t xml:space="preserve">…社長、給与のこと、相談があります。</t>
         </is>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.cool.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.cool.quiet[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
@@ -4677,14 +4677,14 @@
       </c>
       <c r="F136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。</t>
+          <t xml:space="preserve">…社長、私たちの仕事、見ていますか。</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.cool.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.cool.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
@@ -4709,14 +4709,14 @@
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい、わかりました。</t>
+          <t xml:space="preserve">…ありがとうございます。…見ていてくれたんですね。</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.cool.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.cool.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
@@ -4741,14 +4741,14 @@
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。</t>
+          <t xml:space="preserve">…はい、わかりました。</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.cool.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.cool.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
@@ -4773,14 +4773,14 @@
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…見ていてくれたんですね。</t>
+          <t xml:space="preserve">…ありがとうございます。受け取ります。</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.cool.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.cool.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
@@ -4805,14 +4805,14 @@
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい、わかりました。</t>
+          <t xml:space="preserve">…ありがとうございます。やります。</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.cool.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4827,7 +4827,7 @@
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.cool.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
@@ -4837,14 +4837,14 @@
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。受け取ります。</t>
+          <t xml:space="preserve">…はい、わかりました。</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.cool.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.cool.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
@@ -4869,14 +4869,14 @@
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい、わかりました。</t>
+          <t xml:space="preserve">…ありがとうございます。受け取ります。</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.cool.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.cool.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
@@ -4901,14 +4901,14 @@
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…でも、少し、考えます。</t>
+          <t xml:space="preserve">…ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.cool.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.cool.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
@@ -4940,7 +4940,7 @@
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.cool.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.cool.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
@@ -4972,7 +4972,7 @@
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.cool.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.cool.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
@@ -4997,14 +4997,14 @@
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい、わかりました。</t>
+          <t xml:space="preserve">…ありがとうございます。…見ていてくれたんですね。</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.cool.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.cool.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
@@ -5029,14 +5029,14 @@
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。</t>
+          <t xml:space="preserve">…はい、わかりました。</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.cool.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.cool.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
@@ -5061,14 +5061,14 @@
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありません。…出ます。</t>
+          <t xml:space="preserve">…ありがとうございます。受け取ります。</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.cool.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.cool.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
@@ -5093,14 +5093,14 @@
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。</t>
+          <t xml:space="preserve">…はい、わかりました。</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.cool.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5115,7 +5115,7 @@
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.cool.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
@@ -5125,14 +5125,14 @@
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。</t>
+          <t xml:space="preserve">…ありがとうございます。…でも、少し、考えます。</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.cool.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.cool.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
@@ -5157,14 +5157,14 @@
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…休みます。</t>
+          <t xml:space="preserve">…はい、わかりました。</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.cool.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.cool.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
@@ -5189,14 +5189,14 @@
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい、平気です。</t>
+          <t xml:space="preserve">…ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.cool.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.cool.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
@@ -5221,14 +5221,14 @@
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。</t>
+          <t xml:space="preserve">…はい、わかりました。</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.cool.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.cool.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
@@ -5253,14 +5253,14 @@
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい、わかりました。</t>
+          <t xml:space="preserve">…ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.cool.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5275,7 +5275,7 @@
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.cool.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
@@ -5285,14 +5285,14 @@
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。</t>
+          <t xml:space="preserve">…申し訳ありません。…出ます。</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.cool.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.cool.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
@@ -5324,7 +5324,7 @@
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.cool.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.cool.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
@@ -5349,14 +5349,14 @@
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい、わかりました。</t>
+          <t xml:space="preserve">…ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.cool.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.cool.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
@@ -5381,14 +5381,14 @@
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（…何も言わず、目を伏せた）</t>
+          <t xml:space="preserve">…ありがとうございます。…休みます。</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.cool.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.cool.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
@@ -5413,14 +5413,14 @@
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。</t>
+          <t xml:space="preserve">…はい、平気です。</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.cool.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.cool.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
@@ -5445,14 +5445,14 @@
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい、加減します。</t>
+          <t xml:space="preserve">…ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.cool.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.cool.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
@@ -5477,14 +5477,14 @@
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。</t>
+          <t xml:space="preserve">…はい、わかりました。</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.cool.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5499,7 +5499,7 @@
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.cool.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
@@ -5516,7 +5516,7 @@
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.quiet.attack.cool</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5526,12 +5526,12 @@
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.attack.cool</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
@@ -5541,14 +5541,14 @@
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……戻れない</t>
+          <t xml:space="preserve">…ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.quiet.defend.cool</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.defend.cool</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
@@ -5573,29 +5573,29 @@
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……望むなら</t>
+          <t xml:space="preserve">…はい、わかりました。</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES.cool.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
@@ -5605,29 +5605,29 @@
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……静かに、離れたい。</t>
+          <t xml:space="preserve">（…何も言わず、目を伏せた）</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES.cool.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
@@ -5637,29 +5637,29 @@
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まあ、別にいいよ。</t>
+          <t xml:space="preserve">…ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_LEADER_LINES.cool.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_LEADER_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
@@ -5669,29 +5669,29 @@
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……リングで、会う。</t>
+          <t xml:space="preserve">…はい、加減します。</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.cool.quiet.hp_high[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet.hp_high[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
@@ -5701,29 +5701,29 @@
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……負け。それだけ</t>
+          <t xml:space="preserve">…ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.cool.quiet.hp_mid[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet.hp_mid[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
@@ -5733,29 +5733,29 @@
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……っ……</t>
+          <t xml:space="preserve">…ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.cool.quiet.high[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.quiet.attack.cool</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet.high[1]</t>
+          <t xml:space="preserve">quiet.attack.cool</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
@@ -5765,29 +5765,29 @@
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……結果がすべて、だ</t>
+          <t xml:space="preserve">……戻れない</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.cool.quiet.high[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.quiet.defend.cool</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet.high[1]</t>
+          <t xml:space="preserve">quiet.defend.cool</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
@@ -5797,14 +5797,14 @@
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……話すことは、もうない</t>
+          <t xml:space="preserve">……望むなら</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.cool.quiet.high[2]</t>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5814,12 +5814,12 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet.high[2]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
@@ -5829,14 +5829,14 @@
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……決着、つけよう</t>
+          <t xml:space="preserve">……静かに、離れたい。</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.cool.quiet.high[1]</t>
+          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5846,12 +5846,12 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
+          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet.high[1]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
@@ -5861,14 +5861,14 @@
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……いいだろう。受けて立つ</t>
+          <t xml:space="preserve">……まあ、別にいいよ。</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A.cool.quiet.high[1]</t>
+          <t xml:space="preserve">FACTION_F08_LEADER_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A</t>
+          <t xml:space="preserve">FACTION_F08_LEADER_LINES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet.high[1]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
@@ -5893,14 +5893,14 @@
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……話すことは、もう何もない</t>
+          <t xml:space="preserve">……リングで、会う。</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_B.cool.quiet.high[1]</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.cool.quiet.hp_high[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_B</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet.high[1]</t>
+          <t xml:space="preserve">cool.quiet.hp_high[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
@@ -5925,238 +5925,238 @@
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……受ける</t>
+          <t xml:space="preserve">……負け。それだけ</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.cool.quiet[1]</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.cool.quiet.hp_mid[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[1]</t>
+          <t xml:space="preserve">cool.quiet.hp_mid[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…変わった</t>
+          <t xml:space="preserve">……っ……</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.cool.quiet[1]</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.cool.quiet.high[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[1]</t>
+          <t xml:space="preserve">cool.quiet.high[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（——見えた）</t>
+          <t xml:space="preserve">……結果がすべて、だ</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.cool.quiet[1]</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.cool.quiet.high[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fresh.cool.quiet[1]</t>
+          <t xml:space="preserve">cool.quiet.high[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…体は軽い。…今日は、かなり…やれる</t>
+          <t xml:space="preserve">……話すことは、もうない</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.cool.quiet[1]</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.cool.quiet.high[2]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heavy.cool.quiet[1]</t>
+          <t xml:space="preserve">cool.quiet.high[2]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…重い。…やっても、抜けていくだけだ</t>
+          <t xml:space="preserve">……決着、つけよう</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.cool.quiet[1]</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.cool.quiet.high[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warm.cool.quiet[1]</t>
+          <t xml:space="preserve">cool.quiet.high[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…動けている。…ただ、深さがない</t>
+          <t xml:space="preserve">……いいだろう。受けて立つ</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.cool.quiet[1]</t>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A.cool.quiet.high[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.cool.quiet[1]</t>
+          <t xml:space="preserve">cool.quiet.high[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここまでだ</t>
+          <t xml:space="preserve">……話すことは、もう何もない</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.cool.quiet[1]</t>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_B.cool.quiet.high[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_B</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.cool.quiet[1]</t>
+          <t xml:space="preserve">cool.quiet.high[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ、止まらない</t>
+          <t xml:space="preserve">……受ける</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.cool.quiet[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.cool.quiet[1]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
@@ -6181,14 +6181,14 @@
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…実感はある</t>
+          <t xml:space="preserve">…変わった</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.cool.quiet[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">BT_HINT_LINES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.cool.quiet[1]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -6213,14 +6213,14 @@
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この静けさが、答えだ</t>
+          <t xml:space="preserve">（——見えた）</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.cool.quiet[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6230,12 +6230,12 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.cool.quiet[1]</t>
+          <t xml:space="preserve">fresh.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -6245,14 +6245,14 @@
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…背負っていく。この声を</t>
+          <t xml:space="preserve">…体は軽い。…今日は、かなり…やれる</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.cool.quiet[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[1]</t>
+          <t xml:space="preserve">heavy.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6277,14 +6277,14 @@
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……見えない</t>
+          <t xml:space="preserve">…重い。…やっても、抜けていくだけだ</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.cool.quiet[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[1]</t>
+          <t xml:space="preserve">warm.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6309,14 +6309,14 @@
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…闘える</t>
+          <t xml:space="preserve">…動けている。…ただ、深さがない</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.cool.quiet[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6326,12 +6326,12 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[1]</t>
+          <t xml:space="preserve">cap_reached.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6341,14 +6341,14 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……戻った</t>
+          <t xml:space="preserve">…ここまでだ</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.cool.quiet[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6358,12 +6358,12 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.cool.quiet[1]</t>
+          <t xml:space="preserve">ovr_elite.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6373,14 +6373,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…動けない</t>
+          <t xml:space="preserve">…まだ、止まらない</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.cool.quiet[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.cool.quiet[1]</t>
+          <t xml:space="preserve">ovr_growth.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6405,14 +6405,14 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……鈍い</t>
+          <t xml:space="preserve">…実感はある</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.cool.quiet[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6422,12 +6422,12 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.cool.quiet[1]</t>
+          <t xml:space="preserve">ovr_legend.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6437,14 +6437,14 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…遠い</t>
+          <t xml:space="preserve">…この静けさが、答えだ</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.cool.quiet[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.cool.quiet[1]</t>
+          <t xml:space="preserve">pop_star.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6469,14 +6469,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…心が、まだ</t>
+          <t xml:space="preserve">…背負っていく。この声を</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.cool.quiet[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6486,29 +6486,29 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">autumnWarChampion.cool.quiet[1]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全員の勝利だ。</t>
+          <t xml:space="preserve">……見えない</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.cool.quiet[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6518,29 +6518,29 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.cool.quiet[1]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一生の試合だった</t>
+          <t xml:space="preserve">…闘える</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.cool.quiet[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6550,29 +6550,29 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.cool.quiet[1]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ降りない</t>
+          <t xml:space="preserve">……戻った</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.cool.quiet[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6582,29 +6582,29 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.cool.quiet[1]</t>
+          <t xml:space="preserve">defeat.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悔いはない。…ありがとう</t>
+          <t xml:space="preserve">…動けない</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.cool.quiet[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6614,29 +6614,29 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.cool.quiet[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…感謝します</t>
+          <t xml:space="preserve">……鈍い</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.cool.quiet[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6646,29 +6646,29 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.cool.quiet[1]</t>
+          <t xml:space="preserve">injury_severe_recovery.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…積み重ねの結果だ</t>
+          <t xml:space="preserve">…遠い</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.cool.quiet[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6678,29 +6678,29 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.cool.quiet[1]</t>
+          <t xml:space="preserve">penalty_end.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…次</t>
+          <t xml:space="preserve">…心が、まだ</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.springTagChampion.cool.quiet[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6715,7 +6715,7 @@
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">springTagChampion.cool.quiet[1]</t>
+          <t xml:space="preserve">autumnWarChampion.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6725,14 +6725,14 @@
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相棒のおかげだ。</t>
+          <t xml:space="preserve">全員の勝利だ。</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.cool.quiet[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6742,12 +6742,12 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[1]</t>
+          <t xml:space="preserve">bestMatch.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6757,14 +6757,14 @@
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…行きます</t>
+          <t xml:space="preserve">…一生の試合だった</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.cool.quiet[2]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[2]</t>
+          <t xml:space="preserve">champion.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6789,14 +6789,14 @@
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ドームか。悪くない</t>
+          <t xml:space="preserve">…まだ降りない</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.cool.quiet[3]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6806,12 +6806,12 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[3]</t>
+          <t xml:space="preserve">hallOfFame.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6821,14 +6821,14 @@
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（視線だけで応える）</t>
+          <t xml:space="preserve">…悔いはない。…ありがとう</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.cool.quiet[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6838,12 +6838,12 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[1]</t>
+          <t xml:space="preserve">mediaAward.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6853,14 +6853,14 @@
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…満員</t>
+          <t xml:space="preserve">…感謝します</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.cool.quiet[2]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[2]</t>
+          <t xml:space="preserve">mvp.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6885,14 +6885,14 @@
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…忘れない</t>
+          <t xml:space="preserve">…積み重ねの結果だ</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.cool.quiet[3]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[3]</t>
+          <t xml:space="preserve">rookie.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6917,14 +6917,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（遠くを見ている）</t>
+          <t xml:space="preserve">…次</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.cool.quiet[1]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6934,29 +6934,29 @@
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.cool.quiet[1]</t>
+          <t xml:space="preserve">springTagChampion.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪くない。この調子で</t>
+          <t xml:space="preserve">相棒のおかげだ。</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.cool.quiet[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6966,29 +6966,29 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.cool.quiet[1]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪くない仲間だ</t>
+          <t xml:space="preserve">…行きます</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.cool.quiet[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6998,29 +6998,29 @@
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.cool.quiet[1]</t>
+          <t xml:space="preserve">cool.quiet[2]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…大丈夫だ。すぐ戻れる</t>
+          <t xml:space="preserve">…ドームか。悪くない</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.cool.quiet[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.cool.quiet[3]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7030,29 +7030,29 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.cool.quiet[1]</t>
+          <t xml:space="preserve">cool.quiet[3]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ファンの期待には応える</t>
+          <t xml:space="preserve">……（視線だけで応える）</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.cool.quiet[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7062,29 +7062,29 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.cool.quiet[1]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（静かに出口を見ている）</t>
+          <t xml:space="preserve">…満員</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.cool.quiet[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7094,29 +7094,29 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">breakthrough.voice.cool.quiet[1]</t>
+          <t xml:space="preserve">cool.quiet[2]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…環境に恵まれた。それは認める</t>
+          <t xml:space="preserve">…忘れない</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.cool.quiet[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.cool.quiet[3]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7126,29 +7126,29 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G2.voice.cool.quiet[1]</t>
+          <t xml:space="preserve">cool.quiet[3]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう。それだけのことだ</t>
+          <t xml:space="preserve">……（遠くを見ている）</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.cool.quiet[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7158,12 +7158,12 @@
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.voice.cool.quiet[1]</t>
+          <t xml:space="preserve">N1.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7173,14 +7173,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…チャンスは自分で作るものだと思っている</t>
+          <t xml:space="preserve">…悪くない。この調子で</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.cool.quiet[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R2.voice.cool.quiet[1]</t>
+          <t xml:space="preserve">N2.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7205,14 +7205,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…孤独には慣れている</t>
+          <t xml:space="preserve">…悪くない仲間だ</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.cool.quiet[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.modal.cool.quiet[1]</t>
+          <t xml:space="preserve">N3.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7237,14 +7237,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうか。…分かった</t>
+          <t xml:space="preserve">…大丈夫だ。すぐ戻れる</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.cool.quiet[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7254,12 +7254,12 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R4.voice.cool.quiet[1]</t>
+          <t xml:space="preserve">N4.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7269,14 +7269,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…次も同じ結果とは限らない。気を引き締めろ、自分</t>
+          <t xml:space="preserve">…ファンの期待には応える</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.cool.quiet[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.voice.cool.quiet[1]</t>
+          <t xml:space="preserve">N5_low.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7301,14 +7301,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…敗因は分かっている。次までに修正する</t>
+          <t xml:space="preserve">……（静かに出口を見ている）</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.cool.quiet[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7323,7 +7323,7 @@
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warVictory.voice.cool.quiet[1]</t>
+          <t xml:space="preserve">breakthrough.voice.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7333,14 +7333,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…当然の結果だ</t>
+          <t xml:space="preserve">…環境に恵まれた。それは認める</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.cool.quiet[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7350,29 +7350,29 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.cool.quiet[1]</t>
+          <t xml:space="preserve">G2.voice.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがたい</t>
+          <t xml:space="preserve">…そう。それだけのことだ</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.cool.quiet[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7382,29 +7382,29 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.cool.quiet[1]</t>
+          <t xml:space="preserve">G3.voice.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…追い込む</t>
+          <t xml:space="preserve">…チャンスは自分で作るものだと思っている</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.cool.quiet[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7414,29 +7414,29 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.cool.quiet[1]</t>
+          <t xml:space="preserve">R2.voice.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…分かった。応える</t>
+          <t xml:space="preserve">…孤独には慣れている</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.cool.quiet[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7446,29 +7446,29 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.cool.quiet[1]</t>
+          <t xml:space="preserve">R3.modal.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……分かった</t>
+          <t xml:space="preserve">…そうか。…分かった</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.cool.quiet[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7478,29 +7478,29 @@
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.cool.quiet[1]</t>
+          <t xml:space="preserve">R4.voice.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……やる</t>
+          <t xml:space="preserve">…次も同じ結果とは限らない。気を引き締めろ、自分</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.cool.quiet[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7510,29 +7510,29 @@
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.cool.quiet[1]</t>
+          <t xml:space="preserve">R5.voice.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪くなかった</t>
+          <t xml:space="preserve">…敗因は分かっている。次までに修正する</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.cool.quiet[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7542,29 +7542,29 @@
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.cool.quiet[1]</t>
+          <t xml:space="preserve">warVictory.voice.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…感謝する。少し休む</t>
+          <t xml:space="preserve">…当然の結果だ</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.cool.quiet[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.cool.quiet[1]</t>
+          <t xml:space="preserve">bonus.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7589,14 +7589,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…感謝する。早く戻る</t>
+          <t xml:space="preserve">…ありがたい</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.cool.quiet[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7611,7 +7611,7 @@
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.cool.quiet[1]</t>
+          <t xml:space="preserve">camp.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7621,14 +7621,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…吸収する。見ていてくれ</t>
+          <t xml:space="preserve">…追い込む</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.cool.quiet[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.cool.quiet[1]</t>
+          <t xml:space="preserve">encourage_high_trust.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7653,14 +7653,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……やる</t>
+          <t xml:space="preserve">…分かった。応える</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.cool.quiet[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7670,12 +7670,12 @@
       </c>
       <c r="C230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.cool.quiet[1]</t>
+          <t xml:space="preserve">encourage.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7685,14 +7685,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…他所から来た。報告する</t>
+          <t xml:space="preserve">……分かった</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.cool.quiet[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.cool.quiet[1]</t>
+          <t xml:space="preserve">media.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7717,14 +7717,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（静かにテーピングを外している）</t>
+          <t xml:space="preserve">……やる</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.cool.quiet[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7734,12 +7734,12 @@
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.cool.quiet[1]</t>
+          <t xml:space="preserve">party.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7749,14 +7749,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（無言のまま動かず、周囲だけが落ち着かなくなっている）</t>
+          <t xml:space="preserve">…悪くなかった</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.cool.quiet[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.cool.quiet[1]</t>
+          <t xml:space="preserve">refresh_leave.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7781,14 +7781,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに点を三つ置いただけの投稿。ファンの憶測だけが広がっていく）</t>
+          <t xml:space="preserve">…感謝する。少し休む</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.cool.quiet[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7798,12 +7798,12 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.cool.quiet[1]</t>
+          <t xml:space="preserve">special_treatment.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7813,14 +7813,14 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…タイトルマッチを。頼む</t>
+          <t xml:space="preserve">…感謝する。早く戻る</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.cool.quiet[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.cool.quiet[1]</t>
+          <t xml:space="preserve">trainer.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7845,14 +7845,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あいつとの試合を。頼む</t>
+          <t xml:space="preserve">…吸収する。見ていてくれ</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.cool.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7867,7 +7867,7 @@
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.cool.quiet[1]</t>
+          <t xml:space="preserve">E1.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7877,14 +7877,14 @@
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…休む必要がある</t>
+          <t xml:space="preserve">……やる</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.cool.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7899,7 +7899,7 @@
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.cool.quiet[1]</t>
+          <t xml:space="preserve">E6.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -7909,14 +7909,14 @@
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もう、限界だ（静かに、しかし断固として）</t>
+          <t xml:space="preserve">…他所から来た。報告する</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.cool.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7931,7 +7931,7 @@
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.cool.quiet[1]</t>
+          <t xml:space="preserve">S_boycott.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7941,14 +7941,14 @@
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（何も言わず、立ち去ろうとする）</t>
+          <t xml:space="preserve">………（静かにテーピングを外している）</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.cool.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7963,7 +7963,7 @@
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.cool.quiet[1]</t>
+          <t xml:space="preserve">S_grumble.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7973,14 +7973,14 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…鍛えたい。場所を貸してくれ</t>
+          <t xml:space="preserve">（無言のまま動かず、周囲だけが落ち着かなくなっている）</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.cool.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7995,7 +7995,7 @@
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.cool.quiet[1]</t>
+          <t xml:space="preserve">S_sns.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -8005,14 +8005,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…次の世代に、繋ぎたいものがある</t>
+          <t xml:space="preserve">（SNSに点を三つ置いただけの投稿。ファンの憶測だけが広がっていく）</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.cool.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8022,12 +8022,12 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.cool.quiet[1]</t>
+          <t xml:space="preserve">S1.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -8037,14 +8037,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…すぐ戻る</t>
+          <t xml:space="preserve">…タイトルマッチを。頼む</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.cool.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8054,12 +8054,12 @@
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.cool.quiet[1]</t>
+          <t xml:space="preserve">S2.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8069,14 +8069,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あれとは合わない。それだけだ</t>
+          <t xml:space="preserve">…あいつとの試合を。頼む</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.cool.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.cool.quiet[1]</t>
+          <t xml:space="preserve">S3.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8101,14 +8101,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…私は間違っていない</t>
+          <t xml:space="preserve">…休む必要がある</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.cool.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8118,12 +8118,12 @@
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.cool.quiet[1]</t>
+          <t xml:space="preserve">S4_direct.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8133,14 +8133,14 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…無駄口は叩かない。それがブランドには向いているかも</t>
+          <t xml:space="preserve">……もう、限界だ（静かに、しかし断固として）</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.cool.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.cool.quiet[1]</t>
+          <t xml:space="preserve">S4_silent.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8165,14 +8165,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…カメラか。まぁ、やる</t>
+          <t xml:space="preserve">……（何も言わず、立ち去ろうとする）</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.cool.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8182,12 +8182,12 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.cool.quiet[1]</t>
+          <t xml:space="preserve">S5.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8197,14 +8197,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…来てくれた人には、ちゃんと応えたい</t>
+          <t xml:space="preserve">…鍛えたい。場所を貸してくれ</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.cool.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.cool.quiet[1]</t>
+          <t xml:space="preserve">S6.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8229,14 +8229,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…余計なことはしない。ただ歩く。それだけだ</t>
+          <t xml:space="preserve">…次の世代に、繋ぎたいものがある</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.cool.quiet[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8251,7 +8251,7 @@
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.cool.quiet[1]</t>
+          <t xml:space="preserve">B1.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8261,14 +8261,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…写真か。余計なことはしないでくれ</t>
+          <t xml:space="preserve">…すぐ戻る</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.cool.quiet[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.cool.quiet[1]</t>
+          <t xml:space="preserve">B2_fighter1.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8293,14 +8293,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…無駄なことは言わない。それだけだ</t>
+          <t xml:space="preserve">…あれとは合わない。それだけだ</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.cool.quiet[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.cool.quiet[1]</t>
+          <t xml:space="preserve">B2_fighter2.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8325,14 +8325,14 @@
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やる。見ていてくれ</t>
+          <t xml:space="preserve">…私は間違っていない</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.cool.quiet[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8342,29 +8342,29 @@
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[1]</t>
+          <t xml:space="preserve">B4_brand.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…戦わせてくれるなら、応える</t>
+          <t xml:space="preserve">…無駄口は叩かない。それがブランドには向いているかも</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.cool.quiet[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8374,29 +8374,29 @@
       </c>
       <c r="C252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[1]</t>
+          <t xml:space="preserve">B4_cm.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……よろしく</t>
+          <t xml:space="preserve">…カメラか。まぁ、やる</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.cool.quiet[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8406,29 +8406,29 @@
       </c>
       <c r="C253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[2]</t>
+          <t xml:space="preserve">B4_fan.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……始めよう</t>
+          <t xml:space="preserve">…来てくれた人には、ちゃんと応えたい</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.cool.quiet[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8438,29 +8438,29 @@
       </c>
       <c r="C254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[1]</t>
+          <t xml:space="preserve">B4_fashion.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やる。見ていてくれ</t>
+          <t xml:space="preserve">…余計なことはしない。ただ歩く。それだけだ</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.cool.quiet[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8470,29 +8470,29 @@
       </c>
       <c r="C255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[1]</t>
+          <t xml:space="preserve">B4_gravure.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やるべきことをやる</t>
+          <t xml:space="preserve">…写真か。余計なことはしないでくれ</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.cool.quiet[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8502,29 +8502,29 @@
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[2]</t>
+          <t xml:space="preserve">B4_variety.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……すぐ戻る</t>
+          <t xml:space="preserve">…無駄なことは言わない。それだけだ</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.cool.quiet[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8534,29 +8534,29 @@
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.cool.quiet[1]</t>
+          <t xml:space="preserve">B4.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……終わった。それだけだ。……それだけのはずだ</t>
+          <t xml:space="preserve">…やる。見ていてくれ</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.cool.quiet[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8566,12 +8566,12 @@
       </c>
       <c r="C258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.cool.quiet[1]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8581,14 +8581,14 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……終わっていない。……私の中では</t>
+          <t xml:space="preserve">…戦わせてくれるなら、応える</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.cool.quiet[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8598,12 +8598,12 @@
       </c>
       <c r="C259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.cool.quiet[1]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8613,14 +8613,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…戦わせてくれるなら、応える</t>
+          <t xml:space="preserve">……よろしく</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.cool.quiet[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8630,12 +8630,12 @@
       </c>
       <c r="C260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.cool.quiet[1]</t>
+          <t xml:space="preserve">cool.quiet[2]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8645,14 +8645,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……よろしく</t>
+          <t xml:space="preserve">……始めよう</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.cool.quiet[2]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8662,12 +8662,12 @@
       </c>
       <c r="C261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.cool.quiet[2]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8677,14 +8677,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……始めよう</t>
+          <t xml:space="preserve">…やる。見ていてくれ</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.cool.quiet[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8694,12 +8694,12 @@
       </c>
       <c r="C262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.cool.quiet[1]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8709,14 +8709,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ここでやる。……結果で返す</t>
+          <t xml:space="preserve">…やるべきことをやる</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.cool.quiet[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8726,12 +8726,12 @@
       </c>
       <c r="C263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.cool.quiet[1]</t>
+          <t xml:space="preserve">cool.quiet[2]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8741,14 +8741,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やる。見ていてくれ</t>
+          <t xml:space="preserve">……すぐ戻る</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.cool.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8763,7 +8763,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.cool.quiet[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8773,14 +8773,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やるべきことをやる</t>
+          <t xml:space="preserve">……終わった。それだけだ。……それだけのはずだ</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.cool.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8795,7 +8795,7 @@
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.fresh.cool.quiet[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8805,14 +8805,14 @@
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…体は軽い。…今日は、かなり…やれる</t>
+          <t xml:space="preserve">……終わっていない。……私の中では</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.cool.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8827,7 +8827,7 @@
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.heavy.cool.quiet[1]</t>
+          <t xml:space="preserve">draftInterest.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8837,14 +8837,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…重い。…やっても、抜けていくだけだ</t>
+          <t xml:space="preserve">…戦わせてくれるなら、応える</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.cool.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.warm.cool.quiet[1]</t>
+          <t xml:space="preserve">draftJoin.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8869,14 +8869,14 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…動けている。…ただ、深さがない</t>
+          <t xml:space="preserve">……よろしく</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.cool.quiet[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8891,7 +8891,7 @@
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.cool.quiet[2]</t>
+          <t xml:space="preserve">draftJoin.cool.quiet[2]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -8901,14 +8901,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……すぐ戻る</t>
+          <t xml:space="preserve">……始めよう</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.cool.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8923,7 +8923,7 @@
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.cool.quiet[1]</t>
+          <t xml:space="preserve">faGreeting.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -8933,14 +8933,14 @@
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（静かに立ち去る）</t>
+          <t xml:space="preserve">……ここでやる。……結果で返す</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.cool.quiet[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.cool.quiet[2]</t>
+          <t xml:space="preserve">faSigning.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -8965,14 +8965,14 @@
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ありがとう</t>
+          <t xml:space="preserve">…やる。見ていてくれ</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.cool.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8987,7 +8987,7 @@
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.cool.quiet[1]</t>
+          <t xml:space="preserve">faWelcome.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -8997,14 +8997,14 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やるべきことはやる</t>
+          <t xml:space="preserve">…やるべきことをやる</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.cool.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -9019,7 +9019,7 @@
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.cool.quiet[1]</t>
+          <t xml:space="preserve">heatSelf.fresh.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -9029,14 +9029,14 @@
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…期待には、応える</t>
+          <t xml:space="preserve">…体は軽い。…今日は、かなり…やれる</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.cool.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9051,7 +9051,7 @@
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.cool.quiet[1]</t>
+          <t xml:space="preserve">heatSelf.heavy.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9061,14 +9061,14 @@
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…次で終わらせる</t>
+          <t xml:space="preserve">…重い。…やっても、抜けていくだけだ</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.cool.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9083,7 +9083,7 @@
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.cool.quiet[1]</t>
+          <t xml:space="preserve">heatSelf.warm.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9093,14 +9093,14 @@
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…次も勝つ。それだけだ</t>
+          <t xml:space="preserve">…動けている。…ただ、深さがない</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.cool.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9115,7 +9115,7 @@
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.cool.quiet[1]</t>
+          <t xml:space="preserve">injury.cool.quiet[2]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9125,14 +9125,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…認めよう。だが、終わりではない</t>
+          <t xml:space="preserve">……すぐ戻る</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.cool.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.cool.quiet[1]</t>
+          <t xml:space="preserve">release.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9157,14 +9157,14 @@
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ようやくだ。この座は渡さない</t>
+          <t xml:space="preserve">……（静かに立ち去る）</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.cool.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9174,12 +9174,12 @@
       </c>
       <c r="C277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[1]</t>
+          <t xml:space="preserve">release.cool.quiet[2]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9189,14 +9189,14 @@
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（静かに立ち去る）</t>
+          <t xml:space="preserve">……ありがとう</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.cool.quiet[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9206,12 +9206,12 @@
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[2]</t>
+          <t xml:space="preserve">rentalGreeting.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9221,14 +9221,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ありがとう</t>
+          <t xml:space="preserve">…やるべきことはやる</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.cool.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9238,12 +9238,12 @@
       </c>
       <c r="C279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[1]</t>
+          <t xml:space="preserve">scoutGreeting.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9253,14 +9253,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やるべきことはやる</t>
+          <t xml:space="preserve">…期待には、応える</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.cool.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9270,12 +9270,12 @@
       </c>
       <c r="C280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9292,7 +9292,7 @@
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.cool.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9302,12 +9302,12 @@
       </c>
       <c r="C281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[1]</t>
+          <t xml:space="preserve">titleDefense.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9324,7 +9324,7 @@
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.cool.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9334,12 +9334,12 @@
       </c>
       <c r="C282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[1]</t>
+          <t xml:space="preserve">titleLoss.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9356,7 +9356,7 @@
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.cool.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9366,12 +9366,12 @@
       </c>
       <c r="C283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[1]</t>
+          <t xml:space="preserve">titleWin.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9388,7 +9388,7 @@
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.quiet.cool[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9398,29 +9398,29 @@
       </c>
       <c r="C284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.quiet.cool[1]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……終わりだ</t>
+          <t xml:space="preserve">……（静かに立ち去る）</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.quiet.cool[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9430,29 +9430,29 @@
       </c>
       <c r="C285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.quiet.cool[1]</t>
+          <t xml:space="preserve">cool.quiet[2]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……遠い</t>
+          <t xml:space="preserve">……ありがとう</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.quiet.cool[2]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9462,29 +9462,29 @@
       </c>
       <c r="C286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.quiet.cool[2]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もう、隣にいない</t>
+          <t xml:space="preserve">…やるべきことはやる</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.quiet.cool[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9494,29 +9494,29 @@
       </c>
       <c r="C287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.quiet.cool[1]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……悪くない距離感だ</t>
+          <t xml:space="preserve">…次で終わらせる</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.quiet.cool[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9526,29 +9526,29 @@
       </c>
       <c r="C288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.quiet.cool[1]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……この人だけは、信じられる</t>
+          <t xml:space="preserve">…次も勝つ。それだけだ</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.quiet.cool[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9558,29 +9558,29 @@
       </c>
       <c r="C289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.quiet.cool[1]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もう考えない</t>
+          <t xml:space="preserve">…認めよう。だが、終わりではない</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.quiet.cool[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9590,29 +9590,29 @@
       </c>
       <c r="C290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.quiet.cool[2]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……風が止んだ</t>
+          <t xml:space="preserve">…ようやくだ。この座は渡さない</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.quiet.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.quiet.cool[1]</t>
+          <t xml:space="preserve">bond_39_down.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9637,14 +9637,14 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……気になる。ただ、それだけだが</t>
+          <t xml:space="preserve">……終わりだ</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.quiet.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9659,7 +9659,7 @@
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.quiet.cool[1]</t>
+          <t xml:space="preserve">bond_59_down.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9669,14 +9669,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……超えなければ、先へ進めない</t>
+          <t xml:space="preserve">……遠い</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.quiet.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.quiet.cool[2]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9691,7 +9691,7 @@
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.quiet.cool[1]</t>
+          <t xml:space="preserve">bond_59_down.quiet.cool[2]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9701,14 +9701,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……あの相手がいる限り、立ち続ける</t>
+          <t xml:space="preserve">……もう、隣にいない</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.quiet.cool[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9723,7 +9723,7 @@
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.quiet.cool[2]</t>
+          <t xml:space="preserve">bond_60_up.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9733,14 +9733,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……言葉はいらない。リングで話す</t>
+          <t xml:space="preserve">……悪くない距離感だ</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.quiet.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9755,7 +9755,7 @@
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.quiet.cool[1]</t>
+          <t xml:space="preserve">bond_80_up.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9765,14 +9765,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ここにいたい</t>
+          <t xml:space="preserve">……この人だけは、信じられる</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.quiet.cool[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9787,7 +9787,7 @@
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.quiet.cool[2]</t>
+          <t xml:space="preserve">rivalry_29_down.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9797,14 +9797,14 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……この場所を守る</t>
+          <t xml:space="preserve">……もう考えない</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.quiet.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.quiet.cool[2]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9819,7 +9819,7 @@
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.quiet.cool[1]</t>
+          <t xml:space="preserve">rivalry_29_down.quiet.cool[2]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9829,14 +9829,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（荷物をまとめている）</t>
+          <t xml:space="preserve">……風が止んだ</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.quiet.cool[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9851,7 +9851,7 @@
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.quiet.cool[2]</t>
+          <t xml:space="preserve">rivalry_30_up.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -9861,14 +9861,14 @@
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……何も、残っていない</t>
+          <t xml:space="preserve">……気になる。ただ、それだけだが</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.quiet.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9883,7 +9883,7 @@
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.quiet.cool[1]</t>
+          <t xml:space="preserve">rivalry_50_up.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -9893,14 +9893,14 @@
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……この場所に、未来はあるのか</t>
+          <t xml:space="preserve">……超えなければ、先へ進めない</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.cool.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9910,12 +9910,12 @@
       </c>
       <c r="C300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[1]</t>
+          <t xml:space="preserve">rivalry_70_up.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -9925,14 +9925,14 @@
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……調子は落ち着いた。だが後退じゃない</t>
+          <t xml:space="preserve">……あの相手がいる限り、立ち続ける</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.cool.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.quiet.cool[2]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9942,29 +9942,29 @@
       </c>
       <c r="C301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.cool.quiet[1]</t>
+          <t xml:space="preserve">rivalry_70_up.quiet.cool[2]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……最後。立てる。十分</t>
+          <t xml:space="preserve">……言葉はいらない。リングで話す</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.cool.quiet[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -9974,29 +9974,29 @@
       </c>
       <c r="C302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.cool.quiet[2]</t>
+          <t xml:space="preserve">trust_above_75.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……傷は数えない。ただ、いく</t>
+          <t xml:space="preserve">……ここにいたい</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.cool.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.quiet.cool[2]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -10006,29 +10006,29 @@
       </c>
       <c r="C303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.cool.quiet[1]</t>
+          <t xml:space="preserve">trust_above_75.quiet.cool[2]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次</t>
+          <t xml:space="preserve">……この場所を守る</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.cool.quiet[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -10038,29 +10038,29 @@
       </c>
       <c r="C304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.cool.quiet[2]</t>
+          <t xml:space="preserve">trust_below_20.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……倒す。残る</t>
+          <t xml:space="preserve">……（荷物をまとめている）</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.cool.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.quiet.cool[2]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10070,29 +10070,29 @@
       </c>
       <c r="C305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.cool.quiet[1]</t>
+          <t xml:space="preserve">trust_below_20.quiet.cool[2]</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……一人。まだ立ってる。次</t>
+          <t xml:space="preserve">……何も、残っていない</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.cool.quiet[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.quiet.cool[1]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -10102,29 +10102,29 @@
       </c>
       <c r="C306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.cool.quiet[2]</t>
+          <t xml:space="preserve">trust_below_35.quiet.cool[1]</t>
         </is>
       </c>
       <c r="E306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F306" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……退かない。出せ</t>
+          <t xml:space="preserve">……この場所に、未来はあるのか</t>
         </is>
       </c>
     </row>
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.cool.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -10134,29 +10134,29 @@
       </c>
       <c r="C307" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.cool.quiet[1]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E307" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F307" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……三人の結果。言葉は要らない</t>
+          <t xml:space="preserve">……調子は落ち着いた。だが後退じゃない</t>
         </is>
       </c>
     </row>
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.cool.quiet[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -10166,12 +10166,12 @@
       </c>
       <c r="C308" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.cool.quiet[2]</t>
+          <t xml:space="preserve">preFinal.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E308" t="inlineStr" s="2">
@@ -10181,14 +10181,14 @@
       </c>
       <c r="F308" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……一人では不可能だった。それは認める</t>
+          <t xml:space="preserve">……最後。立てる。十分</t>
         </is>
       </c>
     </row>
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.cool.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -10198,12 +10198,12 @@
       </c>
       <c r="C309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.cool.quiet[1]</t>
+          <t xml:space="preserve">preFinal.cool.quiet[2]</t>
         </is>
       </c>
       <c r="E309" t="inlineStr" s="2">
@@ -10213,14 +10213,14 @@
       </c>
       <c r="F309" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……不十分だった。次がある</t>
+          <t xml:space="preserve">……傷は数えない。ただ、いく</t>
         </is>
       </c>
     </row>
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.cool.quiet[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -10230,12 +10230,12 @@
       </c>
       <c r="C310" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D310" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.cool.quiet[2]</t>
+          <t xml:space="preserve">preMatch.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E310" t="inlineStr" s="2">
@@ -10245,14 +10245,14 @@
       </c>
       <c r="F310" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……団体が負けた。それが全て。次に期す</t>
+          <t xml:space="preserve">……次</t>
         </is>
       </c>
     </row>
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.cool.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -10262,12 +10262,12 @@
       </c>
       <c r="C311" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D311" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.cool.quiet[1]</t>
+          <t xml:space="preserve">preMatch.cool.quiet[2]</t>
         </is>
       </c>
       <c r="E311" t="inlineStr" s="2">
@@ -10277,14 +10277,14 @@
       </c>
       <c r="F311" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……立っている。それが結果</t>
+          <t xml:space="preserve">……倒す。残る</t>
         </is>
       </c>
     </row>
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.cool.quiet[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10294,12 +10294,12 @@
       </c>
       <c r="C312" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.cool.quiet[2]</t>
+          <t xml:space="preserve">survivor.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E312" t="inlineStr" s="2">
@@ -10309,14 +10309,14 @@
       </c>
       <c r="F312" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……数えてない。ただ、倒れなかった</t>
+          <t xml:space="preserve">……一人。まだ立ってる。次</t>
         </is>
       </c>
     </row>
     <row r="313" ht="40" customHeight="1">
       <c r="A313" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.cool.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -10326,12 +10326,12 @@
       </c>
       <c r="C313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D313" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.cool.quiet[1]</t>
+          <t xml:space="preserve">survivor.cool.quiet[2]</t>
         </is>
       </c>
       <c r="E313" t="inlineStr" s="2">
@@ -10341,14 +10341,14 @@
       </c>
       <c r="F313" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（トロフィーを静かに掲げる）</t>
+          <t xml:space="preserve">……退かない。出せ</t>
         </is>
       </c>
     </row>
     <row r="314" ht="40" customHeight="1">
       <c r="A314" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.cool.quiet[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="C314" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D314" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.cool.quiet[2]</t>
+          <t xml:space="preserve">champion.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E314" t="inlineStr" s="2">
@@ -10373,14 +10373,14 @@
       </c>
       <c r="F314" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…………ありがとう</t>
+          <t xml:space="preserve">……三人の結果。言葉は要らない</t>
         </is>
       </c>
     </row>
     <row r="315" ht="40" customHeight="1">
       <c r="A315" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.cool.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
@@ -10390,12 +10390,12 @@
       </c>
       <c r="C315" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D315" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.cool.quiet[1]</t>
+          <t xml:space="preserve">champion.cool.quiet[2]</t>
         </is>
       </c>
       <c r="E315" t="inlineStr" s="2">
@@ -10405,14 +10405,14 @@
       </c>
       <c r="F315" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（無言で去る）</t>
+          <t xml:space="preserve">……一人では不可能だった。それは認める</t>
         </is>
       </c>
     </row>
     <row r="316" ht="40" customHeight="1">
       <c r="A316" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.cool.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B316" t="inlineStr" s="2">
@@ -10422,12 +10422,12 @@
       </c>
       <c r="C316" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D316" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.cool.quiet[1]</t>
+          <t xml:space="preserve">defiant.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E316" t="inlineStr" s="2">
@@ -10437,14 +10437,14 @@
       </c>
       <c r="F316" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（静かに頷く）</t>
+          <t xml:space="preserve">……不十分だった。次がある</t>
         </is>
       </c>
     </row>
     <row r="317" ht="40" customHeight="1">
       <c r="A317" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.cool.quiet[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B317" t="inlineStr" s="2">
@@ -10454,12 +10454,12 @@
       </c>
       <c r="C317" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D317" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.cool.quiet[2]</t>
+          <t xml:space="preserve">defiant.cool.quiet[2]</t>
         </is>
       </c>
       <c r="E317" t="inlineStr" s="2">
@@ -10469,14 +10469,14 @@
       </c>
       <c r="F317" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まだ</t>
+          <t xml:space="preserve">……団体が負けた。それが全て。次に期す</t>
         </is>
       </c>
     </row>
     <row r="318" ht="40" customHeight="1">
       <c r="A318" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.cool.quiet[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B318" t="inlineStr" s="2">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="C318" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D318" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.cool.quiet[2]</t>
+          <t xml:space="preserve">gauntlet.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E318" t="inlineStr" s="2">
@@ -10501,14 +10501,14 @@
       </c>
       <c r="F318" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（少し笑顔を見せる）</t>
+          <t xml:space="preserve">……立っている。それが結果</t>
         </is>
       </c>
     </row>
     <row r="319" ht="40" customHeight="1">
       <c r="A319" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.cool.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B319" t="inlineStr" s="2">
@@ -10518,12 +10518,12 @@
       </c>
       <c r="C319" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D319" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.cool.quiet[1]</t>
+          <t xml:space="preserve">gauntlet.cool.quiet[2]</t>
         </is>
       </c>
       <c r="E319" t="inlineStr" s="2">
@@ -10533,14 +10533,14 @@
       </c>
       <c r="F319" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……最後</t>
+          <t xml:space="preserve">……数えてない。ただ、倒れなかった</t>
         </is>
       </c>
     </row>
     <row r="320" ht="40" customHeight="1">
       <c r="A320" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.cool.quiet[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B320" t="inlineStr" s="2">
@@ -10555,7 +10555,7 @@
       </c>
       <c r="D320" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.cool.quiet[2]</t>
+          <t xml:space="preserve">champion.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E320" t="inlineStr" s="2">
@@ -10565,14 +10565,14 @@
       </c>
       <c r="F320" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……全部、出す</t>
+          <t xml:space="preserve">……（トロフィーを静かに掲げる）</t>
         </is>
       </c>
     </row>
     <row r="321" ht="40" customHeight="1">
       <c r="A321" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.cool.quiet[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B321" t="inlineStr" s="2">
@@ -10587,7 +10587,7 @@
       </c>
       <c r="D321" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.cool.quiet[2]</t>
+          <t xml:space="preserve">champion.cool.quiet[2]</t>
         </is>
       </c>
       <c r="E321" t="inlineStr" s="2">
@@ -10597,14 +10597,14 @@
       </c>
       <c r="F321" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（拳を握る）</t>
+          <t xml:space="preserve">…………ありがとう</t>
         </is>
       </c>
     </row>
     <row r="322" ht="40" customHeight="1">
       <c r="A322" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.cool.quiet[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B322" t="inlineStr" s="2">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="D322" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.cool.quiet[2]</t>
+          <t xml:space="preserve">postLose.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E322" t="inlineStr" s="2">
@@ -10629,14 +10629,14 @@
       </c>
       <c r="F322" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（静かに頷く）</t>
+          <t xml:space="preserve">……（無言で去る）</t>
         </is>
       </c>
     </row>
     <row r="323" ht="40" customHeight="1">
       <c r="A323" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.cool.quiet[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B323" t="inlineStr" s="2">
@@ -10646,12 +10646,12 @@
       </c>
       <c r="C323" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D323" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[1]</t>
+          <t xml:space="preserve">postMatchWin.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E323" t="inlineStr" s="2">
@@ -10661,14 +10661,14 @@
       </c>
       <c r="F323" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…結果で語る</t>
+          <t xml:space="preserve">……（静かに頷く）</t>
         </is>
       </c>
     </row>
     <row r="324" ht="40" customHeight="1">
       <c r="A324" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.cool.quiet[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B324" t="inlineStr" s="2">
@@ -10678,12 +10678,12 @@
       </c>
       <c r="C324" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D324" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[1]</t>
+          <t xml:space="preserve">postMatchWin.cool.quiet[2]</t>
         </is>
       </c>
       <c r="E324" t="inlineStr" s="2">
@@ -10693,14 +10693,14 @@
       </c>
       <c r="F324" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（ベルトを静かに抱きしめる）</t>
+          <t xml:space="preserve">……まだ</t>
         </is>
       </c>
     </row>
     <row r="325" ht="40" customHeight="1">
       <c r="A325" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.cool.quiet[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B325" t="inlineStr" s="2">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="C325" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D325" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[1]</t>
+          <t xml:space="preserve">postWin.cool.quiet[2]</t>
         </is>
       </c>
       <c r="E325" t="inlineStr" s="2">
@@ -10725,14 +10725,14 @@
       </c>
       <c r="F325" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……来い</t>
+          <t xml:space="preserve">……（少し笑顔を見せる）</t>
         </is>
       </c>
     </row>
     <row r="326" ht="40" customHeight="1">
       <c r="A326" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.cool.quiet[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B326" t="inlineStr" s="2">
@@ -10742,12 +10742,12 @@
       </c>
       <c r="C326" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D326" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[2]</t>
+          <t xml:space="preserve">preFinal.cool.quiet[1]</t>
         </is>
       </c>
       <c r="E326" t="inlineStr" s="2">
@@ -10757,14 +10757,14 @@
       </c>
       <c r="F326" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（背を向ける）</t>
+          <t xml:space="preserve">……最後</t>
         </is>
       </c>
     </row>
     <row r="327" ht="40" customHeight="1">
       <c r="A327" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.cool.quiet[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B327" t="inlineStr" s="2">
@@ -10774,12 +10774,12 @@
       </c>
       <c r="C327" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D327" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.cool.quiet[2]</t>
+          <t xml:space="preserve">preFinal.cool.quiet[2]</t>
         </is>
       </c>
       <c r="E327" t="inlineStr" s="2">
@@ -10789,14 +10789,14 @@
       </c>
       <c r="F327" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（拳を握りしめる）</t>
+          <t xml:space="preserve">……全部、出す</t>
         </is>
       </c>
     </row>
     <row r="328" ht="40" customHeight="1">
       <c r="A328" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.cool.quiet[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B328" t="inlineStr" s="2">
@@ -10806,12 +10806,12 @@
       </c>
       <c r="C328" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D328" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.cool.quiet[1]</t>
+          <t xml:space="preserve">preMatch.cool.quiet[2]</t>
         </is>
       </c>
       <c r="E328" t="inlineStr" s="2">
@@ -10821,14 +10821,14 @@
       </c>
       <c r="F328" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（静かに頷く）</t>
+          <t xml:space="preserve">……（拳を握る）</t>
         </is>
       </c>
     </row>
     <row r="329" ht="40" customHeight="1">
       <c r="A329" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.cool.quiet[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B329" t="inlineStr" s="2">
@@ -10838,12 +10838,12 @@
       </c>
       <c r="C329" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D329" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[1]</t>
+          <t xml:space="preserve">summon.cool.quiet[2]</t>
         </is>
       </c>
       <c r="E329" t="inlineStr" s="2">
@@ -10853,14 +10853,14 @@
       </c>
       <c r="F329" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……証明した。それだけ</t>
+          <t xml:space="preserve">……（静かに頷く）</t>
         </is>
       </c>
     </row>
     <row r="330" ht="40" customHeight="1">
       <c r="A330" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.cool.quiet[2]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B330" t="inlineStr" s="2">
@@ -10870,12 +10870,12 @@
       </c>
       <c r="C330" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D330" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[2]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E330" t="inlineStr" s="2">
@@ -10885,14 +10885,14 @@
       </c>
       <c r="F330" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……これがうちの力</t>
+          <t xml:space="preserve">…結果で語る</t>
         </is>
       </c>
     </row>
     <row r="331" ht="40" customHeight="1">
       <c r="A331" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.cool.quiet[3]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B331" t="inlineStr" s="2">
@@ -10902,12 +10902,12 @@
       </c>
       <c r="C331" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D331" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[3]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E331" t="inlineStr" s="2">
@@ -10917,14 +10917,14 @@
       </c>
       <c r="F331" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（静かに頷く）</t>
+          <t xml:space="preserve">………（ベルトを静かに抱きしめる）</t>
         </is>
       </c>
     </row>
     <row r="332" ht="40" customHeight="1">
       <c r="A332" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.cool.quiet[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.cool.quiet[1]</t>
         </is>
       </c>
       <c r="B332" t="inlineStr" s="2">
@@ -10934,29 +10934,29 @@
       </c>
       <c r="C332" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D332" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.cool.quiet[1]</t>
+          <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
       <c r="E332" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F332" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここまで来たか</t>
+          <t xml:space="preserve">……来い</t>
         </is>
       </c>
     </row>
     <row r="333" ht="40" customHeight="1">
       <c r="A333" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.cool.quiet[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.cool.quiet[2]</t>
         </is>
       </c>
       <c r="B333" t="inlineStr" s="2">
@@ -10966,59 +10966,283 @@
       </c>
       <c r="C333" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D333" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.quiet[1]</t>
+          <t xml:space="preserve">cool.quiet[2]</t>
         </is>
       </c>
       <c r="E333" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F333" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ここでやる。……結果で返す</t>
+          <t xml:space="preserve">……（背を向ける）</t>
         </is>
       </c>
     </row>
     <row r="334" ht="40" customHeight="1">
       <c r="A334" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.cool.quiet[2]</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_lose.cool.quiet[2]</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……（拳を握りしめる）</t>
+        </is>
+      </c>
+    </row>
+    <row r="335" ht="40" customHeight="1">
+      <c r="A335" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.cool.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.cool.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……（静かに頷く）</t>
+        </is>
+      </c>
+    </row>
+    <row r="336" ht="40" customHeight="1">
+      <c r="A336" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.cool.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">cool.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……証明した。それだけ</t>
+        </is>
+      </c>
+    </row>
+    <row r="337" ht="40" customHeight="1">
+      <c r="A337" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.cool.quiet[2]</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">cool.quiet[2]</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……これがうちの力</t>
+        </is>
+      </c>
+    </row>
+    <row r="338" ht="40" customHeight="1">
+      <c r="A338" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.cool.quiet[3]</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">cool.quiet[3]</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……（静かに頷く）</t>
+        </is>
+      </c>
+    </row>
+    <row r="339" ht="40" customHeight="1">
+      <c r="A339" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.cool.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.cool.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ここまで来たか</t>
+        </is>
+      </c>
+    </row>
+    <row r="340" ht="40" customHeight="1">
+      <c r="A340" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.cool.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">cool.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……ここでやる。……結果で返す</t>
+        </is>
+      </c>
+    </row>
+    <row r="341" ht="40" customHeight="1">
+      <c r="A341" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.cool.quiet[1]</t>
         </is>
       </c>
-      <c r="B334" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr" s="2">
+      <c r="B341" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D334" t="inlineStr" s="12">
+      <c r="D341" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">cool.quiet[1]</t>
         </is>
       </c>
-      <c r="E334" t="inlineStr" s="2">
+      <c r="E341" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F334" t="inlineStr" s="3">
+      <c r="F341" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…期待には、応える</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H334"/>
+  <autoFilter ref="A1:H341"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/クール×寡黙.xlsx
+++ b/セリフ編集/キャラタイプ別/クール×寡黙.xlsx
@@ -2277,7 +2277,7 @@
       </c>
       <c r="F61" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……社長。あの人と。</t>
+          <t xml:space="preserve">……社長。三人で、あちらへ。</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="F62" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……願いが、ひとつ。あの人と。</t>
+          <t xml:space="preserve">……願いが、ひとつ。三人で、あの団体へ。</t>
         </is>
       </c>
     </row>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="F63" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……やりたい相手が、います。</t>
+          <t xml:space="preserve">……行きたい団体が、あります。三人で。</t>
         </is>
       </c>
     </row>
